--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="98">
   <si>
     <t xml:space="preserve">CannonTurretTrain</t>
   </si>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="98">
   <si>
     <t xml:space="preserve">CannonTurretTrain</t>
   </si>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="13965" windowHeight="11670" activeTab="1"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Train_Data" sheetId="1" r:id="rId4"/>
@@ -15,84 +15,192 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="98">
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_cooldown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_projectile_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_projectile_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_projectile_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
   <si>
     <t xml:space="preserve">CannonTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">ColdAirRangeTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
   </si>
   <si>
     <t xml:space="preserve">SniperProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+    <t xml:space="preserve">SniperTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">MissileProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑에 강화 버전이다.</t>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
   </si>
   <si>
     <t xml:space="preserve">레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강하게&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
@@ -101,214 +209,106 @@
     <t xml:space="preserve">저격을 발사해 몇 초 후 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
   </si>
   <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has_skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
     <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
   </si>
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has_skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
     <t xml:space="preserve">range_projectile_prefab_id</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">skill_projectile_prefab_id</t>
   </si>
   <si>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+  </si>
+  <si>
     <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+    <t xml:space="preserve">냉기 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">미사일 포탑</t>
   </si>
   <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
     <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_cooldown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑에 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_projectile_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_projectile_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_projectile_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
   </si>
 </sst>
 </file>
@@ -1012,46 +1012,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1059,19 +1059,19 @@
         <v>20001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1106,67 +1106,67 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="16.75" customHeight="1">
@@ -1174,29 +1174,29 @@
         <v>40001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P2" s="1">
         <v>50</v>
@@ -1208,7 +1208,7 @@
         <v>4</v>
       </c>
       <c r="S2" s="0" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="T2" s="0">
         <v>30</v>
@@ -1222,29 +1222,29 @@
         <v>40002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D3" s="1">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" s="1">
         <v>1</v>
@@ -1256,7 +1256,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="S3" s="0" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="T3" s="0">
         <v>30</v>
@@ -1282,10 +1282,10 @@
         <v>41001</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1">
         <v>150</v>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1313,7 +1313,7 @@
         <v>4</v>
       </c>
       <c r="S7" s="0" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="T7" s="0">
         <v>30</v>
@@ -1327,10 +1327,10 @@
         <v>41002</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="D8" s="1">
         <v>150</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1358,7 +1358,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="S8" s="0" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="T8" s="0">
         <v>30</v>
@@ -1409,70 +1409,70 @@
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="16.75" customHeight="1">
@@ -1480,22 +1480,22 @@
         <v>30001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1517,7 +1517,7 @@
         <v>1</v>
       </c>
       <c r="T2" s="0" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="U2" s="0">
         <v>30</v>
@@ -1531,22 +1531,22 @@
         <v>30002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1568,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="T3" s="0" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="U3" s="0">
         <v>30</v>
@@ -1582,22 +1582,22 @@
         <v>30003</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="D4" s="1">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1619,7 +1619,7 @@
         <v>1</v>
       </c>
       <c r="T4" s="0" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="U4" s="0">
         <v>30</v>
@@ -1633,22 +1633,22 @@
         <v>30004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D5" s="1">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1670,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="T5" s="0" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="U5" s="0">
         <v>30</v>
@@ -1684,22 +1684,22 @@
         <v>30005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="D6" s="1">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1721,7 +1721,7 @@
         <v>3</v>
       </c>
       <c r="T6" s="0" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="U6" s="0">
         <v>30</v>
@@ -1735,29 +1735,29 @@
         <v>30006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="D7" s="1">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E7" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P7" s="1">
         <v>50</v>
@@ -1772,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="T7" s="0" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="U7" s="0">
         <v>30</v>
@@ -1786,22 +1786,22 @@
         <v>30007</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="D8" s="1">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="E8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1823,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="T8" s="0" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="U8" s="0">
         <v>30</v>
@@ -1846,10 +1846,10 @@
         <v>31001</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1">
         <v>150</v>
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="H12" s="1" t="b">
         <v>1</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="0" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="U12" s="0">
         <v>30</v>
@@ -1897,10 +1897,10 @@
         <v>31002</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1">
         <v>150</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="H13" s="1" t="b">
         <v>1</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="0" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="U13" s="0">
         <v>30</v>
@@ -1948,10 +1948,10 @@
         <v>31003</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1">
         <v>150</v>
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="H14" s="1" t="b">
         <v>1</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="0" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="U14" s="0">
         <v>30</v>
@@ -1999,10 +1999,10 @@
         <v>31004</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="D15" s="1">
         <v>150</v>
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="H15" s="1" t="b">
         <v>1</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="0" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="U15" s="0">
         <v>30</v>
@@ -2050,10 +2050,10 @@
         <v>31005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="D16" s="1">
         <v>150</v>
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="H16" s="1" t="b">
         <v>1</v>
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="0" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="U16" s="0">
         <v>30</v>
@@ -2101,10 +2101,10 @@
         <v>31006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1">
         <v>150</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="H17" s="1" t="b">
         <v>1</v>
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="0" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="U17" s="0">
         <v>30</v>
@@ -2152,10 +2152,10 @@
         <v>31007</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="D18" s="1">
         <v>150</v>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="H18" s="1" t="b">
         <v>1</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="0" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="U18" s="0">
         <v>30</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1,56 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="600" activeTab="2"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28545" windowHeight="11700" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="train_data" sheetId="1" r:id="rId1"/>
-    <sheet name="range_train_data" sheetId="2" r:id="rId2"/>
-    <sheet name="turret_train_data" sheetId="3" r:id="rId3"/>
+    <sheet name="train_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="range_train_data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="turret_train_data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="6">
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
   </fonts>
   <fills count="2">
@@ -83,10 +80,10 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,107 +499,95 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet1">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
-    <col min="3" max="3" width="24.16796875" style="1" bestFit="1" customWidth="1"/>
+    <col width="24.16796875" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
-        <v>train_name</v>
-        <is>
-          <t xml:space="preserve">train_name</t>
+        <is>
+          <t>train_name</t>
         </is>
       </c>
       <c r="C1" s="0" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
+        <is>
+          <t>description</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
-        <v>max_hp</v>
-        <is>
-          <t xml:space="preserve">max_hp</t>
+        <is>
+          <t>max_hp</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
-        <v>is_main_train</v>
-        <is>
-          <t xml:space="preserve">is_main_train</t>
+        <is>
+          <t>is_main_train</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
-        <v>prefab_id</v>
-        <is>
-          <t xml:space="preserve">prefab_id</t>
+        <is>
+          <t>prefab_id</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
-        <v>icon_id</v>
-        <is>
-          <t xml:space="preserve">icon_id</t>
+        <is>
+          <t>icon_id</t>
         </is>
       </c>
       <c r="H1" s="0" t="inlineStr">
-        <v>train_skill_data_id</v>
-        <is>
-          <t xml:space="preserve">train_skill_data_id</t>
+        <is>
+          <t>train_skill_data_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">20001</t>
+        <is>
+          <t>20001</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">기본 기차</t>
+        <is>
+          <t>기본 기차</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
-        </is>
-      </c>
-      <c r="D2" s="0">
+        <is>
+          <t>가장 기본이 되는 기차이다.</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">MainTrain</t>
+        <is>
+          <t>MainTrain</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet2">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
@@ -612,370 +597,345 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
-        <v>train_name</v>
-        <is>
-          <t xml:space="preserve">train_name</t>
+        <is>
+          <t>train_name</t>
         </is>
       </c>
       <c r="C1" s="0" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
+        <is>
+          <t>description</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
-        <v>max_hp</v>
-        <is>
-          <t xml:space="preserve">max_hp</t>
+        <is>
+          <t>max_hp</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
-        <v>is_main_train</v>
-        <is>
-          <t xml:space="preserve">is_main_train</t>
+        <is>
+          <t>is_main_train</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
-        <v>prefab_id</v>
-        <is>
-          <t xml:space="preserve">prefab_id</t>
+        <is>
+          <t>prefab_id</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
-        <v>icon_id</v>
-        <is>
-          <t xml:space="preserve">icon_id</t>
+        <is>
+          <t>icon_id</t>
         </is>
       </c>
       <c r="H1" s="0" t="inlineStr">
-        <v>train_skill_data_id</v>
-        <is>
-          <t xml:space="preserve">train_skill_data_id</t>
+        <is>
+          <t>train_skill_data_id</t>
         </is>
       </c>
       <c r="I1" s="0" t="inlineStr">
-        <v>attack_range</v>
-        <is>
-          <t xml:space="preserve">attack_range</t>
-        </is>
-      </c>
-      <c r="J1" s="0" t="inlineStr">
-        <v>attack_damage</v>
-        <is>
-          <t xml:space="preserve">attack_damage</t>
+        <is>
+          <t>attack_range</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>attack_area</t>
         </is>
       </c>
       <c r="K1" s="0" t="inlineStr">
-        <v>attack_count</v>
-        <is>
-          <t xml:space="preserve">attack_count</t>
+        <is>
+          <t>attack_damage</t>
         </is>
       </c>
       <c r="L1" s="0" t="inlineStr">
-        <v>attack_interval</v>
-        <is>
-          <t xml:space="preserve">attack_interval</t>
+        <is>
+          <t>attack_count</t>
         </is>
       </c>
       <c r="M1" s="0" t="inlineStr">
-        <v>range_projectile_prefab_id</v>
-        <is>
-          <t xml:space="preserve">range_projectile_prefab_id</t>
+        <is>
+          <t>attack_interval</t>
         </is>
       </c>
       <c r="N1" s="0" t="inlineStr">
-        <v>critical_chance</v>
-        <is>
-          <t xml:space="preserve">critical_chance</t>
+        <is>
+          <t>range_projectile_prefab_id</t>
         </is>
       </c>
       <c r="O1" s="0" t="inlineStr">
-        <v>critical_damage</v>
-        <is>
-          <t xml:space="preserve">critical_damage</t>
+        <is>
+          <t>critical_chance</t>
         </is>
       </c>
       <c r="P1" s="0" t="inlineStr">
-        <v>passive_skill_data_id</v>
-        <is>
-          <t xml:space="preserve">passive_skill_data_id</t>
+        <is>
+          <t>critical_damage</t>
+        </is>
+      </c>
+      <c r="Q1" s="0" t="inlineStr">
+        <is>
+          <t>passive_skill_data_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">40001</t>
+        <is>
+          <t>40001</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">폭발 포탑</t>
+        <is>
+          <t>폭발 포탑</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">적이 가장 많은 곳으로 위치해 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D2" s="0">
+        <is>
+          <t>적이 가장 많은 곳으로 위치해 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ExplosionRangeTrain</t>
+        <is>
+          <t>ExplosionRangeTrain</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-        </is>
-      </c>
-      <c r="I2" s="0">
+        <is>
+          <t>현대무기_대포_헤리콥터리코를_어쎄신</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="0">
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="K2" s="0">
-        <v>1</v>
-      </c>
-      <c r="L2" s="0">
+      <c r="L2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="M2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ExplosionProjectile</t>
-        </is>
-      </c>
-      <c r="N2" s="0">
-        <v>30</v>
-      </c>
-      <c r="O2" s="0">
+      <c r="N2" s="0" t="inlineStr">
+        <is>
+          <t>ExplosionProjectile</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="P2" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">40002</t>
+        <is>
+          <t>40002</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">냉기 포탑</t>
+        <is>
+          <t>냉기 포탑</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D3" s="0">
+        <is>
+          <t>적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E3" s="0">
+      <c r="E3" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ColdAirRangeTrain</t>
+        <is>
+          <t>ColdAirRangeTrain</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">현대무기_대포_288스마</t>
-        </is>
-      </c>
-      <c r="I3" s="0">
+        <is>
+          <t>현대무기_대포_288스마</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="0">
-        <v>1</v>
-      </c>
-      <c r="K3" s="0">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0">
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ColdAirProjectile</t>
-        </is>
-      </c>
-      <c r="N3" s="0">
-        <v>30</v>
-      </c>
-      <c r="O3" s="0">
+      <c r="N3" s="0" t="inlineStr">
+        <is>
+          <t>ColdAirProjectile</t>
+        </is>
+      </c>
+      <c r="O3" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="P3" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">41001</t>
+        <is>
+          <t>41001</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 폭발 포탑</t>
+        <is>
+          <t>엘리트 폭발 포탑</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">폭발 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D4" s="0">
+        <is>
+          <t>폭발 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E4" s="0">
+      <c r="E4" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteExplosionRangeTrain</t>
+        <is>
+          <t>EliteExplosionRangeTrain</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50008</t>
-        </is>
-      </c>
-      <c r="I4" s="0">
+        <is>
+          <t>50008</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="0">
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <v>500</v>
       </c>
-      <c r="K4" s="0">
-        <v>1</v>
-      </c>
-      <c r="L4" s="0">
+      <c r="L4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="M4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ExplosionProjectile</t>
-        </is>
-      </c>
-      <c r="N4" s="0">
-        <v>30</v>
-      </c>
-      <c r="O4" s="0">
+      <c r="N4" s="0" t="inlineStr">
+        <is>
+          <t>ExplosionProjectile</t>
+        </is>
+      </c>
+      <c r="O4" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="P4" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="P4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60008</t>
+      <c r="Q4" s="0" t="inlineStr">
+        <is>
+          <t>60008</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">41002</t>
+        <is>
+          <t>41002</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 냉기 포탑</t>
+        <is>
+          <t>엘리트 냉기 포탑</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">냉기 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D5" s="0">
+        <is>
+          <t>냉기 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E5" s="0">
+      <c r="E5" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteColdAirRangeTrain</t>
+        <is>
+          <t>EliteColdAirRangeTrain</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50009</t>
-        </is>
-      </c>
-      <c r="I5" s="0">
+        <is>
+          <t>50009</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="J5" s="0">
+      <c r="J5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="K5" s="0">
-        <v>1</v>
-      </c>
-      <c r="L5" s="0">
+      <c r="L5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ColdAirProjectile</t>
-        </is>
-      </c>
-      <c r="N5" s="0">
-        <v>30</v>
-      </c>
-      <c r="O5" s="0">
+      <c r="N5" s="0" t="inlineStr">
+        <is>
+          <t>ColdAirProjectile</t>
+        </is>
+      </c>
+      <c r="O5" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="P5" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="P5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60009</t>
+      <c r="Q5" s="0" t="inlineStr">
+        <is>
+          <t>60009</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet3">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
@@ -983,1114 +943,1046 @@
   <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
-    <col min="2" max="2" width="17.4609375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.15625" style="1" bestFit="1" customWidth="1"/>
+    <col width="17.4609375" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="81.25" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="21.1328125" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
+    <col width="18.7265625" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
+    <col width="20.25" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
+    <col width="23.15625" bestFit="1" customWidth="1" style="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
-        <v>train_name</v>
-        <is>
-          <t xml:space="preserve">train_name</t>
+        <is>
+          <t>train_name</t>
         </is>
       </c>
       <c r="C1" s="0" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
+        <is>
+          <t>description</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
-        <v>max_hp</v>
-        <is>
-          <t xml:space="preserve">max_hp</t>
+        <is>
+          <t>max_hp</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
-        <v>is_main_train</v>
-        <is>
-          <t xml:space="preserve">is_main_train</t>
+        <is>
+          <t>is_main_train</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
-        <v>prefab_id</v>
-        <is>
-          <t xml:space="preserve">prefab_id</t>
+        <is>
+          <t>prefab_id</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
-        <v>icon_id</v>
-        <is>
-          <t xml:space="preserve">icon_id</t>
+        <is>
+          <t>icon_id</t>
         </is>
       </c>
       <c r="H1" s="0" t="inlineStr">
-        <v>train_skill_data_id</v>
-        <is>
-          <t xml:space="preserve">train_skill_data_id</t>
+        <is>
+          <t>train_skill_data_id</t>
         </is>
       </c>
       <c r="I1" s="0" t="inlineStr">
-        <v>attack_range</v>
-        <is>
-          <t xml:space="preserve">attack_range</t>
-        </is>
-      </c>
-      <c r="J1" s="0" t="inlineStr">
-        <v>attack_damage</v>
-        <is>
-          <t xml:space="preserve">attack_damage</t>
+        <is>
+          <t>attack_range</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>attack_area</t>
         </is>
       </c>
       <c r="K1" s="0" t="inlineStr">
-        <v>attack_count</v>
-        <is>
-          <t xml:space="preserve">attack_count</t>
+        <is>
+          <t>attack_damage</t>
         </is>
       </c>
       <c r="L1" s="0" t="inlineStr">
-        <v>attack_interval</v>
-        <is>
-          <t xml:space="preserve">attack_interval</t>
+        <is>
+          <t>attack_count</t>
         </is>
       </c>
       <c r="M1" s="0" t="inlineStr">
-        <v>target_count</v>
-        <is>
-          <t xml:space="preserve">target_count</t>
+        <is>
+          <t>attack_interval</t>
         </is>
       </c>
       <c r="N1" s="0" t="inlineStr">
-        <v>turret_projectile_prefab_id</v>
-        <is>
-          <t xml:space="preserve">turret_projectile_prefab_id</t>
+        <is>
+          <t>target_count</t>
         </is>
       </c>
       <c r="O1" s="0" t="inlineStr">
-        <v>critical_chance</v>
-        <is>
-          <t xml:space="preserve">critical_chance</t>
+        <is>
+          <t>turret_projectile_prefab_id</t>
         </is>
       </c>
       <c r="P1" s="0" t="inlineStr">
-        <v>critical_damage</v>
-        <is>
-          <t xml:space="preserve">critical_damage</t>
+        <is>
+          <t>critical_chance</t>
         </is>
       </c>
       <c r="Q1" s="0" t="inlineStr">
-        <v>passive_skill_data_id</v>
-        <is>
-          <t xml:space="preserve">passive_skill_data_id</t>
+        <is>
+          <t>critical_damage</t>
+        </is>
+      </c>
+      <c r="R1" s="0" t="inlineStr">
+        <is>
+          <t>passive_skill_data_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30001</t>
+        <is>
+          <t>30001</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">기관총 포탑</t>
+        <is>
+          <t>기관총 포탑</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">기관총으로 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D2" s="0">
+        <is>
+          <t>기관총으로 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">NormalTurretTrain</t>
+        <is>
+          <t>NormalTurretTrain</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_08_UI</t>
-        </is>
-      </c>
-      <c r="I2" s="0">
+        <is>
+          <t>Weapon_KMD_08_UI</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="J2" s="0">
+      <c r="J2" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="0">
-        <v>1</v>
-      </c>
-      <c r="L2" s="0">
+      <c r="K2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="M2" s="0">
-        <v>1</v>
-      </c>
-      <c r="N2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">NormalProjectile</t>
-        </is>
-      </c>
-      <c r="O2" s="0">
-        <v>30</v>
-      </c>
-      <c r="P2" s="0">
+      <c r="N2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>NormalProjectile</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30002</t>
+        <is>
+          <t>30002</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">화염 포탑</t>
+        <is>
+          <t>화염 포탑</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D3" s="0">
+        <is>
+          <t>화염으로 지속적인 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E3" s="0">
+      <c r="E3" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">FireTurretTrain</t>
+        <is>
+          <t>FireTurretTrain</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_05_UI</t>
-        </is>
-      </c>
-      <c r="I3" s="0">
+        <is>
+          <t>Weapon_MEL_05_UI</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="J3" s="0">
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K3" s="0">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0">
+      <c r="L3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="0" t="n">
         <v>0.15</v>
       </c>
-      <c r="M3" s="0">
-        <v>1</v>
-      </c>
-      <c r="N3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">FireEffectProjectile</t>
-        </is>
-      </c>
-      <c r="O3" s="0">
-        <v>30</v>
-      </c>
-      <c r="P3" s="0">
+      <c r="N3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="0" t="inlineStr">
+        <is>
+          <t>FireEffectProjectile</t>
+        </is>
+      </c>
+      <c r="P3" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30003</t>
+        <is>
+          <t>30003</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">미사일 포탑</t>
+        <is>
+          <t>미사일 포탑</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
-        </is>
-      </c>
-      <c r="D4" s="0">
+        <is>
+          <t>미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E4" s="0">
+      <c r="E4" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">MissileTurretTrain</t>
+        <is>
+          <t>MissileTurretTrain</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_10_UI</t>
-        </is>
-      </c>
-      <c r="I4" s="0">
+        <is>
+          <t>Weapon_KMD_10_UI</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="J4" s="0">
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="K4" s="0">
-        <v>1</v>
-      </c>
-      <c r="L4" s="0">
+      <c r="L4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="0" t="n">
         <v>1.25</v>
       </c>
-      <c r="M4" s="0">
-        <v>1</v>
-      </c>
-      <c r="N4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">MissileProjectile</t>
-        </is>
-      </c>
-      <c r="O4" s="0">
-        <v>30</v>
-      </c>
-      <c r="P4" s="0">
+      <c r="N4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="0" t="inlineStr">
+        <is>
+          <t>MissileProjectile</t>
+        </is>
+      </c>
+      <c r="P4" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30004</t>
+        <is>
+          <t>30004</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">레이저 포탑</t>
+        <is>
+          <t>레이저 포탑</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D5" s="0">
+        <is>
+          <t>레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E5" s="0">
+      <c r="E5" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">LaserTurretTrain</t>
+        <is>
+          <t>LaserTurretTrain</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_288_19_UI</t>
-        </is>
-      </c>
-      <c r="I5" s="0">
-        <v>30</v>
-      </c>
-      <c r="J5" s="0">
+        <is>
+          <t>Weapon_288_19_UI</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="K5" s="0">
-        <v>1</v>
-      </c>
-      <c r="L5" s="0">
+      <c r="L5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="M5" s="0">
-        <v>1</v>
-      </c>
-      <c r="N5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">LaserProjectile</t>
-        </is>
-      </c>
-      <c r="O5" s="0">
-        <v>30</v>
-      </c>
-      <c r="P5" s="0">
+      <c r="N5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="0" t="inlineStr">
+        <is>
+          <t>LaserProjectile</t>
+        </is>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30005</t>
+        <is>
+          <t>30005</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">전기 포탑</t>
+        <is>
+          <t>전기 포탑</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">화면에 있는 다수의 적들을 통시에 공격한다.</t>
-        </is>
-      </c>
-      <c r="D6" s="0">
+        <is>
+          <t>화면에 있는 다수의 적들을 통시에 공격한다.</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E6" s="0">
+      <c r="E6" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ElectrickTurretTrain</t>
+        <is>
+          <t>ElectrickTurretTrain</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_16_UI</t>
-        </is>
-      </c>
-      <c r="I6" s="0">
+        <is>
+          <t>Weapon_MEL_16_UI</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="J6" s="0">
+      <c r="J6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="K6" s="0">
+      <c r="L6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="L6" s="0">
-        <v>1</v>
-      </c>
-      <c r="M6" s="0">
+      <c r="M6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="N6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ElectrickProjectile</t>
-        </is>
-      </c>
-      <c r="O6" s="0">
-        <v>30</v>
-      </c>
-      <c r="P6" s="0">
+      <c r="O6" s="0" t="inlineStr">
+        <is>
+          <t>ElectrickProjectile</t>
+        </is>
+      </c>
+      <c r="P6" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30006</t>
+        <is>
+          <t>30006</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">포격 포탑</t>
+        <is>
+          <t>포격 포탑</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D7" s="0">
+        <is>
+          <t>거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E7" s="0">
+      <c r="E7" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">CannonTurretTrain</t>
+        <is>
+          <t>CannonTurretTrain</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_14_UI</t>
-        </is>
-      </c>
-      <c r="I7" s="0">
+        <is>
+          <t>Weapon_MEL_14_UI</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="0">
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="K7" s="0">
-        <v>1</v>
-      </c>
-      <c r="L7" s="0">
+      <c r="L7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="0">
-        <v>1</v>
-      </c>
-      <c r="N7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">CannonProjectile</t>
-        </is>
-      </c>
-      <c r="O7" s="0">
-        <v>30</v>
-      </c>
-      <c r="P7" s="0">
+      <c r="N7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="0" t="inlineStr">
+        <is>
+          <t>CannonProjectile</t>
+        </is>
+      </c>
+      <c r="P7" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q7" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30007</t>
+        <is>
+          <t>30007</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">저격 포탑</t>
+        <is>
+          <t>저격 포탑</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
-        </is>
-      </c>
-      <c r="D8" s="0">
+        <is>
+          <t>저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E8" s="0">
+      <c r="E8" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">SniperTurretTrain</t>
+        <is>
+          <t>SniperTurretTrain</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_12_UI</t>
-        </is>
-      </c>
-      <c r="I8" s="0">
-        <v>30</v>
-      </c>
-      <c r="J8" s="0">
+        <is>
+          <t>Weapon_KMD_12_UI</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="K8" s="0">
-        <v>1</v>
-      </c>
-      <c r="L8" s="0">
-        <v>1</v>
-      </c>
-      <c r="M8" s="0">
-        <v>1</v>
-      </c>
-      <c r="N8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">SniperProjectile</t>
-        </is>
-      </c>
-      <c r="O8" s="0">
-        <v>30</v>
-      </c>
-      <c r="P8" s="0">
+      <c r="L8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="0" t="inlineStr">
+        <is>
+          <t>SniperProjectile</t>
+        </is>
+      </c>
+      <c r="P8" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31001</t>
+        <is>
+          <t>31001</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 기관총 포탑</t>
+        <is>
+          <t>엘리트 기관총 포탑</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">기관총 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D9" s="0">
+        <is>
+          <t>기관총 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E9" s="0">
+      <c r="E9" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteNormalTurretTrain</t>
+        <is>
+          <t>EliteNormalTurretTrain</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_08_UI</t>
+        <is>
+          <t>Weapon_KMD_08_UI</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50001</t>
-        </is>
-      </c>
-      <c r="I9" s="0">
+        <is>
+          <t>50001</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="J9" s="0">
+      <c r="J9" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="K9" s="0">
-        <v>1</v>
-      </c>
-      <c r="L9" s="0">
+      <c r="L9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M9" s="0">
-        <v>0</v>
-      </c>
-      <c r="N9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">NormalProjectile</t>
-        </is>
-      </c>
-      <c r="O9" s="0">
-        <v>30</v>
-      </c>
-      <c r="P9" s="0">
+      <c r="N9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="0" t="inlineStr">
+        <is>
+          <t>NormalProjectile</t>
+        </is>
+      </c>
+      <c r="P9" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q9" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60001</t>
+      <c r="R9" s="0" t="inlineStr">
+        <is>
+          <t>60001</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31002</t>
+        <is>
+          <t>31002</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 화염 포탑</t>
+        <is>
+          <t>엘리트 화염 포탑</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">화염 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D10" s="0">
+        <is>
+          <t>화염 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E10" s="0">
+      <c r="E10" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteFireTurretTrain</t>
+        <is>
+          <t>EliteFireTurretTrain</t>
         </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_05_UI</t>
+        <is>
+          <t>Weapon_MEL_05_UI</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50002</t>
-        </is>
-      </c>
-      <c r="I10" s="0">
+        <is>
+          <t>50002</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="J10" s="0">
+      <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="K10" s="0">
-        <v>1</v>
-      </c>
-      <c r="L10" s="0">
+      <c r="L10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="M10" s="0">
-        <v>0</v>
-      </c>
-      <c r="N10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">FireEffectProjectile</t>
-        </is>
-      </c>
-      <c r="O10" s="0">
-        <v>30</v>
-      </c>
-      <c r="P10" s="0">
+      <c r="N10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="0" t="inlineStr">
+        <is>
+          <t>FireEffectProjectile</t>
+        </is>
+      </c>
+      <c r="P10" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60002</t>
+      <c r="R10" s="0" t="inlineStr">
+        <is>
+          <t>60002</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31003</t>
+        <is>
+          <t>31003</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 미사일 포탑</t>
+        <is>
+          <t>엘리트 미사일 포탑</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">미사일 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D11" s="0">
+        <is>
+          <t>미사일 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E11" s="0">
+      <c r="E11" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteMissileTurretTrain</t>
+        <is>
+          <t>EliteMissileTurretTrain</t>
         </is>
       </c>
       <c r="G11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_10_UI</t>
+        <is>
+          <t>Weapon_KMD_10_UI</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50003</t>
-        </is>
-      </c>
-      <c r="I11" s="0">
+        <is>
+          <t>50003</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="J11" s="0">
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="K11" s="0">
-        <v>1</v>
-      </c>
-      <c r="L11" s="0">
+      <c r="L11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="M11" s="0">
-        <v>0</v>
-      </c>
-      <c r="N11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">MissileProjectile</t>
-        </is>
-      </c>
-      <c r="O11" s="0">
-        <v>30</v>
-      </c>
-      <c r="P11" s="0">
+      <c r="N11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="0" t="inlineStr">
+        <is>
+          <t>MissileProjectile</t>
+        </is>
+      </c>
+      <c r="P11" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q11" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60003</t>
+      <c r="R11" s="0" t="inlineStr">
+        <is>
+          <t>60003</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31004</t>
+        <is>
+          <t>31004</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 레이저 포탑</t>
+        <is>
+          <t>엘리트 레이저 포탑</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">레이저 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D12" s="0">
+        <is>
+          <t>레이저 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E12" s="0">
+      <c r="E12" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteLaserTurretTrain</t>
+        <is>
+          <t>EliteLaserTurretTrain</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_288_19_UI</t>
+        <is>
+          <t>Weapon_288_19_UI</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50004</t>
-        </is>
-      </c>
-      <c r="I12" s="0">
+        <is>
+          <t>50004</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="J12" s="0">
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="K12" s="0">
-        <v>1</v>
-      </c>
-      <c r="L12" s="0">
+      <c r="L12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="M12" s="0">
-        <v>0</v>
-      </c>
-      <c r="N12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">LaserProjectile</t>
-        </is>
-      </c>
-      <c r="O12" s="0">
-        <v>30</v>
-      </c>
-      <c r="P12" s="0">
+      <c r="N12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="0" t="inlineStr">
+        <is>
+          <t>LaserProjectile</t>
+        </is>
+      </c>
+      <c r="P12" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q12" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60004</t>
+      <c r="R12" s="0" t="inlineStr">
+        <is>
+          <t>60004</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31005</t>
+        <is>
+          <t>31005</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 전기 포탑</t>
+        <is>
+          <t>엘리트 전기 포탑</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">전기 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D13" s="0">
+        <is>
+          <t>전기 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E13" s="0">
+      <c r="E13" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteElectrickTurretTrain</t>
+        <is>
+          <t>EliteElectrickTurretTrain</t>
         </is>
       </c>
       <c r="G13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_16_UI</t>
+        <is>
+          <t>Weapon_MEL_16_UI</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50005</t>
-        </is>
-      </c>
-      <c r="I13" s="0">
+        <is>
+          <t>50005</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="J13" s="0">
+      <c r="J13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="K13" s="0">
-        <v>1</v>
-      </c>
-      <c r="L13" s="0">
+      <c r="L13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="M13" s="0">
-        <v>0</v>
-      </c>
-      <c r="N13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ElectrickProjectile</t>
-        </is>
-      </c>
-      <c r="O13" s="0">
-        <v>30</v>
-      </c>
-      <c r="P13" s="0">
+      <c r="N13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="0" t="inlineStr">
+        <is>
+          <t>ElectrickProjectile</t>
+        </is>
+      </c>
+      <c r="P13" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q13" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60005</t>
+      <c r="R13" s="0" t="inlineStr">
+        <is>
+          <t>60005</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31006</t>
+        <is>
+          <t>31006</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 포격 포탑</t>
+        <is>
+          <t>엘리트 포격 포탑</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">포격 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D14" s="0">
+        <is>
+          <t>포격 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E14" s="0">
+      <c r="E14" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteCannonTurretTrain</t>
+        <is>
+          <t>EliteCannonTurretTrain</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_14_UI</t>
+        <is>
+          <t>Weapon_MEL_14_UI</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50006</t>
-        </is>
-      </c>
-      <c r="I14" s="0">
+        <is>
+          <t>50006</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="J14" s="0">
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="K14" s="0">
-        <v>1</v>
-      </c>
-      <c r="L14" s="0">
+      <c r="L14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="M14" s="0">
-        <v>0</v>
-      </c>
-      <c r="N14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">CannonProjectile</t>
-        </is>
-      </c>
-      <c r="O14" s="0">
-        <v>30</v>
-      </c>
-      <c r="P14" s="0">
+      <c r="N14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="0" t="inlineStr">
+        <is>
+          <t>CannonProjectile</t>
+        </is>
+      </c>
+      <c r="P14" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q14" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60006</t>
+      <c r="R14" s="0" t="inlineStr">
+        <is>
+          <t>60006</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31007</t>
+        <is>
+          <t>31007</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 저격 포탑</t>
+        <is>
+          <t>엘리트 저격 포탑</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">저격 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D15" s="0">
+        <is>
+          <t>저격 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E15" s="0">
+      <c r="E15" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteSniperTurretTrain</t>
+        <is>
+          <t>EliteSniperTurretTrain</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_12_UI</t>
+        <is>
+          <t>Weapon_KMD_12_UI</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50007</t>
-        </is>
-      </c>
-      <c r="I15" s="0">
+        <is>
+          <t>50007</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="0">
+      <c r="J15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <v>600</v>
       </c>
-      <c r="K15" s="0">
-        <v>1</v>
-      </c>
-      <c r="L15" s="0">
+      <c r="L15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="M15" s="0">
-        <v>0</v>
-      </c>
-      <c r="N15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">SniperProjectile</t>
-        </is>
-      </c>
-      <c r="O15" s="0">
-        <v>30</v>
-      </c>
-      <c r="P15" s="0">
+      <c r="N15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="0" t="inlineStr">
+        <is>
+          <t>SniperProjectile</t>
+        </is>
+      </c>
+      <c r="P15" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q15" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60007</t>
+      <c r="R15" s="0" t="inlineStr">
+        <is>
+          <t>60007</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1,53 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28545" windowHeight="11700" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="600" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="train_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="range_train_data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="turret_train_data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="train_data" sheetId="1" r:id="rId1"/>
+    <sheet name="range_train_data" sheetId="2" r:id="rId2"/>
+    <sheet name="turret_train_data" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
   <fonts count="6">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -80,10 +83,10 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,1490 +502,1661 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
-    <col width="24.16796875" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col min="3" max="3" width="24.16796875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
+        <v>id</v>
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>train_name</t>
+        <v>train_name</v>
+        <is>
+          <t xml:space="preserve">train_name</t>
         </is>
       </c>
       <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>description</t>
+        <v>description</v>
+        <is>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>max_hp</t>
+        <v>max_hp</v>
+        <is>
+          <t xml:space="preserve">max_hp</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
-        <is>
-          <t>is_main_train</t>
+        <v>is_main_train</v>
+        <is>
+          <t xml:space="preserve">is_main_train</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
-        <is>
-          <t>prefab_id</t>
+        <v>prefab_id</v>
+        <is>
+          <t xml:space="preserve">prefab_id</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t>icon_id</t>
+        <v>icon_id</v>
+        <is>
+          <t xml:space="preserve">icon_id</t>
         </is>
       </c>
       <c r="H1" s="0" t="inlineStr">
-        <is>
-          <t>train_skill_data_id</t>
+        <v>train_skill_data_id</v>
+        <is>
+          <t xml:space="preserve">train_skill_data_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>20001</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">20001</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>기본 기차</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">기본 기차</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>가장 기본이 되는 기차이다.</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
+        </is>
+      </c>
+      <c r="D2" s="0">
         <v>250</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="0">
         <v>1</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>MainTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">MainTrain</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
+        <v>id</v>
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>train_name</t>
+        <v>train_name</v>
+        <is>
+          <t xml:space="preserve">train_name</t>
         </is>
       </c>
       <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>description</t>
+        <v>description</v>
+        <is>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>max_hp</t>
+        <v>max_hp</v>
+        <is>
+          <t xml:space="preserve">max_hp</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
-        <is>
-          <t>is_main_train</t>
+        <v>is_main_train</v>
+        <is>
+          <t xml:space="preserve">is_main_train</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
-        <is>
-          <t>prefab_id</t>
+        <v>prefab_id</v>
+        <is>
+          <t xml:space="preserve">prefab_id</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t>icon_id</t>
+        <v>icon_id</v>
+        <is>
+          <t xml:space="preserve">icon_id</t>
         </is>
       </c>
       <c r="H1" s="0" t="inlineStr">
-        <is>
-          <t>train_skill_data_id</t>
+        <v>train_skill_data_id</v>
+        <is>
+          <t xml:space="preserve">train_skill_data_id</t>
         </is>
       </c>
       <c r="I1" s="0" t="inlineStr">
-        <is>
-          <t>attack_range</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>attack_area</t>
+        <v>attack_range</v>
+        <is>
+          <t xml:space="preserve">attack_range</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <v>attack_area</v>
+        <is>
+          <t xml:space="preserve">attack_area</t>
         </is>
       </c>
       <c r="K1" s="0" t="inlineStr">
-        <is>
-          <t>attack_damage</t>
+        <v>attack_damage</v>
+        <is>
+          <t xml:space="preserve">attack_damage</t>
         </is>
       </c>
       <c r="L1" s="0" t="inlineStr">
-        <is>
-          <t>attack_count</t>
+        <v>attack_count</v>
+        <is>
+          <t xml:space="preserve">attack_count</t>
         </is>
       </c>
       <c r="M1" s="0" t="inlineStr">
-        <is>
-          <t>attack_interval</t>
+        <v>attack_interval</v>
+        <is>
+          <t xml:space="preserve">attack_interval</t>
         </is>
       </c>
       <c r="N1" s="0" t="inlineStr">
-        <is>
-          <t>range_projectile_prefab_id</t>
+        <v>range_projectile_prefab_id</v>
+        <is>
+          <t xml:space="preserve">range_projectile_prefab_id</t>
         </is>
       </c>
       <c r="O1" s="0" t="inlineStr">
-        <is>
-          <t>critical_chance</t>
+        <v>critical_chance</v>
+        <is>
+          <t xml:space="preserve">critical_chance</t>
         </is>
       </c>
       <c r="P1" s="0" t="inlineStr">
-        <is>
-          <t>critical_damage</t>
+        <v>critical_damage</v>
+        <is>
+          <t xml:space="preserve">critical_damage</t>
         </is>
       </c>
       <c r="Q1" s="0" t="inlineStr">
-        <is>
-          <t>passive_skill_data_id</t>
+        <v>passive_skill_data_id</v>
+        <is>
+          <t xml:space="preserve">passive_skill_data_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>40001</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">40001</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>폭발 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">폭발 포탑</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>적이 가장 많은 곳으로 위치해 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">적이 가장 많은 곳으로 위치해 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D2" s="0">
         <v>250</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="0">
         <v>0</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>ExplosionRangeTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">ExplosionRangeTrain</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>현대무기_대포_헤리콥터리코를_어쎄신</t>
-        </is>
-      </c>
-      <c r="I2" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+        </is>
+      </c>
+      <c r="I2" s="0">
         <v>5</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="0">
         <v>5</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="0">
         <v>50</v>
       </c>
-      <c r="L2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="0" t="n">
+      <c r="L2" s="0">
+        <v>1</v>
+      </c>
+      <c r="M2" s="0">
         <v>4</v>
       </c>
       <c r="N2" s="0" t="inlineStr">
-        <is>
-          <t>ExplosionProjectile</t>
-        </is>
-      </c>
-      <c r="O2" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">ExplosionProjectile</t>
+        </is>
+      </c>
+      <c r="O2" s="0">
         <v>30</v>
       </c>
-      <c r="P2" s="0" t="n">
+      <c r="P2" s="0">
         <v>0.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>40002</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">40002</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>냉기 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">냉기 포탑</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D3" s="0">
         <v>250</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="0">
         <v>0</v>
       </c>
       <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t>ColdAirRangeTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">ColdAirRangeTrain</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t>현대무기_대포_288스마</t>
-        </is>
-      </c>
-      <c r="I3" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">현대무기_대포_288스마</t>
+        </is>
+      </c>
+      <c r="I3" s="0">
         <v>5</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="0">
         <v>5</v>
       </c>
-      <c r="K3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="0" t="n">
+      <c r="K3" s="0">
+        <v>1</v>
+      </c>
+      <c r="L3" s="0">
+        <v>1</v>
+      </c>
+      <c r="M3" s="0">
         <v>0.1</v>
       </c>
       <c r="N3" s="0" t="inlineStr">
-        <is>
-          <t>ColdAirProjectile</t>
-        </is>
-      </c>
-      <c r="O3" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">ColdAirProjectile</t>
+        </is>
+      </c>
+      <c r="O3" s="0">
         <v>30</v>
       </c>
-      <c r="P3" s="0" t="n">
+      <c r="P3" s="0">
         <v>0.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>41001</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">41001</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>엘리트 폭발 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">엘리트 폭발 포탑</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>폭발 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">폭발 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D4" s="0">
         <v>150</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="0">
         <v>0</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t>EliteExplosionRangeTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">EliteExplosionRangeTrain</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t>50008</t>
-        </is>
-      </c>
-      <c r="I4" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">50008</t>
+        </is>
+      </c>
+      <c r="I4" s="0">
         <v>8</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="0">
         <v>8</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="0">
         <v>500</v>
       </c>
-      <c r="L4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="0" t="n">
+      <c r="L4" s="0">
+        <v>1</v>
+      </c>
+      <c r="M4" s="0">
         <v>4</v>
       </c>
       <c r="N4" s="0" t="inlineStr">
-        <is>
-          <t>ExplosionProjectile</t>
-        </is>
-      </c>
-      <c r="O4" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">ExplosionProjectile</t>
+        </is>
+      </c>
+      <c r="O4" s="0">
         <v>30</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="P4" s="0">
         <v>0.3</v>
       </c>
       <c r="Q4" s="0" t="inlineStr">
-        <is>
-          <t>60008</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">60008</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>41002</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">41002</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>엘리트 냉기 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">엘리트 냉기 포탑</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>냉기 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">냉기 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D5" s="0">
         <v>150</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="0">
         <v>0</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t>EliteColdAirRangeTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">EliteColdAirRangeTrain</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
-        <is>
-          <t>50009</t>
-        </is>
-      </c>
-      <c r="I5" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">50009</t>
+        </is>
+      </c>
+      <c r="I5" s="0">
         <v>13</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="0">
         <v>13</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="0">
         <v>15</v>
       </c>
-      <c r="L5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="0" t="n">
+      <c r="L5" s="0">
+        <v>1</v>
+      </c>
+      <c r="M5" s="0">
         <v>0.1</v>
       </c>
       <c r="N5" s="0" t="inlineStr">
-        <is>
-          <t>ColdAirProjectile</t>
-        </is>
-      </c>
-      <c r="O5" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">ColdAirProjectile</t>
+        </is>
+      </c>
+      <c r="O5" s="0">
         <v>30</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5" s="0">
         <v>0.3</v>
       </c>
       <c r="Q5" s="0" t="inlineStr">
-        <is>
-          <t>60009</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">60009</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
-    <col width="17.4609375" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="81.25" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
-    <col width="21.1328125" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
-    <col width="18.7265625" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
-    <col width="20.25" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
-    <col width="23.15625" bestFit="1" customWidth="1" style="1" min="14" max="14"/>
+    <col min="2" max="2" width="17.4609375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.15625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
+        <v>id</v>
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>train_name</t>
+        <v>train_name</v>
+        <is>
+          <t xml:space="preserve">train_name</t>
         </is>
       </c>
       <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>description</t>
+        <v>description</v>
+        <is>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>max_hp</t>
+        <v>max_hp</v>
+        <is>
+          <t xml:space="preserve">max_hp</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
-        <is>
-          <t>is_main_train</t>
+        <v>is_main_train</v>
+        <is>
+          <t xml:space="preserve">is_main_train</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
-        <is>
-          <t>prefab_id</t>
+        <v>prefab_id</v>
+        <is>
+          <t xml:space="preserve">prefab_id</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t>icon_id</t>
+        <v>icon_id</v>
+        <is>
+          <t xml:space="preserve">icon_id</t>
         </is>
       </c>
       <c r="H1" s="0" t="inlineStr">
-        <is>
-          <t>train_skill_data_id</t>
+        <v>train_skill_data_id</v>
+        <is>
+          <t xml:space="preserve">train_skill_data_id</t>
         </is>
       </c>
       <c r="I1" s="0" t="inlineStr">
-        <is>
-          <t>attack_range</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>attack_area</t>
+        <v>attack_range</v>
+        <is>
+          <t xml:space="preserve">attack_range</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <v>attack_area</v>
+        <is>
+          <t xml:space="preserve">attack_area</t>
         </is>
       </c>
       <c r="K1" s="0" t="inlineStr">
-        <is>
-          <t>attack_damage</t>
+        <v>attack_damage</v>
+        <is>
+          <t xml:space="preserve">attack_damage</t>
         </is>
       </c>
       <c r="L1" s="0" t="inlineStr">
-        <is>
-          <t>attack_count</t>
+        <v>attack_count</v>
+        <is>
+          <t xml:space="preserve">attack_count</t>
         </is>
       </c>
       <c r="M1" s="0" t="inlineStr">
-        <is>
-          <t>attack_interval</t>
+        <v>attack_interval</v>
+        <is>
+          <t xml:space="preserve">attack_interval</t>
         </is>
       </c>
       <c r="N1" s="0" t="inlineStr">
-        <is>
-          <t>target_count</t>
+        <v>target_count</v>
+        <is>
+          <t xml:space="preserve">target_count</t>
         </is>
       </c>
       <c r="O1" s="0" t="inlineStr">
-        <is>
-          <t>turret_projectile_prefab_id</t>
+        <v>turret_projectile_prefab_id</v>
+        <is>
+          <t xml:space="preserve">turret_projectile_prefab_id</t>
         </is>
       </c>
       <c r="P1" s="0" t="inlineStr">
-        <is>
-          <t>critical_chance</t>
+        <v>critical_chance</v>
+        <is>
+          <t xml:space="preserve">critical_chance</t>
         </is>
       </c>
       <c r="Q1" s="0" t="inlineStr">
-        <is>
-          <t>critical_damage</t>
+        <v>critical_damage</v>
+        <is>
+          <t xml:space="preserve">critical_damage</t>
         </is>
       </c>
       <c r="R1" s="0" t="inlineStr">
-        <is>
-          <t>passive_skill_data_id</t>
+        <v>passive_skill_data_id</v>
+        <is>
+          <t xml:space="preserve">passive_skill_data_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>30001</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">30001</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>기관총 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">기관총 포탑</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>기관총으로 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">기관총으로 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D2" s="0">
         <v>250</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="0">
         <v>0</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>NormalTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">NormalTurretTrain</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_KMD_08_UI</t>
-        </is>
-      </c>
-      <c r="I2" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_08_UI</t>
+        </is>
+      </c>
+      <c r="I2" s="0">
         <v>10</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="0">
         <v>10</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="0">
         <v>10</v>
       </c>
-      <c r="L2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="0" t="n">
+      <c r="L2" s="0">
+        <v>1</v>
+      </c>
+      <c r="M2" s="0">
         <v>0.3</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="0">
         <v>1</v>
       </c>
       <c r="O2" s="0" t="inlineStr">
-        <is>
-          <t>NormalProjectile</t>
-        </is>
-      </c>
-      <c r="P2" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">NormalProjectile</t>
+        </is>
+      </c>
+      <c r="P2" s="0">
         <v>30</v>
       </c>
-      <c r="Q2" s="0" t="n">
+      <c r="Q2" s="0">
         <v>0.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>30002</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">30002</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>화염 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">화염 포탑</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>화염으로 지속적인 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D3" s="0">
         <v>250</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="0">
         <v>0</v>
       </c>
       <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t>FireTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">FireTurretTrain</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_MEL_05_UI</t>
-        </is>
-      </c>
-      <c r="I3" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_05_UI</t>
+        </is>
+      </c>
+      <c r="I3" s="0">
         <v>8</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="0">
         <v>8</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="0">
         <v>4</v>
       </c>
-      <c r="L3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="0" t="n">
+      <c r="L3" s="0">
+        <v>1</v>
+      </c>
+      <c r="M3" s="0">
         <v>0.15</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="0">
         <v>1</v>
       </c>
       <c r="O3" s="0" t="inlineStr">
-        <is>
-          <t>FireEffectProjectile</t>
-        </is>
-      </c>
-      <c r="P3" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">FireEffectProjectile</t>
+        </is>
+      </c>
+      <c r="P3" s="0">
         <v>30</v>
       </c>
-      <c r="Q3" s="0" t="n">
+      <c r="Q3" s="0">
         <v>0.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>30003</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">30003</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>미사일 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">미사일 포탑</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
+        </is>
+      </c>
+      <c r="D4" s="0">
         <v>250</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="0">
         <v>0</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t>MissileTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">MissileTurretTrain</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_KMD_10_UI</t>
-        </is>
-      </c>
-      <c r="I4" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_10_UI</t>
+        </is>
+      </c>
+      <c r="I4" s="0">
         <v>10</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="0">
         <v>10</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="0">
         <v>25</v>
       </c>
-      <c r="L4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="0" t="n">
+      <c r="L4" s="0">
+        <v>1</v>
+      </c>
+      <c r="M4" s="0">
         <v>1.25</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="0">
         <v>1</v>
       </c>
       <c r="O4" s="0" t="inlineStr">
-        <is>
-          <t>MissileProjectile</t>
-        </is>
-      </c>
-      <c r="P4" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">MissileProjectile</t>
+        </is>
+      </c>
+      <c r="P4" s="0">
         <v>30</v>
       </c>
-      <c r="Q4" s="0" t="n">
+      <c r="Q4" s="0">
         <v>0.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>30004</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">30004</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>레이저 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">레이저 포탑</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D5" s="0">
         <v>250</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="0">
         <v>0</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t>LaserTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">LaserTurretTrain</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_288_19_UI</t>
-        </is>
-      </c>
-      <c r="I5" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_288_19_UI</t>
+        </is>
+      </c>
+      <c r="I5" s="0">
         <v>30</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="0">
         <v>30</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="0">
         <v>50</v>
       </c>
-      <c r="L5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="0" t="n">
+      <c r="L5" s="0">
+        <v>1</v>
+      </c>
+      <c r="M5" s="0">
         <v>2.5</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="0">
         <v>1</v>
       </c>
       <c r="O5" s="0" t="inlineStr">
-        <is>
-          <t>LaserProjectile</t>
-        </is>
-      </c>
-      <c r="P5" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">LaserProjectile</t>
+        </is>
+      </c>
+      <c r="P5" s="0">
         <v>30</v>
       </c>
-      <c r="Q5" s="0" t="n">
+      <c r="Q5" s="0">
         <v>0.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>30005</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">30005</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>전기 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">전기 포탑</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>화면에 있는 다수의 적들을 통시에 공격한다.</t>
-        </is>
-      </c>
-      <c r="D6" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">화면에 있는 다수의 적들을 통시에 공격한다.</t>
+        </is>
+      </c>
+      <c r="D6" s="0">
         <v>250</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="0">
         <v>0</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
-        <is>
-          <t>ElectrickTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">ElectrickTurretTrain</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_MEL_16_UI</t>
-        </is>
-      </c>
-      <c r="I6" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_16_UI</t>
+        </is>
+      </c>
+      <c r="I6" s="0">
         <v>20</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="0">
         <v>20</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="0">
         <v>10</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="0">
         <v>3</v>
       </c>
-      <c r="M6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="0" t="n">
+      <c r="M6" s="0">
+        <v>1</v>
+      </c>
+      <c r="N6" s="0">
         <v>3</v>
       </c>
       <c r="O6" s="0" t="inlineStr">
-        <is>
-          <t>ElectrickProjectile</t>
-        </is>
-      </c>
-      <c r="P6" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">ElectrickProjectile</t>
+        </is>
+      </c>
+      <c r="P6" s="0">
         <v>30</v>
       </c>
-      <c r="Q6" s="0" t="n">
+      <c r="Q6" s="0">
         <v>0.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>30006</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">30006</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>포격 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">포격 포탑</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D7" s="0">
         <v>250</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="0">
         <v>0</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t>CannonTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">CannonTurretTrain</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_MEL_14_UI</t>
-        </is>
-      </c>
-      <c r="I7" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_14_UI</t>
+        </is>
+      </c>
+      <c r="I7" s="0">
         <v>3</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="0">
         <v>3</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="0">
         <v>50</v>
       </c>
-      <c r="L7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="0" t="n">
+      <c r="L7" s="0">
+        <v>1</v>
+      </c>
+      <c r="M7" s="0">
         <v>3</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="0">
         <v>1</v>
       </c>
       <c r="O7" s="0" t="inlineStr">
-        <is>
-          <t>CannonProjectile</t>
-        </is>
-      </c>
-      <c r="P7" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">CannonProjectile</t>
+        </is>
+      </c>
+      <c r="P7" s="0">
         <v>30</v>
       </c>
-      <c r="Q7" s="0" t="n">
+      <c r="Q7" s="0">
         <v>0.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>30007</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">30007</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>저격 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">저격 포탑</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
+        </is>
+      </c>
+      <c r="D8" s="0">
         <v>250</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="0">
         <v>0</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t>SniperTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">SniperTurretTrain</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_KMD_12_UI</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_12_UI</t>
+        </is>
+      </c>
+      <c r="I8" s="0">
         <v>30</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="0">
         <v>30</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="0">
         <v>50</v>
       </c>
-      <c r="L8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="0" t="n">
+      <c r="L8" s="0">
+        <v>1</v>
+      </c>
+      <c r="M8" s="0">
+        <v>1</v>
+      </c>
+      <c r="N8" s="0">
         <v>1</v>
       </c>
       <c r="O8" s="0" t="inlineStr">
-        <is>
-          <t>SniperProjectile</t>
-        </is>
-      </c>
-      <c r="P8" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">SniperProjectile</t>
+        </is>
+      </c>
+      <c r="P8" s="0">
         <v>30</v>
       </c>
-      <c r="Q8" s="0" t="n">
+      <c r="Q8" s="0">
         <v>0.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>31001</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">31001</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>엘리트 기관총 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">엘리트 기관총 포탑</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>기관총 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D9" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">기관총 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D9" s="0">
         <v>150</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="0">
         <v>0</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
-        <is>
-          <t>EliteNormalTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">EliteNormalTurretTrain</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_KMD_08_UI</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_08_UI</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t>50001</t>
-        </is>
-      </c>
-      <c r="I9" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">50001</t>
+        </is>
+      </c>
+      <c r="I9" s="0">
         <v>10</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="0">
         <v>10</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="K9" s="0">
         <v>50</v>
       </c>
-      <c r="L9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="0" t="n">
+      <c r="L9" s="0">
+        <v>1</v>
+      </c>
+      <c r="M9" s="0">
         <v>0.1</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="0">
         <v>0</v>
       </c>
       <c r="O9" s="0" t="inlineStr">
-        <is>
-          <t>NormalProjectile</t>
-        </is>
-      </c>
-      <c r="P9" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">NormalProjectile</t>
+        </is>
+      </c>
+      <c r="P9" s="0">
         <v>30</v>
       </c>
-      <c r="Q9" s="0" t="n">
+      <c r="Q9" s="0">
         <v>0.3</v>
       </c>
       <c r="R9" s="0" t="inlineStr">
-        <is>
-          <t>60001</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">60001</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>31002</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">31002</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>엘리트 화염 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">엘리트 화염 포탑</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>화염 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D10" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">화염 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D10" s="0">
         <v>150</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="0">
         <v>0</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t>EliteFireTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">EliteFireTurretTrain</t>
         </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_MEL_05_UI</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_05_UI</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>50002</t>
-        </is>
-      </c>
-      <c r="I10" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">50002</t>
+        </is>
+      </c>
+      <c r="I10" s="0">
         <v>10</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="0">
         <v>10</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10" s="0">
         <v>25</v>
       </c>
-      <c r="L10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="0" t="n">
+      <c r="L10" s="0">
+        <v>1</v>
+      </c>
+      <c r="M10" s="0">
         <v>0.1</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="0">
         <v>0</v>
       </c>
       <c r="O10" s="0" t="inlineStr">
-        <is>
-          <t>FireEffectProjectile</t>
-        </is>
-      </c>
-      <c r="P10" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">FireEffectProjectile</t>
+        </is>
+      </c>
+      <c r="P10" s="0">
         <v>30</v>
       </c>
-      <c r="Q10" s="0" t="n">
+      <c r="Q10" s="0">
         <v>0.3</v>
       </c>
       <c r="R10" s="0" t="inlineStr">
-        <is>
-          <t>60002</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">60002</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>31003</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">31003</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>엘리트 미사일 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">엘리트 미사일 포탑</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>미사일 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D11" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">미사일 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D11" s="0">
         <v>150</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="0">
         <v>0</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t>EliteMissileTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">EliteMissileTurretTrain</t>
         </is>
       </c>
       <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_KMD_10_UI</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_10_UI</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t>50003</t>
-        </is>
-      </c>
-      <c r="I11" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">50003</t>
+        </is>
+      </c>
+      <c r="I11" s="0">
         <v>10</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" s="0">
         <v>10</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="0">
         <v>100</v>
       </c>
-      <c r="L11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="0" t="n">
+      <c r="L11" s="0">
+        <v>1</v>
+      </c>
+      <c r="M11" s="0">
         <v>0.5</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="0">
         <v>0</v>
       </c>
       <c r="O11" s="0" t="inlineStr">
-        <is>
-          <t>MissileProjectile</t>
-        </is>
-      </c>
-      <c r="P11" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">MissileProjectile</t>
+        </is>
+      </c>
+      <c r="P11" s="0">
         <v>30</v>
       </c>
-      <c r="Q11" s="0" t="n">
+      <c r="Q11" s="0">
         <v>0.3</v>
       </c>
       <c r="R11" s="0" t="inlineStr">
-        <is>
-          <t>60003</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">60003</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>31004</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">31004</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>엘리트 레이저 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">엘리트 레이저 포탑</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>레이저 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D12" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">레이저 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D12" s="0">
         <v>150</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="0">
         <v>0</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
-        <is>
-          <t>EliteLaserTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">EliteLaserTurretTrain</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_288_19_UI</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_288_19_UI</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>50004</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">50004</t>
+        </is>
+      </c>
+      <c r="I12" s="0">
         <v>10</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" s="0">
         <v>10</v>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="K12" s="0">
         <v>300</v>
       </c>
-      <c r="L12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="0" t="n">
+      <c r="L12" s="0">
+        <v>1</v>
+      </c>
+      <c r="M12" s="0">
         <v>3</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="0">
         <v>0</v>
       </c>
       <c r="O12" s="0" t="inlineStr">
-        <is>
-          <t>LaserProjectile</t>
-        </is>
-      </c>
-      <c r="P12" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">LaserProjectile</t>
+        </is>
+      </c>
+      <c r="P12" s="0">
         <v>30</v>
       </c>
-      <c r="Q12" s="0" t="n">
+      <c r="Q12" s="0">
         <v>0.3</v>
       </c>
       <c r="R12" s="0" t="inlineStr">
-        <is>
-          <t>60004</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">60004</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>31005</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">31005</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>엘리트 전기 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">엘리트 전기 포탑</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t>전기 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D13" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">전기 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D13" s="0">
         <v>150</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="0">
         <v>0</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
-        <is>
-          <t>EliteElectrickTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">EliteElectrickTurretTrain</t>
         </is>
       </c>
       <c r="G13" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_MEL_16_UI</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_16_UI</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t>50005</t>
-        </is>
-      </c>
-      <c r="I13" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">50005</t>
+        </is>
+      </c>
+      <c r="I13" s="0">
         <v>10</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="0">
         <v>10</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="K13" s="0">
         <v>400</v>
       </c>
-      <c r="L13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="0" t="n">
+      <c r="L13" s="0">
+        <v>1</v>
+      </c>
+      <c r="M13" s="0">
         <v>5</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="0">
         <v>0</v>
       </c>
       <c r="O13" s="0" t="inlineStr">
-        <is>
-          <t>ElectrickProjectile</t>
-        </is>
-      </c>
-      <c r="P13" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">ElectrickProjectile</t>
+        </is>
+      </c>
+      <c r="P13" s="0">
         <v>30</v>
       </c>
-      <c r="Q13" s="0" t="n">
+      <c r="Q13" s="0">
         <v>0.3</v>
       </c>
       <c r="R13" s="0" t="inlineStr">
-        <is>
-          <t>60005</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">60005</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>31006</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">31006</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t>엘리트 포격 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">엘리트 포격 포탑</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
-        <is>
-          <t>포격 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D14" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">포격 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D14" s="0">
         <v>150</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="0">
         <v>0</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
-        <is>
-          <t>EliteCannonTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">EliteCannonTurretTrain</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_MEL_14_UI</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_14_UI</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
-        <is>
-          <t>50006</t>
-        </is>
-      </c>
-      <c r="I14" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">50006</t>
+        </is>
+      </c>
+      <c r="I14" s="0">
         <v>10</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="0">
         <v>10</v>
       </c>
-      <c r="K14" s="0" t="n">
+      <c r="K14" s="0">
         <v>400</v>
       </c>
-      <c r="L14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="0" t="n">
+      <c r="L14" s="0">
+        <v>1</v>
+      </c>
+      <c r="M14" s="0">
         <v>3</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="0">
         <v>0</v>
       </c>
       <c r="O14" s="0" t="inlineStr">
-        <is>
-          <t>CannonProjectile</t>
-        </is>
-      </c>
-      <c r="P14" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">CannonProjectile</t>
+        </is>
+      </c>
+      <c r="P14" s="0">
         <v>30</v>
       </c>
-      <c r="Q14" s="0" t="n">
+      <c r="Q14" s="0">
         <v>0.3</v>
       </c>
       <c r="R14" s="0" t="inlineStr">
-        <is>
-          <t>60006</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">60006</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>31007</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">31007</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t>엘리트 저격 포탑</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">엘리트 저격 포탑</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
-        <is>
-          <t>저격 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D15" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">저격 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D15" s="0">
         <v>150</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="0">
         <v>0</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
-        <is>
-          <t>EliteSniperTurretTrain</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">EliteSniperTurretTrain</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
-        <is>
-          <t>Weapon_KMD_12_UI</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_12_UI</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
-        <is>
-          <t>50007</t>
-        </is>
-      </c>
-      <c r="I15" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">50007</t>
+        </is>
+      </c>
+      <c r="I15" s="0">
         <v>10</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="0">
         <v>10</v>
       </c>
-      <c r="K15" s="0" t="n">
+      <c r="K15" s="0">
         <v>600</v>
       </c>
-      <c r="L15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="0" t="n">
+      <c r="L15" s="0">
+        <v>1</v>
+      </c>
+      <c r="M15" s="0">
         <v>1.5</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="0">
         <v>0</v>
       </c>
       <c r="O15" s="0" t="inlineStr">
-        <is>
-          <t>SniperProjectile</t>
-        </is>
-      </c>
-      <c r="P15" s="0" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">SniperProjectile</t>
+        </is>
+      </c>
+      <c r="P15" s="0">
         <v>30</v>
       </c>
-      <c r="Q15" s="0" t="n">
+      <c r="Q15" s="0">
         <v>0.3</v>
       </c>
       <c r="R15" s="0" t="inlineStr">
-        <is>
-          <t>60007</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">60007</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1,56 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="600" activeTab="2"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28545" windowHeight="11700" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="train_data" sheetId="1" r:id="rId1"/>
-    <sheet name="range_train_data" sheetId="2" r:id="rId2"/>
-    <sheet name="turret_train_data" sheetId="3" r:id="rId3"/>
+    <sheet name="train_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="range_train_data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="turret_train_data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="6">
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
   </fonts>
   <fills count="2">
@@ -83,10 +80,10 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,1661 +499,2041 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet1">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
-    <col min="3" max="3" width="24.16796875" style="1" bestFit="1" customWidth="1"/>
+    <col width="24.16796875" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
-        <v>train_name</v>
-        <is>
-          <t xml:space="preserve">train_name</t>
+        <is>
+          <t>train_name</t>
         </is>
       </c>
       <c r="C1" s="0" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
+        <is>
+          <t>description</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
-        <v>max_hp</v>
-        <is>
-          <t xml:space="preserve">max_hp</t>
+        <is>
+          <t>max_hp</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
-        <v>is_main_train</v>
-        <is>
-          <t xml:space="preserve">is_main_train</t>
+        <is>
+          <t>is_main_train</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
-        <v>prefab_id</v>
-        <is>
-          <t xml:space="preserve">prefab_id</t>
+        <is>
+          <t>prefab_id</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
-        <v>icon_id</v>
-        <is>
-          <t xml:space="preserve">icon_id</t>
+        <is>
+          <t>icon_id</t>
         </is>
       </c>
       <c r="H1" s="0" t="inlineStr">
-        <v>train_skill_data_id</v>
-        <is>
-          <t xml:space="preserve">train_skill_data_id</t>
+        <is>
+          <t>train_skill_data_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">20001</t>
+        <is>
+          <t>20001</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">기본 기차</t>
+        <is>
+          <t>기본 기차</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
-        </is>
-      </c>
-      <c r="D2" s="0">
+        <is>
+          <t>가장 기본이 되는 기차이다.</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">MainTrain</t>
+        <is>
+          <t>MainTrain</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet2">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
-        <v>train_name</v>
-        <is>
-          <t xml:space="preserve">train_name</t>
+        <is>
+          <t>train_name</t>
         </is>
       </c>
       <c r="C1" s="0" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
+        <is>
+          <t>description</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
-        <v>max_hp</v>
-        <is>
-          <t xml:space="preserve">max_hp</t>
+        <is>
+          <t>max_hp</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
-        <v>is_main_train</v>
-        <is>
-          <t xml:space="preserve">is_main_train</t>
+        <is>
+          <t>is_main_train</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
-        <v>prefab_id</v>
-        <is>
-          <t xml:space="preserve">prefab_id</t>
+        <is>
+          <t>prefab_id</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
-        <v>icon_id</v>
-        <is>
-          <t xml:space="preserve">icon_id</t>
+        <is>
+          <t>icon_id</t>
         </is>
       </c>
       <c r="H1" s="0" t="inlineStr">
-        <v>train_skill_data_id</v>
-        <is>
-          <t xml:space="preserve">train_skill_data_id</t>
+        <is>
+          <t>train_skill_data_id</t>
         </is>
       </c>
       <c r="I1" s="0" t="inlineStr">
-        <v>attack_range</v>
-        <is>
-          <t xml:space="preserve">attack_range</t>
+        <is>
+          <t>attack_range</t>
         </is>
       </c>
       <c r="J1" s="0" t="inlineStr">
-        <v>attack_area</v>
-        <is>
-          <t xml:space="preserve">attack_area</t>
+        <is>
+          <t>attack_area</t>
         </is>
       </c>
       <c r="K1" s="0" t="inlineStr">
-        <v>attack_damage</v>
-        <is>
-          <t xml:space="preserve">attack_damage</t>
+        <is>
+          <t>attack_damage</t>
         </is>
       </c>
       <c r="L1" s="0" t="inlineStr">
-        <v>attack_count</v>
-        <is>
-          <t xml:space="preserve">attack_count</t>
+        <is>
+          <t>attack_count</t>
         </is>
       </c>
       <c r="M1" s="0" t="inlineStr">
-        <v>attack_interval</v>
-        <is>
-          <t xml:space="preserve">attack_interval</t>
+        <is>
+          <t>attack_interval</t>
         </is>
       </c>
       <c r="N1" s="0" t="inlineStr">
-        <v>range_projectile_prefab_id</v>
-        <is>
-          <t xml:space="preserve">range_projectile_prefab_id</t>
+        <is>
+          <t>range_projectile_prefab_id</t>
         </is>
       </c>
       <c r="O1" s="0" t="inlineStr">
-        <v>critical_chance</v>
-        <is>
-          <t xml:space="preserve">critical_chance</t>
+        <is>
+          <t>critical_chance</t>
         </is>
       </c>
       <c r="P1" s="0" t="inlineStr">
-        <v>critical_damage</v>
-        <is>
-          <t xml:space="preserve">critical_damage</t>
+        <is>
+          <t>critical_damage</t>
         </is>
       </c>
       <c r="Q1" s="0" t="inlineStr">
-        <v>passive_skill_data_id</v>
-        <is>
-          <t xml:space="preserve">passive_skill_data_id</t>
+        <is>
+          <t>passive_skill_data_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">40001</t>
+        <is>
+          <t>40001</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">폭발 포탑</t>
+        <is>
+          <t>폭발 포탑</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">적이 가장 많은 곳으로 위치해 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D2" s="0">
+        <is>
+          <t>적이 가장 많은 곳으로 위치해 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ExplosionRangeTrain</t>
+        <is>
+          <t>ExplosionRangeTrain</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-        </is>
-      </c>
-      <c r="I2" s="0">
+        <is>
+          <t>현대무기_대포_헤리콥터리코를_어쎄신</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J2" s="0">
+      <c r="J2" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="K2" s="0">
+      <c r="K2" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="L2" s="0">
-        <v>1</v>
-      </c>
-      <c r="M2" s="0">
+      <c r="L2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="0" t="n">
         <v>4</v>
       </c>
       <c r="N2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ExplosionProjectile</t>
-        </is>
-      </c>
-      <c r="O2" s="0">
-        <v>30</v>
-      </c>
-      <c r="P2" s="0">
+        <is>
+          <t>ExplosionProjectile</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="P2" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">40002</t>
+        <is>
+          <t>40002</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">냉기 포탑</t>
+        <is>
+          <t>냉기 포탑</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D3" s="0">
+        <is>
+          <t>적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E3" s="0">
+      <c r="E3" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ColdAirRangeTrain</t>
+        <is>
+          <t>ColdAirRangeTrain</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">현대무기_대포_288스마</t>
-        </is>
-      </c>
-      <c r="I3" s="0">
+        <is>
+          <t>현대무기_대포_288스마</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="0">
+      <c r="J3" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="K3" s="0">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0">
-        <v>1</v>
-      </c>
-      <c r="M3" s="0">
+      <c r="K3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="0" t="n">
         <v>0.1</v>
       </c>
       <c r="N3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ColdAirProjectile</t>
-        </is>
-      </c>
-      <c r="O3" s="0">
-        <v>30</v>
-      </c>
-      <c r="P3" s="0">
+        <is>
+          <t>ColdAirProjectile</t>
+        </is>
+      </c>
+      <c r="O3" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="P3" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">41001</t>
+        <is>
+          <t>41001</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 폭발 포탑</t>
+        <is>
+          <t>엘리트 폭발 포탑</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">폭발 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D4" s="0">
+        <is>
+          <t>폭발 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E4" s="0">
+      <c r="E4" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteExplosionRangeTrain</t>
+        <is>
+          <t>EliteExplosionRangeTrain</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50008</t>
-        </is>
-      </c>
-      <c r="I4" s="0">
+        <is>
+          <t>50008</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="0">
+      <c r="J4" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="K4" s="0">
+      <c r="K4" s="0" t="n">
         <v>500</v>
       </c>
-      <c r="L4" s="0">
-        <v>1</v>
-      </c>
-      <c r="M4" s="0">
+      <c r="L4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="0" t="n">
         <v>4</v>
       </c>
       <c r="N4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ExplosionProjectile</t>
-        </is>
-      </c>
-      <c r="O4" s="0">
-        <v>30</v>
-      </c>
-      <c r="P4" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="Q4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60008</t>
-        </is>
-      </c>
+        <is>
+          <t>ExplosionProjectile</t>
+        </is>
+      </c>
+      <c r="O4" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="P4" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q4" s="0" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">41002</t>
+        <is>
+          <t>41002</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 냉기 포탑</t>
+        <is>
+          <t>엘리트 냉기 포탑</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">냉기 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D5" s="0">
+        <is>
+          <t>냉기 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E5" s="0">
+      <c r="E5" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteColdAirRangeTrain</t>
+        <is>
+          <t>EliteColdAirRangeTrain</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50009</t>
-        </is>
-      </c>
-      <c r="I5" s="0">
+        <is>
+          <t>50009</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="J5" s="0">
+      <c r="J5" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="K5" s="0">
+      <c r="K5" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="L5" s="0">
-        <v>1</v>
-      </c>
-      <c r="M5" s="0">
+      <c r="L5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="0" t="n">
         <v>0.1</v>
       </c>
       <c r="N5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ColdAirProjectile</t>
-        </is>
-      </c>
-      <c r="O5" s="0">
-        <v>30</v>
-      </c>
-      <c r="P5" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="Q5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60009</t>
+        <is>
+          <t>ColdAirProjectile</t>
+        </is>
+      </c>
+      <c r="O5" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q5" s="0" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>42001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>엘리트 폭발 포탑</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>폭발 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>150</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>EliteExplosionRangeTrain</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>500</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ExplosionProjectile</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>30</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>60008</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>42002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>엘리트 냉기 포탑</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>냉기 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>EliteColdAirRangeTrain</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" t="n">
+        <v>15</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ColdAirProjectile</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>30</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>60009</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet3">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
-    <col min="2" max="2" width="17.4609375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.15625" style="1" bestFit="1" customWidth="1"/>
+    <col width="17.4609375" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col width="81.25" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="21.1328125" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
+    <col width="18.7265625" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
+    <col width="20.25" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
+    <col width="23.15625" bestFit="1" customWidth="1" style="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
-        <v>train_name</v>
-        <is>
-          <t xml:space="preserve">train_name</t>
+        <is>
+          <t>train_name</t>
         </is>
       </c>
       <c r="C1" s="0" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
+        <is>
+          <t>description</t>
         </is>
       </c>
       <c r="D1" s="0" t="inlineStr">
-        <v>max_hp</v>
-        <is>
-          <t xml:space="preserve">max_hp</t>
+        <is>
+          <t>max_hp</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
-        <v>is_main_train</v>
-        <is>
-          <t xml:space="preserve">is_main_train</t>
+        <is>
+          <t>is_main_train</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
-        <v>prefab_id</v>
-        <is>
-          <t xml:space="preserve">prefab_id</t>
+        <is>
+          <t>prefab_id</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
-        <v>icon_id</v>
-        <is>
-          <t xml:space="preserve">icon_id</t>
+        <is>
+          <t>icon_id</t>
         </is>
       </c>
       <c r="H1" s="0" t="inlineStr">
-        <v>train_skill_data_id</v>
-        <is>
-          <t xml:space="preserve">train_skill_data_id</t>
+        <is>
+          <t>train_skill_data_id</t>
         </is>
       </c>
       <c r="I1" s="0" t="inlineStr">
-        <v>attack_range</v>
-        <is>
-          <t xml:space="preserve">attack_range</t>
+        <is>
+          <t>attack_range</t>
         </is>
       </c>
       <c r="J1" s="0" t="inlineStr">
-        <v>attack_area</v>
-        <is>
-          <t xml:space="preserve">attack_area</t>
+        <is>
+          <t>attack_area</t>
         </is>
       </c>
       <c r="K1" s="0" t="inlineStr">
-        <v>attack_damage</v>
-        <is>
-          <t xml:space="preserve">attack_damage</t>
+        <is>
+          <t>attack_damage</t>
         </is>
       </c>
       <c r="L1" s="0" t="inlineStr">
-        <v>attack_count</v>
-        <is>
-          <t xml:space="preserve">attack_count</t>
+        <is>
+          <t>attack_count</t>
         </is>
       </c>
       <c r="M1" s="0" t="inlineStr">
-        <v>attack_interval</v>
-        <is>
-          <t xml:space="preserve">attack_interval</t>
+        <is>
+          <t>attack_interval</t>
         </is>
       </c>
       <c r="N1" s="0" t="inlineStr">
-        <v>target_count</v>
-        <is>
-          <t xml:space="preserve">target_count</t>
+        <is>
+          <t>target_count</t>
         </is>
       </c>
       <c r="O1" s="0" t="inlineStr">
-        <v>turret_projectile_prefab_id</v>
-        <is>
-          <t xml:space="preserve">turret_projectile_prefab_id</t>
+        <is>
+          <t>turret_projectile_prefab_id</t>
         </is>
       </c>
       <c r="P1" s="0" t="inlineStr">
-        <v>critical_chance</v>
-        <is>
-          <t xml:space="preserve">critical_chance</t>
+        <is>
+          <t>critical_chance</t>
         </is>
       </c>
       <c r="Q1" s="0" t="inlineStr">
-        <v>critical_damage</v>
-        <is>
-          <t xml:space="preserve">critical_damage</t>
+        <is>
+          <t>critical_damage</t>
         </is>
       </c>
       <c r="R1" s="0" t="inlineStr">
-        <v>passive_skill_data_id</v>
-        <is>
-          <t xml:space="preserve">passive_skill_data_id</t>
+        <is>
+          <t>passive_skill_data_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30001</t>
+        <is>
+          <t>30001</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">기관총 포탑</t>
+        <is>
+          <t>기관총 포탑</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">기관총으로 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D2" s="0">
+        <is>
+          <t>기관총으로 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">NormalTurretTrain</t>
+        <is>
+          <t>NormalTurretTrain</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_08_UI</t>
-        </is>
-      </c>
-      <c r="I2" s="0">
-        <v>10</v>
-      </c>
-      <c r="J2" s="0">
-        <v>10</v>
-      </c>
-      <c r="K2" s="0">
-        <v>10</v>
-      </c>
-      <c r="L2" s="0">
-        <v>1</v>
-      </c>
-      <c r="M2" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="N2" s="0">
+        <is>
+          <t>Weapon_KMD_08_UI</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="O2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">NormalProjectile</t>
-        </is>
-      </c>
-      <c r="P2" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="0">
+        <is>
+          <t>NormalProjectile</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30002</t>
+        <is>
+          <t>30002</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">화염 포탑</t>
+        <is>
+          <t>화염 포탑</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D3" s="0">
+        <is>
+          <t>화염으로 지속적인 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E3" s="0">
+      <c r="E3" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">FireTurretTrain</t>
+        <is>
+          <t>FireTurretTrain</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_05_UI</t>
-        </is>
-      </c>
-      <c r="I3" s="0">
+        <is>
+          <t>Weapon_MEL_05_UI</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="J3" s="0">
+      <c r="J3" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="K3" s="0">
+      <c r="K3" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="L3" s="0">
-        <v>1</v>
-      </c>
-      <c r="M3" s="0">
+      <c r="L3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="0" t="n">
         <v>0.15</v>
       </c>
-      <c r="N3" s="0">
+      <c r="N3" s="0" t="n">
         <v>1</v>
       </c>
       <c r="O3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">FireEffectProjectile</t>
-        </is>
-      </c>
-      <c r="P3" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="0">
+        <is>
+          <t>FireEffectProjectile</t>
+        </is>
+      </c>
+      <c r="P3" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30003</t>
+        <is>
+          <t>30003</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">미사일 포탑</t>
+        <is>
+          <t>미사일 포탑</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
-        </is>
-      </c>
-      <c r="D4" s="0">
+        <is>
+          <t>미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E4" s="0">
+      <c r="E4" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">MissileTurretTrain</t>
+        <is>
+          <t>MissileTurretTrain</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_10_UI</t>
-        </is>
-      </c>
-      <c r="I4" s="0">
-        <v>10</v>
-      </c>
-      <c r="J4" s="0">
-        <v>10</v>
-      </c>
-      <c r="K4" s="0">
+        <is>
+          <t>Weapon_KMD_10_UI</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="L4" s="0">
-        <v>1</v>
-      </c>
-      <c r="M4" s="0">
+      <c r="L4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="0" t="n">
         <v>1.25</v>
       </c>
-      <c r="N4" s="0">
+      <c r="N4" s="0" t="n">
         <v>1</v>
       </c>
       <c r="O4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">MissileProjectile</t>
-        </is>
-      </c>
-      <c r="P4" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q4" s="0">
+        <is>
+          <t>MissileProjectile</t>
+        </is>
+      </c>
+      <c r="P4" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30004</t>
+        <is>
+          <t>30004</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">레이저 포탑</t>
+        <is>
+          <t>레이저 포탑</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D5" s="0">
+        <is>
+          <t>레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E5" s="0">
+      <c r="E5" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">LaserTurretTrain</t>
+        <is>
+          <t>LaserTurretTrain</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_288_19_UI</t>
-        </is>
-      </c>
-      <c r="I5" s="0">
-        <v>30</v>
-      </c>
-      <c r="J5" s="0">
-        <v>30</v>
-      </c>
-      <c r="K5" s="0">
+        <is>
+          <t>Weapon_288_19_UI</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="L5" s="0">
-        <v>1</v>
-      </c>
-      <c r="M5" s="0">
+      <c r="L5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="N5" s="0">
+      <c r="N5" s="0" t="n">
         <v>1</v>
       </c>
       <c r="O5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">LaserProjectile</t>
-        </is>
-      </c>
-      <c r="P5" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="0">
+        <is>
+          <t>LaserProjectile</t>
+        </is>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30005</t>
+        <is>
+          <t>30005</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">전기 포탑</t>
+        <is>
+          <t>전기 포탑</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">화면에 있는 다수의 적들을 통시에 공격한다.</t>
-        </is>
-      </c>
-      <c r="D6" s="0">
+        <is>
+          <t>화면에 있는 다수의 적들을 통시에 공격한다.</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E6" s="0">
+      <c r="E6" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ElectrickTurretTrain</t>
+        <is>
+          <t>ElectrickTurretTrain</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_16_UI</t>
-        </is>
-      </c>
-      <c r="I6" s="0">
+        <is>
+          <t>Weapon_MEL_16_UI</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="J6" s="0">
+      <c r="J6" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="K6" s="0">
-        <v>10</v>
-      </c>
-      <c r="L6" s="0">
+      <c r="K6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="M6" s="0">
-        <v>1</v>
-      </c>
-      <c r="N6" s="0">
+      <c r="M6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="0" t="n">
         <v>3</v>
       </c>
       <c r="O6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ElectrickProjectile</t>
-        </is>
-      </c>
-      <c r="P6" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q6" s="0">
+        <is>
+          <t>ElectrickProjectile</t>
+        </is>
+      </c>
+      <c r="P6" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30006</t>
+        <is>
+          <t>30006</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">포격 포탑</t>
+        <is>
+          <t>포격 포탑</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
-        </is>
-      </c>
-      <c r="D7" s="0">
+        <is>
+          <t>거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E7" s="0">
+      <c r="E7" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">CannonTurretTrain</t>
+        <is>
+          <t>CannonTurretTrain</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_14_UI</t>
-        </is>
-      </c>
-      <c r="I7" s="0">
+        <is>
+          <t>Weapon_MEL_14_UI</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="0">
+      <c r="J7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="0">
+      <c r="K7" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="L7" s="0">
-        <v>1</v>
-      </c>
-      <c r="M7" s="0">
+      <c r="L7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="N7" s="0">
+      <c r="N7" s="0" t="n">
         <v>1</v>
       </c>
       <c r="O7" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">CannonProjectile</t>
-        </is>
-      </c>
-      <c r="P7" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q7" s="0">
+        <is>
+          <t>CannonProjectile</t>
+        </is>
+      </c>
+      <c r="P7" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q7" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30007</t>
+        <is>
+          <t>30007</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">저격 포탑</t>
+        <is>
+          <t>저격 포탑</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
-        </is>
-      </c>
-      <c r="D8" s="0">
+        <is>
+          <t>저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="n">
         <v>250</v>
       </c>
-      <c r="E8" s="0">
+      <c r="E8" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">SniperTurretTrain</t>
+        <is>
+          <t>SniperTurretTrain</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_12_UI</t>
-        </is>
-      </c>
-      <c r="I8" s="0">
-        <v>30</v>
-      </c>
-      <c r="J8" s="0">
-        <v>30</v>
-      </c>
-      <c r="K8" s="0">
+        <is>
+          <t>Weapon_KMD_12_UI</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="L8" s="0">
-        <v>1</v>
-      </c>
-      <c r="M8" s="0">
-        <v>1</v>
-      </c>
-      <c r="N8" s="0">
+      <c r="L8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="0" t="n">
         <v>1</v>
       </c>
       <c r="O8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">SniperProjectile</t>
-        </is>
-      </c>
-      <c r="P8" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q8" s="0">
+        <is>
+          <t>SniperProjectile</t>
+        </is>
+      </c>
+      <c r="P8" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="0" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31001</t>
+        <is>
+          <t>31001</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 기관총 포탑</t>
+        <is>
+          <t>엘리트 기관총 포탑</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">기관총 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D9" s="0">
+        <is>
+          <t>기관총 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E9" s="0">
+      <c r="E9" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteNormalTurretTrain</t>
+        <is>
+          <t>EliteNormalTurretTrain</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_08_UI</t>
+        <is>
+          <t>Weapon_KMD_08_UI</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50001</t>
-        </is>
-      </c>
-      <c r="I9" s="0">
-        <v>10</v>
-      </c>
-      <c r="J9" s="0">
-        <v>10</v>
-      </c>
-      <c r="K9" s="0">
+        <is>
+          <t>50001</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="L9" s="0">
-        <v>1</v>
-      </c>
-      <c r="M9" s="0">
+      <c r="L9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="N9" s="0">
+      <c r="N9" s="0" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">NormalProjectile</t>
-        </is>
-      </c>
-      <c r="P9" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q9" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="R9" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60001</t>
-        </is>
-      </c>
+        <is>
+          <t>NormalProjectile</t>
+        </is>
+      </c>
+      <c r="P9" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q9" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R9" s="0" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31002</t>
+        <is>
+          <t>31002</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 화염 포탑</t>
+        <is>
+          <t>엘리트 화염 포탑</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">화염 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D10" s="0">
+        <is>
+          <t>화염 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E10" s="0">
+      <c r="E10" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteFireTurretTrain</t>
+        <is>
+          <t>EliteFireTurretTrain</t>
         </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_05_UI</t>
+        <is>
+          <t>Weapon_MEL_05_UI</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50002</t>
-        </is>
-      </c>
-      <c r="I10" s="0">
-        <v>10</v>
-      </c>
-      <c r="J10" s="0">
-        <v>10</v>
-      </c>
-      <c r="K10" s="0">
+        <is>
+          <t>50002</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="L10" s="0">
-        <v>1</v>
-      </c>
-      <c r="M10" s="0">
+      <c r="L10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="N10" s="0">
+      <c r="N10" s="0" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">FireEffectProjectile</t>
-        </is>
-      </c>
-      <c r="P10" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q10" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="R10" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60002</t>
-        </is>
-      </c>
+        <is>
+          <t>FireEffectProjectile</t>
+        </is>
+      </c>
+      <c r="P10" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31003</t>
+        <is>
+          <t>31003</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 미사일 포탑</t>
+        <is>
+          <t>엘리트 미사일 포탑</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">미사일 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D11" s="0">
+        <is>
+          <t>미사일 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E11" s="0">
+      <c r="E11" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteMissileTurretTrain</t>
+        <is>
+          <t>EliteMissileTurretTrain</t>
         </is>
       </c>
       <c r="G11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_10_UI</t>
+        <is>
+          <t>Weapon_KMD_10_UI</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50003</t>
-        </is>
-      </c>
-      <c r="I11" s="0">
-        <v>10</v>
-      </c>
-      <c r="J11" s="0">
-        <v>10</v>
-      </c>
-      <c r="K11" s="0">
+        <is>
+          <t>50003</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="L11" s="0">
-        <v>1</v>
-      </c>
-      <c r="M11" s="0">
+      <c r="L11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="N11" s="0">
+      <c r="N11" s="0" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">MissileProjectile</t>
-        </is>
-      </c>
-      <c r="P11" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q11" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="R11" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60003</t>
-        </is>
-      </c>
+        <is>
+          <t>MissileProjectile</t>
+        </is>
+      </c>
+      <c r="P11" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q11" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31004</t>
+        <is>
+          <t>31004</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 레이저 포탑</t>
+        <is>
+          <t>엘리트 레이저 포탑</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">레이저 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D12" s="0">
+        <is>
+          <t>레이저 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E12" s="0">
+      <c r="E12" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteLaserTurretTrain</t>
+        <is>
+          <t>EliteLaserTurretTrain</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_288_19_UI</t>
+        <is>
+          <t>Weapon_288_19_UI</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50004</t>
-        </is>
-      </c>
-      <c r="I12" s="0">
-        <v>10</v>
-      </c>
-      <c r="J12" s="0">
-        <v>10</v>
-      </c>
-      <c r="K12" s="0">
+        <is>
+          <t>50004</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="L12" s="0">
-        <v>1</v>
-      </c>
-      <c r="M12" s="0">
+      <c r="L12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="N12" s="0">
+      <c r="N12" s="0" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">LaserProjectile</t>
-        </is>
-      </c>
-      <c r="P12" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q12" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="R12" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60004</t>
-        </is>
-      </c>
+        <is>
+          <t>LaserProjectile</t>
+        </is>
+      </c>
+      <c r="P12" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q12" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31005</t>
+        <is>
+          <t>31005</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 전기 포탑</t>
+        <is>
+          <t>엘리트 전기 포탑</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">전기 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D13" s="0">
+        <is>
+          <t>전기 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E13" s="0">
+      <c r="E13" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteElectrickTurretTrain</t>
+        <is>
+          <t>EliteElectrickTurretTrain</t>
         </is>
       </c>
       <c r="G13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_16_UI</t>
+        <is>
+          <t>Weapon_MEL_16_UI</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50005</t>
-        </is>
-      </c>
-      <c r="I13" s="0">
-        <v>10</v>
-      </c>
-      <c r="J13" s="0">
-        <v>10</v>
-      </c>
-      <c r="K13" s="0">
+        <is>
+          <t>50005</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="L13" s="0">
-        <v>1</v>
-      </c>
-      <c r="M13" s="0">
+      <c r="L13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="N13" s="0">
+      <c r="N13" s="0" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ElectrickProjectile</t>
-        </is>
-      </c>
-      <c r="P13" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q13" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="R13" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60005</t>
-        </is>
-      </c>
+        <is>
+          <t>ElectrickProjectile</t>
+        </is>
+      </c>
+      <c r="P13" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q13" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31006</t>
+        <is>
+          <t>31006</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 포격 포탑</t>
+        <is>
+          <t>엘리트 포격 포탑</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">포격 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D14" s="0">
+        <is>
+          <t>포격 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E14" s="0">
+      <c r="E14" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteCannonTurretTrain</t>
+        <is>
+          <t>EliteCannonTurretTrain</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_14_UI</t>
+        <is>
+          <t>Weapon_MEL_14_UI</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50006</t>
-        </is>
-      </c>
-      <c r="I14" s="0">
-        <v>10</v>
-      </c>
-      <c r="J14" s="0">
-        <v>10</v>
-      </c>
-      <c r="K14" s="0">
+        <is>
+          <t>50006</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="L14" s="0">
-        <v>1</v>
-      </c>
-      <c r="M14" s="0">
+      <c r="L14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="0">
+      <c r="N14" s="0" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">CannonProjectile</t>
-        </is>
-      </c>
-      <c r="P14" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q14" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="R14" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60006</t>
-        </is>
-      </c>
+        <is>
+          <t>CannonProjectile</t>
+        </is>
+      </c>
+      <c r="P14" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q14" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R14" s="0" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">31007</t>
+        <is>
+          <t>31007</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">엘리트 저격 포탑</t>
+        <is>
+          <t>엘리트 저격 포탑</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">저격 포탑의 강화 버전이다.</t>
-        </is>
-      </c>
-      <c r="D15" s="0">
+        <is>
+          <t>저격 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="n">
         <v>150</v>
       </c>
-      <c r="E15" s="0">
+      <c r="E15" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">EliteSniperTurretTrain</t>
+        <is>
+          <t>EliteSniperTurretTrain</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_12_UI</t>
+        <is>
+          <t>Weapon_KMD_12_UI</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50007</t>
-        </is>
-      </c>
-      <c r="I15" s="0">
-        <v>10</v>
-      </c>
-      <c r="J15" s="0">
-        <v>10</v>
-      </c>
-      <c r="K15" s="0">
+        <is>
+          <t>50007</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <v>600</v>
       </c>
-      <c r="L15" s="0">
-        <v>1</v>
-      </c>
-      <c r="M15" s="0">
+      <c r="L15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="N15" s="0">
+      <c r="N15" s="0" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">SniperProjectile</t>
-        </is>
-      </c>
-      <c r="P15" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q15" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="R15" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">60007</t>
+        <is>
+          <t>SniperProjectile</t>
+        </is>
+      </c>
+      <c r="P15" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q15" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R15" s="0" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>32001</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>엘리트 기관총 포탑</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>기관총 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>150</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>EliteNormalTurretTrain</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Weapon_KMD_08_UI</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" t="n">
+        <v>50</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NormalProjectile</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>60001</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>32002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>엘리트 화염 포탑</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>화염 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>150</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>EliteFireTurretTrain</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Weapon_MEL_05_UI</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" t="n">
+        <v>25</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>FireEffectProjectile</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>60002</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>32003</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>엘리트 미사일 포탑</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>미사일 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>150</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>EliteMissileTurretTrain</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Weapon_KMD_10_UI</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10</v>
+      </c>
+      <c r="K18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>MissileProjectile</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>60003</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>32004</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>엘리트 레이저 포탑</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>레이저 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>150</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>EliteLaserTurretTrain</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Weapon_288_19_UI</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" t="n">
+        <v>300</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>LaserProjectile</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>60004</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>32005</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>엘리트 전기 포탑</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>전기 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>150</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>EliteElectrickTurretTrain</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Weapon_MEL_16_UI</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" t="n">
+        <v>400</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>ElectrickProjectile</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>60005</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>32006</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>엘리트 포격 포탑</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>포격 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>150</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>EliteCannonTurretTrain</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Weapon_MEL_14_UI</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" t="n">
+        <v>10</v>
+      </c>
+      <c r="K21" t="n">
+        <v>400</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>CannonProjectile</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>60006</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>32007</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>엘리트 저격 포탑</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>저격 포탑의 강화 버전이다.</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>150</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>EliteSniperTurretTrain</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Weapon_KMD_12_UI</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" t="n">
+        <v>10</v>
+      </c>
+      <c r="K22" t="n">
+        <v>600</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>SniperProjectile</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>60007</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="121">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -382,6 +382,9 @@
   </si>
   <si>
     <t xml:space="preserve">50006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
   </si>
 </sst>
 </file>
@@ -800,7 +803,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="0"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="3" max="3" width="24.140625" style="1" bestFit="1" customWidth="1"/>
@@ -829,7 +832,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>7</v>
+        <v>20</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55">
@@ -897,34 +903,34 @@
         <v>6</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.55">
@@ -949,28 +955,28 @@
       <c r="G2" s="0" t="s">
         <v>25</v>
       </c>
+      <c r="H2" s="0">
+        <v>5</v>
+      </c>
       <c r="I2" s="0">
         <v>5</v>
       </c>
       <c r="J2" s="0">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="K2" s="0">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L2" s="0">
-        <v>1</v>
-      </c>
-      <c r="M2" s="0">
         <v>4</v>
       </c>
-      <c r="N2" s="0" t="s">
+      <c r="M2" s="0" t="s">
         <v>26</v>
       </c>
+      <c r="N2" s="0">
+        <v>30</v>
+      </c>
       <c r="O2" s="0">
-        <v>30</v>
-      </c>
-      <c r="P2" s="0">
         <v>0.3</v>
       </c>
     </row>
@@ -996,28 +1002,28 @@
       <c r="G3" s="0" t="s">
         <v>31</v>
       </c>
+      <c r="H3" s="0">
+        <v>5</v>
+      </c>
       <c r="I3" s="0">
         <v>5</v>
       </c>
       <c r="J3" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3" s="0">
         <v>1</v>
       </c>
       <c r="L3" s="0">
-        <v>1</v>
-      </c>
-      <c r="M3" s="0">
         <v>0.1</v>
       </c>
-      <c r="N3" s="0" t="s">
+      <c r="M3" s="0" t="s">
         <v>32</v>
       </c>
+      <c r="N3" s="0">
+        <v>30</v>
+      </c>
       <c r="O3" s="0">
-        <v>30</v>
-      </c>
-      <c r="P3" s="0">
         <v>0.3</v>
       </c>
     </row>
@@ -1037,32 +1043,32 @@
       <c r="F4" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="0" t="s">
-        <v>36</v>
+      <c r="H4" s="0">
+        <v>8</v>
       </c>
       <c r="I4" s="0">
         <v>8</v>
       </c>
       <c r="J4" s="0">
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="K4" s="0">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="L4" s="0">
-        <v>1</v>
-      </c>
-      <c r="M4" s="0">
         <v>4</v>
       </c>
-      <c r="N4" s="0" t="s">
+      <c r="M4" s="0" t="s">
         <v>26</v>
       </c>
+      <c r="N4" s="0">
+        <v>30</v>
+      </c>
       <c r="O4" s="0">
-        <v>30</v>
-      </c>
-      <c r="P4" s="0">
         <v>0.3</v>
+      </c>
+      <c r="Q4" s="0">
+        <v>50008</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.55">
@@ -1081,32 +1087,32 @@
       <c r="F5" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="0" t="s">
-        <v>40</v>
+      <c r="H5" s="0">
+        <v>13</v>
       </c>
       <c r="I5" s="0">
         <v>13</v>
       </c>
       <c r="J5" s="0">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K5" s="0">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L5" s="0">
-        <v>1</v>
-      </c>
-      <c r="M5" s="0">
         <v>0.1</v>
       </c>
-      <c r="N5" s="0" t="s">
+      <c r="M5" s="0" t="s">
         <v>32</v>
       </c>
+      <c r="N5" s="0">
+        <v>30</v>
+      </c>
       <c r="O5" s="0">
-        <v>30</v>
-      </c>
-      <c r="P5" s="0">
         <v>0.3</v>
+      </c>
+      <c r="Q5" s="0">
+        <v>50009</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.55">
@@ -1125,35 +1131,35 @@
       <c r="F6" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="0" t="s">
-        <v>36</v>
+      <c r="H6" s="0">
+        <v>8</v>
       </c>
       <c r="I6" s="0">
         <v>8</v>
       </c>
       <c r="J6" s="0">
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="K6" s="0">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="L6" s="0">
-        <v>1</v>
-      </c>
-      <c r="M6" s="0">
         <v>4</v>
       </c>
-      <c r="N6" s="0" t="s">
+      <c r="M6" s="0" t="s">
         <v>26</v>
       </c>
+      <c r="N6" s="0">
+        <v>30</v>
+      </c>
       <c r="O6" s="0">
-        <v>30</v>
-      </c>
-      <c r="P6" s="0">
         <v>0.3</v>
       </c>
-      <c r="Q6" s="0" t="s">
+      <c r="P6" s="0" t="s">
         <v>42</v>
+      </c>
+      <c r="Q6" s="0">
+        <v>50008</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.55">
@@ -1172,35 +1178,35 @@
       <c r="F7" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="0" t="s">
-        <v>40</v>
+      <c r="H7" s="0">
+        <v>13</v>
       </c>
       <c r="I7" s="0">
         <v>13</v>
       </c>
       <c r="J7" s="0">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K7" s="0">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L7" s="0">
-        <v>1</v>
-      </c>
-      <c r="M7" s="0">
         <v>0.1</v>
       </c>
-      <c r="N7" s="0" t="s">
+      <c r="M7" s="0" t="s">
         <v>32</v>
       </c>
+      <c r="N7" s="0">
+        <v>30</v>
+      </c>
       <c r="O7" s="0">
-        <v>30</v>
-      </c>
-      <c r="P7" s="0">
         <v>0.3</v>
       </c>
-      <c r="Q7" s="0" t="s">
+      <c r="P7" s="0" t="s">
         <v>44</v>
+      </c>
+      <c r="Q7" s="0">
+        <v>50009</v>
       </c>
     </row>
   </sheetData>
@@ -1249,37 +1255,37 @@
         <v>6</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>20</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.55">
@@ -1304,6 +1310,9 @@
       <c r="G2" s="0" t="s">
         <v>51</v>
       </c>
+      <c r="H2" s="0">
+        <v>10</v>
+      </c>
       <c r="I2" s="0">
         <v>10</v>
       </c>
@@ -1311,24 +1320,21 @@
         <v>10</v>
       </c>
       <c r="K2" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L2" s="0">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M2" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="N2" s="0">
-        <v>1</v>
-      </c>
-      <c r="O2" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="0" t="s">
         <v>52</v>
       </c>
+      <c r="O2" s="0">
+        <v>30</v>
+      </c>
       <c r="P2" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="0">
         <v>0.3</v>
       </c>
     </row>
@@ -1354,31 +1360,31 @@
       <c r="G3" s="0" t="s">
         <v>57</v>
       </c>
+      <c r="H3" s="0">
+        <v>8</v>
+      </c>
       <c r="I3" s="0">
         <v>8</v>
       </c>
       <c r="J3" s="0">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K3" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3" s="0">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="M3" s="0">
-        <v>0.15</v>
-      </c>
-      <c r="N3" s="0">
-        <v>1</v>
-      </c>
-      <c r="O3" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="0" t="s">
         <v>58</v>
       </c>
+      <c r="O3" s="0">
+        <v>30</v>
+      </c>
       <c r="P3" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="0">
         <v>0.3</v>
       </c>
     </row>
@@ -1404,31 +1410,31 @@
       <c r="G4" s="0" t="s">
         <v>63</v>
       </c>
+      <c r="H4" s="0">
+        <v>10</v>
+      </c>
       <c r="I4" s="0">
         <v>10</v>
       </c>
       <c r="J4" s="0">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K4" s="0">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L4" s="0">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="M4" s="0">
-        <v>1.25</v>
-      </c>
-      <c r="N4" s="0">
-        <v>1</v>
-      </c>
-      <c r="O4" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" s="0" t="s">
         <v>64</v>
       </c>
+      <c r="O4" s="0">
+        <v>30</v>
+      </c>
       <c r="P4" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q4" s="0">
         <v>0.3</v>
       </c>
     </row>
@@ -1454,31 +1460,31 @@
       <c r="G5" s="0" t="s">
         <v>69</v>
       </c>
+      <c r="H5" s="0">
+        <v>30</v>
+      </c>
       <c r="I5" s="0">
         <v>30</v>
       </c>
       <c r="J5" s="0">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K5" s="0">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L5" s="0">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="M5" s="0">
-        <v>2.5</v>
-      </c>
-      <c r="N5" s="0">
-        <v>1</v>
-      </c>
-      <c r="O5" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" s="0" t="s">
         <v>70</v>
       </c>
+      <c r="O5" s="0">
+        <v>30</v>
+      </c>
       <c r="P5" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="0">
         <v>0.3</v>
       </c>
     </row>
@@ -1504,31 +1510,31 @@
       <c r="G6" s="0" t="s">
         <v>75</v>
       </c>
+      <c r="H6" s="0">
+        <v>20</v>
+      </c>
       <c r="I6" s="0">
         <v>20</v>
       </c>
       <c r="J6" s="0">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K6" s="0">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L6" s="0">
+        <v>1</v>
+      </c>
+      <c r="M6" s="0">
         <v>3</v>
       </c>
-      <c r="M6" s="0">
-        <v>1</v>
-      </c>
-      <c r="N6" s="0">
-        <v>3</v>
-      </c>
-      <c r="O6" s="0" t="s">
+      <c r="N6" s="0" t="s">
         <v>76</v>
       </c>
+      <c r="O6" s="0">
+        <v>30</v>
+      </c>
       <c r="P6" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q6" s="0">
         <v>0.3</v>
       </c>
     </row>
@@ -1554,31 +1560,31 @@
       <c r="G7" s="0" t="s">
         <v>81</v>
       </c>
+      <c r="H7" s="0">
+        <v>3</v>
+      </c>
       <c r="I7" s="0">
         <v>3</v>
       </c>
       <c r="J7" s="0">
+        <v>50</v>
+      </c>
+      <c r="K7" s="0">
+        <v>1</v>
+      </c>
+      <c r="L7" s="0">
         <v>3</v>
       </c>
-      <c r="K7" s="0">
-        <v>50</v>
-      </c>
-      <c r="L7" s="0">
-        <v>1</v>
-      </c>
       <c r="M7" s="0">
-        <v>3</v>
-      </c>
-      <c r="N7" s="0">
-        <v>1</v>
-      </c>
-      <c r="O7" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" s="0" t="s">
         <v>82</v>
       </c>
+      <c r="O7" s="0">
+        <v>30</v>
+      </c>
       <c r="P7" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q7" s="0">
         <v>0.3</v>
       </c>
     </row>
@@ -1604,14 +1610,17 @@
       <c r="G8" s="0" t="s">
         <v>87</v>
       </c>
+      <c r="H8" s="0">
+        <v>30</v>
+      </c>
       <c r="I8" s="0">
         <v>30</v>
       </c>
       <c r="J8" s="0">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K8" s="0">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L8" s="0">
         <v>1</v>
@@ -1619,16 +1628,13 @@
       <c r="M8" s="0">
         <v>1</v>
       </c>
-      <c r="N8" s="0">
-        <v>1</v>
-      </c>
-      <c r="O8" s="0" t="s">
+      <c r="N8" s="0" t="s">
         <v>88</v>
       </c>
+      <c r="O8" s="0">
+        <v>30</v>
+      </c>
       <c r="P8" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q8" s="0">
         <v>0.3</v>
       </c>
     </row>
@@ -1652,38 +1658,38 @@
       <c r="G9" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="0" t="s">
-        <v>117</v>
+      <c r="H9" s="0">
+        <v>10</v>
       </c>
       <c r="I9" s="0">
         <v>10</v>
       </c>
       <c r="J9" s="0">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="K9" s="0">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L9" s="0">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M9" s="0">
-        <v>0.1</v>
-      </c>
-      <c r="N9" s="0">
-        <v>0</v>
-      </c>
-      <c r="O9" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="N9" s="0" t="s">
         <v>52</v>
       </c>
+      <c r="O9" s="0">
+        <v>30</v>
+      </c>
       <c r="P9" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q9" s="0">
         <v>0.3</v>
       </c>
-      <c r="R9" s="0" t="s">
+      <c r="Q9" s="0" t="s">
         <v>103</v>
+      </c>
+      <c r="R9" s="0">
+        <v>50001</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.55">
@@ -1706,34 +1712,34 @@
       <c r="G10" s="0" t="s">
         <v>57</v>
       </c>
+      <c r="H10" s="0">
+        <v>10</v>
+      </c>
       <c r="I10" s="0">
         <v>10</v>
       </c>
       <c r="J10" s="0">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K10" s="0">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L10" s="0">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M10" s="0">
-        <v>0.1</v>
-      </c>
-      <c r="N10" s="0">
-        <v>0</v>
-      </c>
-      <c r="O10" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="N10" s="0" t="s">
         <v>58</v>
       </c>
+      <c r="O10" s="0">
+        <v>30</v>
+      </c>
       <c r="P10" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q10" s="0">
         <v>0.3</v>
       </c>
-      <c r="R10" s="0" t="s">
+      <c r="Q10" s="0" t="s">
         <v>104</v>
       </c>
     </row>
@@ -1757,34 +1763,34 @@
       <c r="G11" s="0" t="s">
         <v>63</v>
       </c>
+      <c r="H11" s="0">
+        <v>10</v>
+      </c>
       <c r="I11" s="0">
         <v>10</v>
       </c>
       <c r="J11" s="0">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K11" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L11" s="0">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M11" s="0">
-        <v>0.5</v>
-      </c>
-      <c r="N11" s="0">
-        <v>0</v>
-      </c>
-      <c r="O11" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="N11" s="0" t="s">
         <v>64</v>
       </c>
+      <c r="O11" s="0">
+        <v>30</v>
+      </c>
       <c r="P11" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q11" s="0">
         <v>0.3</v>
       </c>
-      <c r="R11" s="0" t="s">
+      <c r="Q11" s="0" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1808,34 +1814,34 @@
       <c r="G12" s="0" t="s">
         <v>69</v>
       </c>
+      <c r="H12" s="0">
+        <v>30</v>
+      </c>
       <c r="I12" s="0">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J12" s="0">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="K12" s="0">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="L12" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12" s="0">
-        <v>3</v>
-      </c>
-      <c r="N12" s="0">
-        <v>0</v>
-      </c>
-      <c r="O12" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="N12" s="0" t="s">
         <v>70</v>
       </c>
+      <c r="O12" s="0">
+        <v>30</v>
+      </c>
       <c r="P12" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q12" s="0">
         <v>0.3</v>
       </c>
-      <c r="R12" s="0" t="s">
+      <c r="Q12" s="0" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1859,38 +1865,38 @@
       <c r="G13" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="H13" s="0" t="s">
-        <v>118</v>
+      <c r="H13" s="0">
+        <v>10</v>
       </c>
       <c r="I13" s="0">
         <v>10</v>
       </c>
       <c r="J13" s="0">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="K13" s="0">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="L13" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M13" s="0">
-        <v>5</v>
-      </c>
-      <c r="N13" s="0">
-        <v>0</v>
-      </c>
-      <c r="O13" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="N13" s="0" t="s">
         <v>76</v>
       </c>
+      <c r="O13" s="0">
+        <v>30</v>
+      </c>
       <c r="P13" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q13" s="0">
         <v>0.3</v>
       </c>
-      <c r="R13" s="0" t="s">
+      <c r="Q13" s="0" t="s">
         <v>107</v>
+      </c>
+      <c r="R13" s="0">
+        <v>50005</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.55">
@@ -1913,38 +1919,38 @@
       <c r="G14" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="H14" s="0" t="s">
-        <v>119</v>
+      <c r="H14" s="0">
+        <v>10</v>
       </c>
       <c r="I14" s="0">
         <v>10</v>
       </c>
       <c r="J14" s="0">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="K14" s="0">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="L14" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M14" s="0">
-        <v>3</v>
-      </c>
-      <c r="N14" s="0">
-        <v>0</v>
-      </c>
-      <c r="O14" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="N14" s="0" t="s">
         <v>82</v>
       </c>
+      <c r="O14" s="0">
+        <v>30</v>
+      </c>
       <c r="P14" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q14" s="0">
         <v>0.3</v>
       </c>
-      <c r="R14" s="0" t="s">
+      <c r="Q14" s="0" t="s">
         <v>108</v>
+      </c>
+      <c r="R14" s="0">
+        <v>50006</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.55">
@@ -1967,34 +1973,34 @@
       <c r="G15" s="0" t="s">
         <v>87</v>
       </c>
+      <c r="H15" s="0">
+        <v>10</v>
+      </c>
       <c r="I15" s="0">
         <v>10</v>
       </c>
       <c r="J15" s="0">
-        <v>10</v>
+        <v>600</v>
       </c>
       <c r="K15" s="0">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="L15" s="0">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M15" s="0">
-        <v>1.5</v>
-      </c>
-      <c r="N15" s="0">
-        <v>0</v>
-      </c>
-      <c r="O15" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="N15" s="0" t="s">
         <v>88</v>
       </c>
+      <c r="O15" s="0">
+        <v>30</v>
+      </c>
       <c r="P15" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q15" s="0">
         <v>0.3</v>
       </c>
-      <c r="R15" s="0" t="s">
+      <c r="Q15" s="0" t="s">
         <v>109</v>
       </c>
     </row>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="train_data" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="119">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -45,9 +45,6 @@
     <t xml:space="preserve">icon_id</t>
   </si>
   <si>
-    <t xml:space="preserve">train_skill_data_id</t>
-  </si>
-  <si>
     <t xml:space="preserve">20001</t>
   </si>
   <si>
@@ -123,42 +120,24 @@
     <t xml:space="preserve">ColdAirProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">41001</t>
-  </si>
-  <si>
     <t xml:space="preserve">엘리트 폭발 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">EliteExplosionRangeTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">50008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41002</t>
-  </si>
-  <si>
     <t xml:space="preserve">엘리트 냉기 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">EliteColdAirRangeTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">50009</t>
-  </si>
-  <si>
     <t xml:space="preserve">42001</t>
   </si>
   <si>
-    <t xml:space="preserve">60008</t>
-  </si>
-  <si>
     <t xml:space="preserve">42002</t>
   </si>
   <si>
-    <t xml:space="preserve">60009</t>
-  </si>
-  <si>
     <t xml:space="preserve">target_count</t>
   </si>
   <si>
@@ -336,24 +315,6 @@
     <t xml:space="preserve">60001</t>
   </si>
   <si>
-    <t xml:space="preserve">60002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60007</t>
-  </si>
-  <si>
     <t xml:space="preserve">31001</t>
   </si>
   <si>
@@ -375,16 +336,63 @@
     <t xml:space="preserve">31007</t>
   </si>
   <si>
-    <t xml:space="preserve">50001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006</t>
-  </si>
-  <si>
     <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">60011;60012;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50002;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -392,7 +400,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -401,6 +409,13 @@
     <font>
       <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -427,40 +442,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF94A5DF"/>
-          <bgColor rgb="FF94A5DF"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color rgb="FF6182D6"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF6182D6"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFAEBFEA"/>
-          <bgColor rgb="FFAEBFEA"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -495,12 +489,10 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="5">
-      <tableStyleElement type="firstColumn" dxfId="4"/>
-      <tableStyleElement type="lastColumn" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="3">
+      <tableStyleElement type="firstColumn" dxfId="2"/>
+      <tableStyleElement type="lastColumn" dxfId="1"/>
+      <tableStyleElement type="firstRowStripe"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0"/>
   </tableStyles>
@@ -809,7 +801,7 @@
     <col min="3" max="3" width="24.140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
@@ -832,21 +824,21 @@
         <v>6</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="C2" s="0" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>10</v>
       </c>
       <c r="D2" s="0">
         <v>250</v>
@@ -855,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -870,7 +862,7 @@
   <sheetPr codeName="Sheet2">
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="0"/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -878,6 +870,8 @@
     <col min="6" max="6" width="24.2109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.35546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.55">
@@ -903,45 +897,45 @@
         <v>6</v>
       </c>
       <c r="H1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="J1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="K1" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="L1" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="M1" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="N1" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="O1" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="P1" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="0" t="s">
-        <v>20</v>
-      </c>
       <c r="Q1" s="0" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.55">
       <c r="A2" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="C2" s="0" t="s">
         <v>22</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>23</v>
       </c>
       <c r="D2" s="0">
         <v>250</v>
@@ -950,10 +944,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="0" t="s">
         <v>24</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>25</v>
       </c>
       <c r="H2" s="0">
         <v>5</v>
@@ -971,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" s="0">
         <v>30</v>
@@ -982,13 +976,13 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.55">
       <c r="A3" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="C3" s="0" t="s">
         <v>28</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>29</v>
       </c>
       <c r="D3" s="0">
         <v>250</v>
@@ -997,10 +991,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H3" s="0">
         <v>5</v>
@@ -1018,7 +1012,7 @@
         <v>0.1</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N3" s="0">
         <v>30</v>
@@ -1029,10 +1023,10 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.55">
       <c r="A4" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D4" s="0">
         <v>150</v>
@@ -1041,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H4" s="0">
         <v>8</v>
@@ -1059,7 +1053,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N4" s="0">
         <v>30</v>
@@ -1067,8 +1061,11 @@
       <c r="O4" s="0">
         <v>0.3</v>
       </c>
-      <c r="Q4" s="0">
-        <v>50008</v>
+      <c r="P4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.55">
@@ -1076,7 +1073,7 @@
         <v>37</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D5" s="0">
         <v>150</v>
@@ -1085,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H5" s="0">
         <v>13</v>
@@ -1103,7 +1100,7 @@
         <v>0.1</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N5" s="0">
         <v>30</v>
@@ -1111,102 +1108,11 @@
       <c r="O5" s="0">
         <v>0.3</v>
       </c>
-      <c r="Q5" s="0">
-        <v>50009</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.55">
-      <c r="A6" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="0">
-        <v>150</v>
-      </c>
-      <c r="E6" s="0">
-        <v>0</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="0">
-        <v>8</v>
-      </c>
-      <c r="I6" s="0">
-        <v>8</v>
-      </c>
-      <c r="J6" s="0">
-        <v>500</v>
-      </c>
-      <c r="K6" s="0">
-        <v>1</v>
-      </c>
-      <c r="L6" s="0">
-        <v>4</v>
-      </c>
-      <c r="M6" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="0">
-        <v>30</v>
-      </c>
-      <c r="O6" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="P6" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" s="0">
-        <v>50008</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.55">
-      <c r="A7" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="0">
-        <v>150</v>
-      </c>
-      <c r="E7" s="0">
-        <v>0</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="0">
-        <v>13</v>
-      </c>
-      <c r="I7" s="0">
-        <v>13</v>
-      </c>
-      <c r="J7" s="0">
-        <v>15</v>
-      </c>
-      <c r="K7" s="0">
-        <v>1</v>
-      </c>
-      <c r="L7" s="0">
-        <v>0.1</v>
-      </c>
-      <c r="M7" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7" s="0">
-        <v>30</v>
-      </c>
-      <c r="O7" s="0">
-        <v>0.3</v>
-      </c>
-      <c r="P7" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q7" s="0">
-        <v>50009</v>
+      <c r="P5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1230,6 +1136,9 @@
     <col min="7" max="7" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.2109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.55">
@@ -1255,48 +1164,48 @@
         <v>6</v>
       </c>
       <c r="H1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="J1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="K1" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="L1" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="0" t="s">
-        <v>16</v>
-      </c>
       <c r="M1" s="0" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O1" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="Q1" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="0" t="s">
-        <v>20</v>
-      </c>
       <c r="R1" s="0" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A2" s="0" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D2" s="0">
         <v>250</v>
@@ -1305,10 +1214,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H2" s="0">
         <v>10</v>
@@ -1329,7 +1238,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="O2" s="0">
         <v>30</v>
@@ -1340,13 +1249,13 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A3" s="0" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D3" s="0">
         <v>250</v>
@@ -1355,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H3" s="0">
         <v>8</v>
@@ -1379,7 +1288,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="0" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="O3" s="0">
         <v>30</v>
@@ -1390,13 +1299,13 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A4" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D4" s="0">
         <v>250</v>
@@ -1405,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H4" s="0">
         <v>10</v>
@@ -1429,7 +1338,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="O4" s="0">
         <v>30</v>
@@ -1440,13 +1349,13 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A5" s="0" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D5" s="0">
         <v>250</v>
@@ -1455,10 +1364,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H5" s="0">
         <v>30</v>
@@ -1479,7 +1388,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="O5" s="0">
         <v>30</v>
@@ -1490,13 +1399,13 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A6" s="0" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D6" s="0">
         <v>250</v>
@@ -1505,10 +1414,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H6" s="0">
         <v>20</v>
@@ -1529,7 +1438,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="O6" s="0">
         <v>30</v>
@@ -1540,13 +1449,13 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A7" s="0" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D7" s="0">
         <v>250</v>
@@ -1555,10 +1464,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H7" s="0">
         <v>3</v>
@@ -1579,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="0" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="O7" s="0">
         <v>30</v>
@@ -1590,13 +1499,13 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A8" s="0" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D8" s="0">
         <v>250</v>
@@ -1605,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H8" s="0">
         <v>30</v>
@@ -1629,7 +1538,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="0" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="O8" s="0">
         <v>30</v>
@@ -1640,10 +1549,10 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A9" s="0" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C9" s="0"/>
       <c r="D9" s="0">
@@ -1653,10 +1562,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H9" s="0">
         <v>10</v>
@@ -1677,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="0" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="O9" s="0">
         <v>30</v>
@@ -1686,18 +1595,18 @@
         <v>0.3</v>
       </c>
       <c r="Q9" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="R9" s="0">
-        <v>50001</v>
+        <v>96</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A10" s="0" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C10" s="0"/>
       <c r="D10" s="0">
@@ -1707,10 +1616,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H10" s="0">
         <v>10</v>
@@ -1731,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="0" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="O10" s="0">
         <v>30</v>
@@ -1739,16 +1648,19 @@
       <c r="P10" s="0">
         <v>0.3</v>
       </c>
-      <c r="Q10" s="0" t="s">
-        <v>104</v>
+      <c r="Q10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A11" s="0" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C11" s="0"/>
       <c r="D11" s="0">
@@ -1758,10 +1670,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H11" s="0">
         <v>10</v>
@@ -1782,7 +1694,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="0" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="O11" s="0">
         <v>30</v>
@@ -1790,16 +1702,16 @@
       <c r="P11" s="0">
         <v>0.3</v>
       </c>
-      <c r="Q11" s="0" t="s">
-        <v>105</v>
+      <c r="Q11" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A12" s="0" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C12" s="0"/>
       <c r="D12" s="0">
@@ -1809,10 +1721,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H12" s="0">
         <v>30</v>
@@ -1833,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="0" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="O12" s="0">
         <v>30</v>
@@ -1841,16 +1753,16 @@
       <c r="P12" s="0">
         <v>0.3</v>
       </c>
-      <c r="Q12" s="0" t="s">
-        <v>106</v>
+      <c r="Q12" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A13" s="0" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C13" s="0"/>
       <c r="D13" s="0">
@@ -1860,10 +1772,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H13" s="0">
         <v>10</v>
@@ -1884,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="0" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="O13" s="0">
         <v>30</v>
@@ -1892,19 +1804,19 @@
       <c r="P13" s="0">
         <v>0.3</v>
       </c>
-      <c r="Q13" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="R13" s="0">
-        <v>50005</v>
+      <c r="Q13" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A14" s="0" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C14" s="0"/>
       <c r="D14" s="0">
@@ -1914,10 +1826,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H14" s="0">
         <v>10</v>
@@ -1938,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="0" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="O14" s="0">
         <v>30</v>
@@ -1946,19 +1858,19 @@
       <c r="P14" s="0">
         <v>0.3</v>
       </c>
-      <c r="Q14" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="R14" s="0">
-        <v>50006</v>
+      <c r="Q14" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.55">
       <c r="A15" s="0" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C15" s="0"/>
       <c r="D15" s="0">
@@ -1968,10 +1880,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H15" s="0">
         <v>10</v>
@@ -1992,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="0" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="O15" s="0">
         <v>30</v>
@@ -2000,8 +1912,8 @@
       <c r="P15" s="0">
         <v>0.3</v>
       </c>
-      <c r="Q15" s="0" t="s">
-        <v>109</v>
+      <c r="Q15" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="119">
   <si>
     <t xml:space="preserve">id</t>
   </si>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -3,403 +3,408 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\02_Resources\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14512B00-9693-4695-8B6B-E22D66C0B75C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="2"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="train_data" sheetId="1" r:id="rId1"/>
     <sheet name="range_train_data" sheetId="2" r:id="rId2"/>
     <sheet name="turret_train_data" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr/>
-  <fileRecoveryPr autoRecover="0" crashSave="0" dataExtractLoad="0" repairLoad="0"/>
+  <calcPr calcId="0"/>
+  <fileRecoveryPr autoRecover="0"/>
   <extLst>
-    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="119">
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기본 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적이 가장 많은 곳으로 위치해 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 통시에 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="119">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>train_name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>max_hp</t>
+  </si>
+  <si>
+    <t>is_main_train</t>
+  </si>
+  <si>
+    <t>prefab_id</t>
+  </si>
+  <si>
+    <t>icon_id</t>
+  </si>
+  <si>
+    <t>20001</t>
+  </si>
+  <si>
+    <t>기본 기차</t>
+  </si>
+  <si>
+    <t>가장 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t>MainTrain</t>
+  </si>
+  <si>
+    <t>attack_range</t>
+  </si>
+  <si>
+    <t>attack_area</t>
+  </si>
+  <si>
+    <t>attack_damage</t>
+  </si>
+  <si>
+    <t>attack_count</t>
+  </si>
+  <si>
+    <t>attack_interval</t>
+  </si>
+  <si>
+    <t>range_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t>critical_chance</t>
+  </si>
+  <si>
+    <t>critical_damage</t>
+  </si>
+  <si>
+    <t>passive_skill_data_id</t>
+  </si>
+  <si>
+    <t>40001</t>
+  </si>
+  <si>
+    <t>폭발 포탑</t>
+  </si>
+  <si>
+    <t>적이 가장 많은 곳으로 위치해 피해를 준다.</t>
+  </si>
+  <si>
+    <t>ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t>현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t>ExplosionProjectile</t>
+  </si>
+  <si>
+    <t>40002</t>
+  </si>
+  <si>
+    <t>냉기 포탑</t>
+  </si>
+  <si>
+    <t>적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
+  </si>
+  <si>
+    <t>ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t>현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t>ColdAirProjectile</t>
+  </si>
+  <si>
+    <t>엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t>EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t>엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t>EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t>42001</t>
+  </si>
+  <si>
+    <t>42002</t>
+  </si>
+  <si>
+    <t>target_count</t>
+  </si>
+  <si>
+    <t>turret_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t>30001</t>
+  </si>
+  <si>
+    <t>기관총 포탑</t>
+  </si>
+  <si>
+    <t>기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t>NormalTurretTrain</t>
+  </si>
+  <si>
+    <t>Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t>NormalProjectile</t>
+  </si>
+  <si>
+    <t>30002</t>
+  </si>
+  <si>
+    <t>화염 포탑</t>
+  </si>
+  <si>
+    <t>화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t>FireTurretTrain</t>
+  </si>
+  <si>
+    <t>Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t>FireEffectProjectile</t>
+  </si>
+  <si>
+    <t>30003</t>
+  </si>
+  <si>
+    <t>미사일 포탑</t>
+  </si>
+  <si>
+    <t>미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t>MissileTurretTrain</t>
+  </si>
+  <si>
+    <t>Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t>MissileProjectile</t>
+  </si>
+  <si>
+    <t>30004</t>
+  </si>
+  <si>
+    <t>레이저 포탑</t>
+  </si>
+  <si>
+    <t>레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
+  </si>
+  <si>
+    <t>LaserTurretTrain</t>
+  </si>
+  <si>
+    <t>Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t>LaserProjectile</t>
+  </si>
+  <si>
+    <t>30005</t>
+  </si>
+  <si>
+    <t>전기 포탑</t>
+  </si>
+  <si>
+    <t>화면에 있는 다수의 적들을 통시에 공격한다.</t>
+  </si>
+  <si>
+    <t>ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t>Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t>ElectrickProjectile</t>
+  </si>
+  <si>
+    <t>30006</t>
+  </si>
+  <si>
+    <t>포격 포탑</t>
+  </si>
+  <si>
+    <t>거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
+  </si>
+  <si>
+    <t>CannonTurretTrain</t>
+  </si>
+  <si>
+    <t>Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t>CannonProjectile</t>
+  </si>
+  <si>
+    <t>30007</t>
+  </si>
+  <si>
+    <t>저격 포탑</t>
+  </si>
+  <si>
+    <t>저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
+  </si>
+  <si>
+    <t>SniperTurretTrain</t>
+  </si>
+  <si>
+    <t>Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t>SniperProjectile</t>
+  </si>
+  <si>
+    <t>엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t>EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t>엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t>EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t>엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t>EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t>엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t>EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t>엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t>EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t>엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t>EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t>엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t>EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t>60001</t>
+  </si>
+  <si>
+    <t>31001</t>
+  </si>
+  <si>
+    <t>31002</t>
+  </si>
+  <si>
+    <t>31003</t>
+  </si>
+  <si>
+    <t>31004</t>
+  </si>
+  <si>
+    <t>31005</t>
+  </si>
+  <si>
+    <t>31006</t>
+  </si>
+  <si>
+    <t>31007</t>
+  </si>
+  <si>
+    <t>active_skill_data_id</t>
+  </si>
+  <si>
+    <t>60004;60005;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">60006;60007;</t>
+    <t>60006;60007;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">60002;60003;</t>
+    <t>60002;60003;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
+    <t>60008;60009;60010;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">60011;60012;</t>
+    <t>60011;60012;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">60013;</t>
+    <t>60013;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">60014;60015;</t>
+    <t>60014;60015;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">60016;60017;60018</t>
+    <t>60016;60017;60018</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">50001;</t>
+    <t>50001;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">50002;</t>
+    <t>50002;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">50003;</t>
+    <t>50003;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">50004;</t>
+    <t>50004;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">50005;</t>
+    <t>50005;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">50006;</t>
+    <t>50006;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -454,23 +459,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF94A5DF"/>
-          <bgColor rgb="FF94A5DF"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color rgb="FF6182D6"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF6182D6"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -489,19 +478,18 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="3">
-      <tableStyleElement type="firstColumn" dxfId="2"/>
-      <tableStyleElement type="lastColumn" dxfId="1"/>
-      <tableStyleElement type="firstRowStripe"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="firstColumn" dxfId="1"/>
+      <tableStyleElement type="lastColumn" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}"/>
   </tableStyles>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -728,7 +716,7 @@
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
-          <a:sp3d prstMaterial="warmMatte">
+          <a:sp3d>
             <a:bevelT w="63500" h="25400"/>
           </a:sp3d>
         </a:effectStyle>
@@ -791,79 +779,79 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="0"/>
+    <outlinePr summaryBelow="0" summaryRight="0" showOutlineSymbols="0"/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="24.140625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>250</v>
       </c>
-      <c r="E2" s="0">
-        <v>1</v>
-      </c>
-      <c r="F2" s="0" t="s">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="0"/>
+    <outlinePr summaryBelow="0" summaryRight="0" showOutlineSymbols="0"/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.5703125" bestFit="1" customWidth="1"/>
@@ -874,191 +862,191 @@
     <col min="17" max="17" width="17.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.55">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>250</v>
       </c>
-      <c r="E2" s="0">
-        <v>0</v>
-      </c>
-      <c r="F2" s="0" t="s">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="0">
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="I2" s="0">
+      <c r="I2">
         <v>5</v>
       </c>
-      <c r="J2" s="0">
+      <c r="J2">
         <v>50</v>
       </c>
-      <c r="K2" s="0">
-        <v>1</v>
-      </c>
-      <c r="L2" s="0">
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>4</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="0">
-        <v>30</v>
-      </c>
-      <c r="O2" s="0">
+      <c r="N2">
+        <v>30</v>
+      </c>
+      <c r="O2">
         <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.55">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>250</v>
       </c>
-      <c r="E3" s="0">
-        <v>0</v>
-      </c>
-      <c r="F3" s="0" t="s">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="0">
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3">
         <v>5</v>
       </c>
-      <c r="I3" s="0">
+      <c r="I3">
         <v>5</v>
       </c>
-      <c r="J3" s="0">
-        <v>1</v>
-      </c>
-      <c r="K3" s="0">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0">
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
         <v>0.1</v>
       </c>
-      <c r="M3" s="0" t="s">
+      <c r="M3" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="0">
-        <v>30</v>
-      </c>
-      <c r="O3" s="0">
+      <c r="N3">
+        <v>30</v>
+      </c>
+      <c r="O3">
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.55">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>150</v>
       </c>
-      <c r="E4" s="0">
-        <v>0</v>
-      </c>
-      <c r="F4" s="0" t="s">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="0">
+      <c r="H4">
         <v>8</v>
       </c>
-      <c r="I4" s="0">
+      <c r="I4">
         <v>8</v>
       </c>
-      <c r="J4" s="0">
+      <c r="J4">
         <v>500</v>
       </c>
-      <c r="K4" s="0">
-        <v>1</v>
-      </c>
-      <c r="L4" s="0">
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>4</v>
       </c>
-      <c r="M4" s="0" t="s">
+      <c r="M4" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="0">
-        <v>30</v>
-      </c>
-      <c r="O4" s="0">
+      <c r="N4">
+        <v>30</v>
+      </c>
+      <c r="O4">
         <v>0.3</v>
       </c>
       <c r="P4" s="2" t="s">
@@ -1068,44 +1056,44 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.55">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>150</v>
       </c>
-      <c r="E5" s="0">
-        <v>0</v>
-      </c>
-      <c r="F5" s="0" t="s">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="0">
+      <c r="H5">
         <v>13</v>
       </c>
-      <c r="I5" s="0">
+      <c r="I5">
         <v>13</v>
       </c>
-      <c r="J5" s="0">
+      <c r="J5">
         <v>15</v>
       </c>
-      <c r="K5" s="0">
-        <v>1</v>
-      </c>
-      <c r="L5" s="0">
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
         <v>0.1</v>
       </c>
-      <c r="M5" s="0" t="s">
+      <c r="M5" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="0">
-        <v>30</v>
-      </c>
-      <c r="O5" s="0">
+      <c r="N5">
+        <v>30</v>
+      </c>
+      <c r="O5">
         <v>0.3</v>
       </c>
       <c r="P5" s="2" t="s">
@@ -1117,18 +1105,18 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="0"/>
+    <outlinePr summaryBelow="0" summaryRight="0" showOutlineSymbols="0"/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <dimension ref="A1:R15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="81.2109375" style="1" bestFit="1" customWidth="1"/>
@@ -1141,511 +1129,511 @@
     <col min="18" max="18" width="17.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" s="0" t="s">
+      <c r="Q1" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="0" t="s">
+      <c r="R1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>250</v>
       </c>
-      <c r="E2" s="0">
-        <v>0</v>
-      </c>
-      <c r="F2" s="0" t="s">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="0">
+      <c r="H2">
         <v>10</v>
       </c>
-      <c r="I2" s="0">
+      <c r="I2">
         <v>10</v>
       </c>
-      <c r="J2" s="0">
+      <c r="J2">
         <v>10</v>
       </c>
-      <c r="K2" s="0">
-        <v>1</v>
-      </c>
-      <c r="L2" s="0">
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>0.3</v>
       </c>
-      <c r="M2" s="0">
-        <v>1</v>
-      </c>
-      <c r="N2" s="0" t="s">
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
         <v>45</v>
       </c>
-      <c r="O2" s="0">
-        <v>30</v>
-      </c>
-      <c r="P2" s="0">
+      <c r="O2">
+        <v>30</v>
+      </c>
+      <c r="P2">
         <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>250</v>
       </c>
-      <c r="E3" s="0">
-        <v>0</v>
-      </c>
-      <c r="F3" s="0" t="s">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="0">
+      <c r="H3">
         <v>8</v>
       </c>
-      <c r="I3" s="0">
+      <c r="I3">
         <v>8</v>
       </c>
-      <c r="J3" s="0">
+      <c r="J3">
         <v>4</v>
       </c>
-      <c r="K3" s="0">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0">
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
         <v>0.15</v>
       </c>
-      <c r="M3" s="0">
-        <v>1</v>
-      </c>
-      <c r="N3" s="0" t="s">
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
         <v>51</v>
       </c>
-      <c r="O3" s="0">
-        <v>30</v>
-      </c>
-      <c r="P3" s="0">
+      <c r="O3">
+        <v>30</v>
+      </c>
+      <c r="P3">
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>250</v>
       </c>
-      <c r="E4" s="0">
-        <v>0</v>
-      </c>
-      <c r="F4" s="0" t="s">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="0">
+      <c r="H4">
         <v>10</v>
       </c>
-      <c r="I4" s="0">
+      <c r="I4">
         <v>10</v>
       </c>
-      <c r="J4" s="0">
+      <c r="J4">
         <v>25</v>
       </c>
-      <c r="K4" s="0">
-        <v>1</v>
-      </c>
-      <c r="L4" s="0">
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1.25</v>
       </c>
-      <c r="M4" s="0">
-        <v>1</v>
-      </c>
-      <c r="N4" s="0" t="s">
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="0">
-        <v>30</v>
-      </c>
-      <c r="P4" s="0">
+      <c r="O4">
+        <v>30</v>
+      </c>
+      <c r="P4">
         <v>0.3</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>250</v>
       </c>
-      <c r="E5" s="0">
-        <v>0</v>
-      </c>
-      <c r="F5" s="0" t="s">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" t="s">
         <v>62</v>
       </c>
-      <c r="H5" s="0">
-        <v>30</v>
-      </c>
-      <c r="I5" s="0">
-        <v>30</v>
-      </c>
-      <c r="J5" s="0">
+      <c r="H5">
+        <v>30</v>
+      </c>
+      <c r="I5">
+        <v>30</v>
+      </c>
+      <c r="J5">
         <v>50</v>
       </c>
-      <c r="K5" s="0">
-        <v>1</v>
-      </c>
-      <c r="L5" s="0">
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
         <v>2.5</v>
       </c>
-      <c r="M5" s="0">
-        <v>1</v>
-      </c>
-      <c r="N5" s="0" t="s">
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5" t="s">
         <v>63</v>
       </c>
-      <c r="O5" s="0">
-        <v>30</v>
-      </c>
-      <c r="P5" s="0">
+      <c r="O5">
+        <v>30</v>
+      </c>
+      <c r="P5">
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="0">
+      <c r="D6">
         <v>250</v>
       </c>
-      <c r="E6" s="0">
-        <v>0</v>
-      </c>
-      <c r="F6" s="0" t="s">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
         <v>67</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="0">
+      <c r="H6">
         <v>20</v>
       </c>
-      <c r="I6" s="0">
+      <c r="I6">
         <v>20</v>
       </c>
-      <c r="J6" s="0">
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="K6" s="0">
+      <c r="K6">
         <v>3</v>
       </c>
-      <c r="L6" s="0">
-        <v>1</v>
-      </c>
-      <c r="M6" s="0">
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
         <v>3</v>
       </c>
-      <c r="N6" s="0" t="s">
+      <c r="N6" t="s">
         <v>69</v>
       </c>
-      <c r="O6" s="0">
-        <v>30</v>
-      </c>
-      <c r="P6" s="0">
+      <c r="O6">
+        <v>30</v>
+      </c>
+      <c r="P6">
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7">
         <v>250</v>
       </c>
-      <c r="E7" s="0">
-        <v>0</v>
-      </c>
-      <c r="F7" s="0" t="s">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="0">
+      <c r="H7">
         <v>3</v>
       </c>
-      <c r="I7" s="0">
+      <c r="I7">
         <v>3</v>
       </c>
-      <c r="J7" s="0">
+      <c r="J7">
         <v>50</v>
       </c>
-      <c r="K7" s="0">
-        <v>1</v>
-      </c>
-      <c r="L7" s="0">
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
         <v>3</v>
       </c>
-      <c r="M7" s="0">
-        <v>1</v>
-      </c>
-      <c r="N7" s="0" t="s">
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7" t="s">
         <v>75</v>
       </c>
-      <c r="O7" s="0">
-        <v>30</v>
-      </c>
-      <c r="P7" s="0">
+      <c r="O7">
+        <v>30</v>
+      </c>
+      <c r="P7">
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>250</v>
       </c>
-      <c r="E8" s="0">
-        <v>0</v>
-      </c>
-      <c r="F8" s="0" t="s">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="0">
-        <v>30</v>
-      </c>
-      <c r="I8" s="0">
-        <v>30</v>
-      </c>
-      <c r="J8" s="0">
+      <c r="H8">
+        <v>30</v>
+      </c>
+      <c r="I8">
+        <v>30</v>
+      </c>
+      <c r="J8">
         <v>50</v>
       </c>
-      <c r="K8" s="0">
-        <v>1</v>
-      </c>
-      <c r="L8" s="0">
-        <v>1</v>
-      </c>
-      <c r="M8" s="0">
-        <v>1</v>
-      </c>
-      <c r="N8" s="0" t="s">
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8" t="s">
         <v>81</v>
       </c>
-      <c r="O8" s="0">
-        <v>30</v>
-      </c>
-      <c r="P8" s="0">
+      <c r="O8">
+        <v>30</v>
+      </c>
+      <c r="P8">
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="0"/>
-      <c r="D9" s="0">
+      <c r="C9"/>
+      <c r="D9">
         <v>150</v>
       </c>
-      <c r="E9" s="0">
-        <v>0</v>
-      </c>
-      <c r="F9" s="0" t="s">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="0">
+      <c r="H9">
         <v>10</v>
       </c>
-      <c r="I9" s="0">
+      <c r="I9">
         <v>10</v>
       </c>
-      <c r="J9" s="0">
+      <c r="J9">
         <v>50</v>
       </c>
-      <c r="K9" s="0">
-        <v>1</v>
-      </c>
-      <c r="L9" s="0">
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
         <v>0.1</v>
       </c>
-      <c r="M9" s="0">
-        <v>0</v>
-      </c>
-      <c r="N9" s="0" t="s">
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
         <v>45</v>
       </c>
-      <c r="O9" s="0">
-        <v>30</v>
-      </c>
-      <c r="P9" s="0">
+      <c r="O9">
+        <v>30</v>
+      </c>
+      <c r="P9">
         <v>0.3</v>
       </c>
-      <c r="Q9" s="0" t="s">
+      <c r="Q9" t="s">
         <v>96</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="0"/>
-      <c r="D10" s="0">
+      <c r="C10"/>
+      <c r="D10">
         <v>150</v>
       </c>
-      <c r="E10" s="0">
-        <v>0</v>
-      </c>
-      <c r="F10" s="0" t="s">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="0">
+      <c r="H10">
         <v>10</v>
       </c>
-      <c r="I10" s="0">
+      <c r="I10">
         <v>10</v>
       </c>
-      <c r="J10" s="0">
+      <c r="J10">
         <v>25</v>
       </c>
-      <c r="K10" s="0">
-        <v>1</v>
-      </c>
-      <c r="L10" s="0">
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
         <v>0.1</v>
       </c>
-      <c r="M10" s="0">
-        <v>0</v>
-      </c>
-      <c r="N10" s="0" t="s">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
         <v>51</v>
       </c>
-      <c r="O10" s="0">
-        <v>30</v>
-      </c>
-      <c r="P10" s="0">
+      <c r="O10">
+        <v>30</v>
+      </c>
+      <c r="P10">
         <v>0.3</v>
       </c>
       <c r="Q10" s="2" t="s">
@@ -1655,153 +1643,153 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A11" s="0" t="s">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="0"/>
-      <c r="D11" s="0">
+      <c r="C11"/>
+      <c r="D11">
         <v>150</v>
       </c>
-      <c r="E11" s="0">
-        <v>0</v>
-      </c>
-      <c r="F11" s="0" t="s">
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="0">
+      <c r="H11">
         <v>10</v>
       </c>
-      <c r="I11" s="0">
+      <c r="I11">
         <v>10</v>
       </c>
-      <c r="J11" s="0">
+      <c r="J11">
         <v>100</v>
       </c>
-      <c r="K11" s="0">
-        <v>1</v>
-      </c>
-      <c r="L11" s="0">
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
         <v>0.5</v>
       </c>
-      <c r="M11" s="0">
-        <v>0</v>
-      </c>
-      <c r="N11" s="0" t="s">
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
         <v>57</v>
       </c>
-      <c r="O11" s="0">
-        <v>30</v>
-      </c>
-      <c r="P11" s="0">
+      <c r="O11">
+        <v>30</v>
+      </c>
+      <c r="P11">
         <v>0.3</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A12" s="0" t="s">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="0"/>
-      <c r="D12" s="0">
+      <c r="C12"/>
+      <c r="D12">
         <v>150</v>
       </c>
-      <c r="E12" s="0">
-        <v>0</v>
-      </c>
-      <c r="F12" s="0" t="s">
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
         <v>89</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" t="s">
         <v>62</v>
       </c>
-      <c r="H12" s="0">
-        <v>30</v>
-      </c>
-      <c r="I12" s="0">
+      <c r="H12">
+        <v>30</v>
+      </c>
+      <c r="I12">
         <v>10</v>
       </c>
-      <c r="J12" s="0">
+      <c r="J12">
         <v>300</v>
       </c>
-      <c r="K12" s="0">
-        <v>1</v>
-      </c>
-      <c r="L12" s="0">
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
         <v>3</v>
       </c>
-      <c r="M12" s="0">
-        <v>0</v>
-      </c>
-      <c r="N12" s="0" t="s">
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
         <v>63</v>
       </c>
-      <c r="O12" s="0">
-        <v>30</v>
-      </c>
-      <c r="P12" s="0">
+      <c r="O12">
+        <v>30</v>
+      </c>
+      <c r="P12">
         <v>0.3</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A13" s="0" t="s">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="0"/>
-      <c r="D13" s="0">
+      <c r="C13"/>
+      <c r="D13">
         <v>150</v>
       </c>
-      <c r="E13" s="0">
-        <v>0</v>
-      </c>
-      <c r="F13" s="0" t="s">
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
         <v>91</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" t="s">
         <v>68</v>
       </c>
-      <c r="H13" s="0">
+      <c r="H13">
         <v>10</v>
       </c>
-      <c r="I13" s="0">
+      <c r="I13">
         <v>10</v>
       </c>
-      <c r="J13" s="0">
+      <c r="J13">
         <v>400</v>
       </c>
-      <c r="K13" s="0">
-        <v>1</v>
-      </c>
-      <c r="L13" s="0">
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
         <v>5</v>
       </c>
-      <c r="M13" s="0">
-        <v>0</v>
-      </c>
-      <c r="N13" s="0" t="s">
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
         <v>69</v>
       </c>
-      <c r="O13" s="0">
-        <v>30</v>
-      </c>
-      <c r="P13" s="0">
+      <c r="O13">
+        <v>30</v>
+      </c>
+      <c r="P13">
         <v>0.3</v>
       </c>
       <c r="Q13" s="2" t="s">
@@ -1811,51 +1799,51 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A14" s="0" t="s">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="0"/>
-      <c r="D14" s="0">
+      <c r="C14"/>
+      <c r="D14">
         <v>150</v>
       </c>
-      <c r="E14" s="0">
-        <v>0</v>
-      </c>
-      <c r="F14" s="0" t="s">
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="G14" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="0">
+      <c r="H14">
         <v>10</v>
       </c>
-      <c r="I14" s="0">
+      <c r="I14">
         <v>10</v>
       </c>
-      <c r="J14" s="0">
+      <c r="J14">
         <v>400</v>
       </c>
-      <c r="K14" s="0">
-        <v>1</v>
-      </c>
-      <c r="L14" s="0">
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
         <v>3</v>
       </c>
-      <c r="M14" s="0">
-        <v>0</v>
-      </c>
-      <c r="N14" s="0" t="s">
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
         <v>75</v>
       </c>
-      <c r="O14" s="0">
-        <v>30</v>
-      </c>
-      <c r="P14" s="0">
+      <c r="O14">
+        <v>30</v>
+      </c>
+      <c r="P14">
         <v>0.3</v>
       </c>
       <c r="Q14" s="2" t="s">
@@ -1865,51 +1853,51 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55">
-      <c r="A15" s="0" t="s">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="0"/>
-      <c r="D15" s="0">
+      <c r="C15"/>
+      <c r="D15">
         <v>150</v>
       </c>
-      <c r="E15" s="0">
-        <v>0</v>
-      </c>
-      <c r="F15" s="0" t="s">
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="s">
         <v>95</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="G15" t="s">
         <v>80</v>
       </c>
-      <c r="H15" s="0">
+      <c r="H15">
         <v>10</v>
       </c>
-      <c r="I15" s="0">
+      <c r="I15">
         <v>10</v>
       </c>
-      <c r="J15" s="0">
+      <c r="J15">
         <v>600</v>
       </c>
-      <c r="K15" s="0">
-        <v>1</v>
-      </c>
-      <c r="L15" s="0">
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
         <v>1.5</v>
       </c>
-      <c r="M15" s="0">
-        <v>0</v>
-      </c>
-      <c r="N15" s="0" t="s">
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
         <v>81</v>
       </c>
-      <c r="O15" s="0">
-        <v>30</v>
-      </c>
-      <c r="P15" s="0">
+      <c r="O15">
+        <v>30</v>
+      </c>
+      <c r="P15">
         <v>0.3</v>
       </c>
       <c r="Q15" s="2" t="s">
@@ -1918,7 +1906,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092901" footer="0.30000001192092901"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -561,7 +561,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" ns1:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2">
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="0"/>
     <pageSetUpPr/>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="H5" s="0">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I5" s="0">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J5" s="0">
         <v>15</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -17,397 +17,397 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="131">
   <si>
+    <t xml:space="preserve">지속적인 범위 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">빠른 속도로 적에게 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일을 발사해 범위 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
+    <t xml:space="preserve">적으 관통하는 탄을 발사해 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
   </si>
   <si>
     <t xml:space="preserve">엘리트 미사일 포탑</t>
   </si>
   <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
     <t xml:space="preserve">엘리트 전기 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">MainTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">엘리트 저격 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
   </si>
   <si>
     <t xml:space="preserve">엘리트 포격 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기본 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 통시에 공격한다.</t>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 통시에 공격하고 기절 시킵니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저를 발사해 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 범위 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
   </si>
   <si>
     <t xml:space="preserve">turret_projectile_prefab_id</t>
   </si>
   <si>
+    <t xml:space="preserve">range_projectile_prefab_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">적이 가장 많은 곳으로 위치해 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
+    <t xml:space="preserve">거대한 미사일을 발사해 넓은 범위에 피해를 줍니다.</t>
   </si>
 </sst>
 </file>
@@ -549,15 +549,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -716,18 +708,17 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="2">
-      <tableStyleElement type="headerRow" size="1" dxfId="1"/>
-      <tableStyleElement type="totalRow" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="1">
+      <tableStyleElement type="headerRow" size="1"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
-      <tableStyleElement type="wholeTable" size="1" dxfId="2"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="7"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="6"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="5"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="3"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="4"/>
+      <tableStyleElement type="wholeTable" size="1" dxfId="1"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="6"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="5"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="4"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="3"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -1025,39 +1016,39 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="0" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="0" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>112</v>
+        <v>26</v>
       </c>
       <c r="D2" s="0">
         <v>250</v>
@@ -1066,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1088,66 +1079,66 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="0" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="H1" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="O1" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="O1" s="0" t="s">
-        <v>108</v>
-      </c>
       <c r="P1" s="0" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>125</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="0" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D2" s="0">
         <v>250</v>
@@ -1156,10 +1147,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="I2" s="0">
         <v>5</v>
@@ -1177,7 +1168,7 @@
         <v>4</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="O2" s="0">
         <v>30</v>
@@ -1188,13 +1179,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="0" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="D3" s="0">
         <v>250</v>
@@ -1203,10 +1194,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="I3" s="0">
         <v>5</v>
@@ -1224,7 +1215,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="N3" s="0" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O3" s="0">
         <v>30</v>
@@ -1235,13 +1226,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="0" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="D4" s="0">
         <v>150</v>
@@ -1250,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I4" s="0">
         <v>8</v>
@@ -1271,7 +1262,7 @@
         <v>4</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="O4" s="0">
         <v>30</v>
@@ -1280,18 +1271,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="0" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="D5" s="0">
         <v>150</v>
@@ -1300,10 +1291,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>126</v>
+        <v>6</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="I5" s="0">
         <v>13</v>
@@ -1321,7 +1312,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O5" s="0">
         <v>30</v>
@@ -1330,7 +1321,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1358,69 +1349,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="0" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>35</v>
+        <v>112</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="H1" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="P1" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="O1" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="P1" s="0" t="s">
-        <v>108</v>
-      </c>
       <c r="Q1" s="0" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>125</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="0" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="D2" s="0">
         <v>250</v>
@@ -1429,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="I2" s="0">
         <v>10</v>
@@ -1453,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="P2" s="0">
         <v>30</v>
@@ -1464,13 +1455,13 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="0" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D3" s="0">
         <v>250</v>
@@ -1479,10 +1470,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="I3" s="0">
         <v>8</v>
@@ -1503,7 +1494,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="0" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
       <c r="P3" s="0">
         <v>30</v>
@@ -1514,13 +1505,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="0" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D4" s="0">
         <v>250</v>
@@ -1529,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="I4" s="0">
         <v>10</v>
@@ -1553,7 +1544,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="0" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="P4" s="0">
         <v>30</v>
@@ -1564,13 +1555,13 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="0" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="D5" s="0">
         <v>250</v>
@@ -1579,10 +1570,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I5" s="0">
         <v>30</v>
@@ -1603,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="0" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="P5" s="0">
         <v>30</v>
@@ -1614,13 +1605,13 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="0" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D6" s="0">
         <v>250</v>
@@ -1629,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>128</v>
+        <v>11</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="I6" s="0">
         <v>20</v>
@@ -1653,7 +1644,7 @@
         <v>3</v>
       </c>
       <c r="O6" s="0" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="P6" s="0">
         <v>30</v>
@@ -1664,13 +1655,13 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="0" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D7" s="0">
         <v>250</v>
@@ -1679,10 +1670,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="I7" s="0">
         <v>3</v>
@@ -1703,7 +1694,7 @@
         <v>1</v>
       </c>
       <c r="O7" s="0" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="P7" s="0">
         <v>30</v>
@@ -1714,13 +1705,13 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="0" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D8" s="0">
         <v>250</v>
@@ -1729,10 +1720,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="I8" s="0">
         <v>30</v>
@@ -1753,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="P8" s="0">
         <v>30</v>
@@ -1764,13 +1755,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="0" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="D9" s="0">
         <v>150</v>
@@ -1779,13 +1770,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>121</v>
+        <v>7</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="I9" s="0">
         <v>10</v>
@@ -1806,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="0" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="P9" s="0">
         <v>30</v>
@@ -1815,18 +1806,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R9" s="0" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="0" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>107</v>
+        <v>31</v>
       </c>
       <c r="D10" s="0">
         <v>150</v>
@@ -1835,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>122</v>
+        <v>12</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="I10" s="0">
         <v>10</v>
@@ -1862,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="0" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
       <c r="P10" s="0">
         <v>30</v>
@@ -1871,18 +1862,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R10" s="0" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="0" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D11" s="0">
         <v>150</v>
@@ -1891,13 +1882,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>129</v>
+        <v>4</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="I11" s="0">
         <v>10</v>
@@ -1918,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="0" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="P11" s="0">
         <v>30</v>
@@ -1927,18 +1918,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R11" s="0" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="0" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D12" s="0">
         <v>150</v>
@@ -1947,13 +1938,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I12" s="0">
         <v>10</v>
@@ -1974,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="0" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="P12" s="0">
         <v>30</v>
@@ -1983,18 +1974,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R12" s="0" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="0" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="D13" s="0">
         <v>150</v>
@@ -2003,13 +1994,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="I13" s="0">
         <v>10</v>
@@ -2030,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="P13" s="0">
         <v>30</v>
@@ -2039,18 +2030,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R13" s="0" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="0" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="D14" s="0">
         <v>150</v>
@@ -2059,13 +2050,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>124</v>
+        <v>9</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="I14" s="0">
         <v>10</v>
@@ -2086,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="0" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="P14" s="0">
         <v>30</v>
@@ -2095,18 +2086,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R14" s="0" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="0" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="D15" s="0">
         <v>150</v>
@@ -2115,13 +2106,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>130</v>
+        <v>8</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="I15" s="0">
         <v>10</v>
@@ -2142,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="0" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="P15" s="0">
         <v>30</v>
@@ -2151,7 +2142,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R15" s="0" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -561,7 +561,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" ns1:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2">
     <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="0"/>
     <pageSetUpPr/>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="118">
   <si>
     <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
   </si>
@@ -1040,13 +1040,13 @@
         <v>106</v>
       </c>
       <c r="H4" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I4" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J4" s="1">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
@@ -1093,7 +1093,7 @@
         <v>5</v>
       </c>
       <c r="J5" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
@@ -1574,16 +1574,16 @@
         <v>10</v>
       </c>
       <c r="J9" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>4</v>
@@ -1622,22 +1622,22 @@
         <v>16</v>
       </c>
       <c r="H10" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I10" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J10" s="1">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.14999999999999999</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>115</v>
@@ -1680,16 +1680,16 @@
         <v>10</v>
       </c>
       <c r="J11" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="1">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="M11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>2</v>
@@ -1728,19 +1728,19 @@
         <v>30</v>
       </c>
       <c r="I12" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J12" s="1">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
       </c>
       <c r="L12" s="1">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>85</v>
@@ -1776,22 +1776,22 @@
         <v>11</v>
       </c>
       <c r="H13" s="1">
+        <v>20</v>
+      </c>
+      <c r="I13" s="1">
+        <v>20</v>
+      </c>
+      <c r="J13" s="1">
         <v>10</v>
       </c>
-      <c r="I13" s="1">
-        <v>10</v>
-      </c>
-      <c r="J13" s="1">
-        <v>400</v>
-      </c>
       <c r="K13" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13" s="1">
         <v>1</v>
       </c>
       <c r="M13" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>20</v>
@@ -1830,13 +1830,13 @@
         <v>13</v>
       </c>
       <c r="H14" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I14" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J14" s="1">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
@@ -1845,7 +1845,7 @@
         <v>3</v>
       </c>
       <c r="M14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>21</v>
@@ -1884,22 +1884,22 @@
         <v>6</v>
       </c>
       <c r="H15" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I15" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J15" s="1">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>8</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="118">
   <si>
     <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
   </si>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,399 +15,399 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="131">
+  <si>
+    <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
   <si>
     <t xml:space="preserve">적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
   </si>
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
     <t xml:space="preserve">레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
   </si>
   <si>
+    <t xml:space="preserve">60004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
     <t xml:space="preserve">엘리트 미사일 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">엘리트 전기 포탑</t>
   </si>
   <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
     <t xml:space="preserve">MainTrain</t>
   </si>
   <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
     <t xml:space="preserve">엘리트 기관총 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">엘리트 폭발 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기본 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">range_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
   </si>
   <si>
     <t xml:space="preserve">화면에 있는 다수의 적들을 통시에 공격한다.</t>
   </si>
   <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
-  </si>
-  <si>
     <t xml:space="preserve">적이 가장 많은 곳으로 위치해 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
   </si>
 </sst>
 </file>
@@ -549,31 +549,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-      </border>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -716,18 +692,15 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="2">
-      <tableStyleElement type="headerRow" size="1" dxfId="1"/>
-      <tableStyleElement type="totalRow" size="1"/>
-    </tableStyle>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
     <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
-      <tableStyleElement type="wholeTable" size="1" dxfId="2"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="7"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="6"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="5"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="3"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="4"/>
+      <tableStyleElement type="wholeTable" size="1"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="5"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="4"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="3"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -1025,39 +998,39 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="0" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="0" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="D2" s="0">
         <v>250</v>
@@ -1066,7 +1039,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1088,66 +1061,66 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="0" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="0" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="D2" s="0">
         <v>250</v>
@@ -1156,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="I2" s="0">
         <v>5</v>
@@ -1177,7 +1150,7 @@
         <v>4</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="O2" s="0">
         <v>30</v>
@@ -1188,13 +1161,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="0" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="D3" s="0">
         <v>250</v>
@@ -1203,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="I3" s="0">
         <v>5</v>
@@ -1224,7 +1197,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="N3" s="0" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="O3" s="0">
         <v>30</v>
@@ -1235,13 +1208,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="0" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="D4" s="0">
         <v>150</v>
@@ -1250,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I4" s="0">
         <v>8</v>
@@ -1271,7 +1244,7 @@
         <v>4</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="O4" s="0">
         <v>30</v>
@@ -1280,18 +1253,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="0" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="D5" s="0">
         <v>150</v>
@@ -1300,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>126</v>
+        <v>20</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="I5" s="0">
         <v>13</v>
@@ -1321,7 +1294,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="O5" s="0">
         <v>30</v>
@@ -1330,7 +1303,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1351,76 +1324,76 @@
     <col min="6" max="6" width="21.1328125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.00390625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.00390625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.00390625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="9.00390625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.15625" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="0" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="0" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="D2" s="0">
         <v>250</v>
@@ -1429,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I2" s="0">
         <v>10</v>
@@ -1447,13 +1420,13 @@
         <v>1</v>
       </c>
       <c r="M2" s="0">
-        <v>0.29999999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="N2" s="0">
         <v>1</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="P2" s="0">
         <v>30</v>
@@ -1464,13 +1437,13 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="0" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D3" s="0">
         <v>250</v>
@@ -1479,10 +1452,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="I3" s="0">
         <v>8</v>
@@ -1491,19 +1464,19 @@
         <v>8</v>
       </c>
       <c r="K3" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L3" s="0">
         <v>1</v>
       </c>
       <c r="M3" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="N3" s="0">
         <v>1</v>
       </c>
       <c r="O3" s="0" t="s">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="P3" s="0">
         <v>30</v>
@@ -1514,13 +1487,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="0" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="D4" s="0">
         <v>250</v>
@@ -1529,10 +1502,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="I4" s="0">
         <v>10</v>
@@ -1547,13 +1520,13 @@
         <v>1</v>
       </c>
       <c r="M4" s="0">
-        <v>0.90000000000000002</v>
+        <v>1</v>
       </c>
       <c r="N4" s="0">
         <v>1</v>
       </c>
       <c r="O4" s="0" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="P4" s="0">
         <v>30</v>
@@ -1564,13 +1537,13 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="0" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="D5" s="0">
         <v>250</v>
@@ -1579,10 +1552,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I5" s="0">
         <v>30</v>
@@ -1603,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="0" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="P5" s="0">
         <v>30</v>
@@ -1614,13 +1587,13 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="0" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D6" s="0">
         <v>250</v>
@@ -1629,10 +1602,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="I6" s="0">
         <v>20</v>
@@ -1647,13 +1620,13 @@
         <v>3</v>
       </c>
       <c r="M6" s="0">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="N6" s="0">
         <v>3</v>
       </c>
       <c r="O6" s="0" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="P6" s="0">
         <v>30</v>
@@ -1664,13 +1637,13 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="0" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D7" s="0">
         <v>250</v>
@@ -1679,13 +1652,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="I7" s="0">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J7" s="0">
         <v>3</v>
@@ -1703,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="O7" s="0" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="P7" s="0">
         <v>30</v>
@@ -1714,13 +1687,13 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="0" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="D8" s="0">
         <v>250</v>
@@ -1729,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I8" s="0">
         <v>30</v>
@@ -1753,7 +1726,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="P8" s="0">
         <v>30</v>
@@ -1764,13 +1737,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="0" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="D9" s="0">
         <v>150</v>
@@ -1779,13 +1752,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I9" s="0">
         <v>10</v>
@@ -1806,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="0" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="P9" s="0">
         <v>30</v>
@@ -1815,18 +1788,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R9" s="0" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="0" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>37</v>
+        <v>111</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="D10" s="0">
         <v>150</v>
@@ -1835,13 +1808,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I10" s="0">
         <v>10</v>
@@ -1862,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="0" t="s">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="P10" s="0">
         <v>30</v>
@@ -1871,18 +1844,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R10" s="0" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="0" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="D11" s="0">
         <v>150</v>
@@ -1891,13 +1864,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I11" s="0">
         <v>10</v>
@@ -1918,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="0" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="P11" s="0">
         <v>30</v>
@@ -1927,18 +1900,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R11" s="0" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="0" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D12" s="0">
         <v>150</v>
@@ -1947,13 +1920,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="I12" s="0">
         <v>10</v>
@@ -1974,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="0" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="P12" s="0">
         <v>30</v>
@@ -1983,18 +1956,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R12" s="0" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="0" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="D13" s="0">
         <v>150</v>
@@ -2003,13 +1976,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I13" s="0">
         <v>10</v>
@@ -2030,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="P13" s="0">
         <v>30</v>
@@ -2039,18 +2012,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R13" s="0" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="0" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="D14" s="0">
         <v>150</v>
@@ -2059,13 +2032,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="I14" s="0">
         <v>10</v>
@@ -2086,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="0" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="P14" s="0">
         <v>30</v>
@@ -2095,18 +2068,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R14" s="0" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="0" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="D15" s="0">
         <v>150</v>
@@ -2115,13 +2088,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I15" s="0">
         <v>10</v>
@@ -2142,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="0" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="P15" s="0">
         <v>30</v>
@@ -2151,7 +2124,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R15" s="0" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,399 +15,399 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="131">
-  <si>
-    <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="131">
+  <si>
+    <t xml:space="preserve">다수의 적을 공격하고 감전 시킵니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">높은 공격 속도로 적을 공격합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저를 발사해 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt;범위 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일을 발사해 범위 피해를 줍니다,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적을 관통하며 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">넓은 범위에 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑의 강화 버전이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
   </si>
   <si>
     <t xml:space="preserve">target_count</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
     <t xml:space="preserve">포격 포탑의 강화 버전이다.</t>
   </si>
   <si>
     <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적이 가장 많은 곳으로 위치해 피해를 준다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">range_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">EliteColdAirRangeTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
   </si>
   <si>
     <t xml:space="preserve">EliteSniperTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">passive_skill_data_id</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑의 강화 버전이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기본 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 통시에 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적이 가장 많은 곳으로 위치해 피해를 준다.</t>
+    <t xml:space="preserve">범위에 지속적으로 피해를 줍니다.</t>
   </si>
 </sst>
 </file>
@@ -549,15 +549,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -693,14 +685,13 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
-      <tableStyleElement type="wholeTable" size="1"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="5"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="4"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="6">
+      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="3"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="2"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" size="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="1"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -998,39 +989,39 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="0" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>117</v>
+        <v>28</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="0" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="D2" s="0">
         <v>250</v>
@@ -1039,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1061,66 +1052,66 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="0" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="C1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="N1" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>127</v>
-      </c>
       <c r="O1" s="0" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="0" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="D2" s="0">
         <v>250</v>
@@ -1129,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="I2" s="0">
         <v>5</v>
@@ -1150,7 +1141,7 @@
         <v>4</v>
       </c>
       <c r="N2" s="0" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="O2" s="0">
         <v>30</v>
@@ -1161,13 +1152,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="0" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="D3" s="0">
         <v>250</v>
@@ -1176,10 +1167,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="I3" s="0">
         <v>5</v>
@@ -1197,7 +1188,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="N3" s="0" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="O3" s="0">
         <v>30</v>
@@ -1208,13 +1199,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="0" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>123</v>
+        <v>34</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="D4" s="0">
         <v>150</v>
@@ -1223,10 +1214,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="I4" s="0">
         <v>8</v>
@@ -1244,7 +1235,7 @@
         <v>4</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="O4" s="0">
         <v>30</v>
@@ -1253,18 +1244,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="0" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>119</v>
+        <v>25</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="D5" s="0">
         <v>150</v>
@@ -1273,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="I5" s="0">
         <v>13</v>
@@ -1294,7 +1285,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="O5" s="0">
         <v>30</v>
@@ -1303,7 +1294,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1331,69 +1322,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="0" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>117</v>
+        <v>28</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="G1" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="M1" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="H1" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>14</v>
-      </c>
       <c r="N1" s="0" t="s">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="0" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" s="0">
         <v>250</v>
@@ -1402,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="I2" s="0">
         <v>10</v>
@@ -1426,7 +1417,7 @@
         <v>1</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="P2" s="0">
         <v>30</v>
@@ -1437,13 +1428,13 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="0" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="D3" s="0">
         <v>250</v>
@@ -1452,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="I3" s="0">
         <v>8</v>
@@ -1476,7 +1467,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="0" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="P3" s="0">
         <v>30</v>
@@ -1487,13 +1478,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="0" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="0">
         <v>250</v>
@@ -1502,10 +1493,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="I4" s="0">
         <v>10</v>
@@ -1526,7 +1517,7 @@
         <v>1</v>
       </c>
       <c r="O4" s="0" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="P4" s="0">
         <v>30</v>
@@ -1537,13 +1528,13 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="0" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="D5" s="0">
         <v>250</v>
@@ -1552,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="I5" s="0">
         <v>30</v>
@@ -1576,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="0" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="P5" s="0">
         <v>30</v>
@@ -1587,13 +1578,13 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="0" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="D6" s="0">
         <v>250</v>
@@ -1602,10 +1593,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="I6" s="0">
         <v>20</v>
@@ -1626,7 +1617,7 @@
         <v>3</v>
       </c>
       <c r="O6" s="0" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="P6" s="0">
         <v>30</v>
@@ -1637,13 +1628,13 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="0" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>126</v>
+        <v>5</v>
       </c>
       <c r="D7" s="0">
         <v>250</v>
@@ -1652,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I7" s="0">
         <v>20</v>
@@ -1676,7 +1667,7 @@
         <v>1</v>
       </c>
       <c r="O7" s="0" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="P7" s="0">
         <v>30</v>
@@ -1687,13 +1678,13 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="0" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="D8" s="0">
         <v>250</v>
@@ -1702,10 +1693,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="I8" s="0">
         <v>30</v>
@@ -1726,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="P8" s="0">
         <v>30</v>
@@ -1737,13 +1728,13 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="0" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D9" s="0">
         <v>150</v>
@@ -1752,13 +1743,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="I9" s="0">
         <v>10</v>
@@ -1779,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="0" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="P9" s="0">
         <v>30</v>
@@ -1788,18 +1779,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R9" s="0" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="0" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="D10" s="0">
         <v>150</v>
@@ -1808,13 +1799,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="I10" s="0">
         <v>10</v>
@@ -1835,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="0" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="P10" s="0">
         <v>30</v>
@@ -1844,18 +1835,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R10" s="0" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="0" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D11" s="0">
         <v>150</v>
@@ -1864,13 +1855,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="I11" s="0">
         <v>10</v>
@@ -1891,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="0" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="P11" s="0">
         <v>30</v>
@@ -1900,18 +1891,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R11" s="0" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="0" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>110</v>
+        <v>45</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D12" s="0">
         <v>150</v>
@@ -1920,13 +1911,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="I12" s="0">
         <v>10</v>
@@ -1947,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="0" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="P12" s="0">
         <v>30</v>
@@ -1956,18 +1947,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R12" s="0" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="0" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>113</v>
+        <v>7</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="D13" s="0">
         <v>150</v>
@@ -1976,13 +1967,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="I13" s="0">
         <v>10</v>
@@ -2003,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="P13" s="0">
         <v>30</v>
@@ -2012,18 +2003,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R13" s="0" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="0" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="D14" s="0">
         <v>150</v>
@@ -2032,13 +2023,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="I14" s="0">
         <v>10</v>
@@ -2059,7 +2050,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="0" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="P14" s="0">
         <v>30</v>
@@ -2068,18 +2059,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R14" s="0" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="0" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="D15" s="0">
         <v>150</v>
@@ -2088,13 +2079,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="I15" s="0">
         <v>10</v>
@@ -2115,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="0" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="P15" s="0">
         <v>30</v>
@@ -2124,7 +2115,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="R15" s="0" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1,375 +1,374 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
+  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="train_data" sheetId="1" r:id="rId4"/>
     <sheet name="range_train_data" sheetId="2" r:id="rId5"/>
     <sheet name="turret_train_data" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="118">
-  <si>
-    <t xml:space="preserve">미사일로 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다. 공격속도는 느리다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격을 발사해 몇 번 큰 &lt;color=#FFDD52&gt;&lt;shake&gt;강한 피해&lt;/shake&gt;&lt;/color&gt;를 준다.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="118">
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다수의 적을 공격하고 감전 시킵니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일을 발사해 범위 피해를 줍니다,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주변 적을 둔화 시키며 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">넓은 범위에 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적을 관통하며 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저를 발사해 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt;범위 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위에 지속적으로 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
   </si>
   <si>
     <t xml:space="preserve">MissileProjectile</t>
   </si>
   <si>
+    <t xml:space="preserve">높은 공격 속도로 적을 공격합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주변 적을 밀치며 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">CannonTurretTrain</t>
   </si>
   <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
     <t xml:space="preserve">NormalProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기본 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
   </si>
   <si>
     <t xml:space="preserve">레이저 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
   </si>
   <si>
     <t xml:space="preserve">60013;</t>
   </si>
   <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
     <t xml:space="preserve">30003</t>
   </si>
   <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
   </si>
   <si>
     <t xml:space="preserve">50004;</t>
   </si>
   <si>
-    <t xml:space="preserve">42001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적이 가장 많은 곳으로 이동속도를 떨어뜨려 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60011;60012;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
   </si>
   <si>
     <t xml:space="preserve">critical_chance</t>
   </si>
   <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
     <t xml:space="preserve">is_main_train</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60011;60012;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
+    <t xml:space="preserve">range_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
   </si>
   <si>
     <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 번 큰 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 통시에 공격한다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적이 가장 많은 곳으로 위치해 피해를 준다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
   </si>
 </sst>
 </file>
@@ -377,7 +376,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -408,6 +407,11 @@
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -418,7 +422,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="1" diagonalDown="1">
       <left>
         <color indexed="64"/>
       </left>
@@ -431,10 +435,61 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
+      <diagonal>
+        <color indexed="64"/>
+      </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -445,7 +500,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -453,10 +508,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf/>
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -489,28 +543,133 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F2"/>
+          <bgColor rgb="FFDCE6F2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF96B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F2"/>
+          <bgColor rgb="FFDCE6F2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF96B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE5"/>
+          <bgColor rgb="FFB8CCE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE5"/>
+          <bgColor rgb="FFB8CCE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
-      <tableStyleElement type="wholeTable" size="1"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="5"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="4"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="8">
+      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="3"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="2"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" size="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="1"/>
+      <tableStyleElement type="secondColumnStripe" size="1"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
-      <tableStyleElement type="wholeTable" size="1" dxfId="6"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="11"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="10"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+      <tableStyleElement type="wholeTable" size="1" dxfId="5"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="10"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="9"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="8"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="6"/>
+      <tableStyleElement type="secondRowStripe" size="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="7"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -801,49 +960,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="3" max="3" width="24.140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D2" s="1">
         <v>250</v>
@@ -852,11 +1011,11 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
@@ -865,7 +1024,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -878,66 +1037,66 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="D2" s="1">
         <v>250</v>
@@ -946,10 +1105,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="H2" s="1">
         <v>5</v>
@@ -967,7 +1126,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="N2" s="1">
         <v>30</v>
@@ -978,13 +1137,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1">
         <v>250</v>
@@ -993,10 +1152,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H3" s="1">
         <v>5</v>
@@ -1011,10 +1170,10 @@
         <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>0.15</v>
+        <v>0.14999999999999999</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N3" s="1">
         <v>30</v>
@@ -1025,10 +1184,10 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D4" s="1">
         <v>150</v>
@@ -1037,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="H4" s="1">
         <v>5</v>
@@ -1055,7 +1214,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="N4" s="1">
         <v>30</v>
@@ -1064,18 +1223,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1">
         <v>150</v>
@@ -1084,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1">
         <v>5</v>
@@ -1102,7 +1261,7 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N5" s="1">
         <v>30</v>
@@ -1111,14 +1270,14 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
@@ -1131,6 +1290,7 @@
   <cols>
     <col min="2" max="2" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="81.2109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.2109375" style="2" bestFit="1" customWidth="1"/>
@@ -1143,69 +1303,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="D2" s="1">
         <v>250</v>
@@ -1214,10 +1374,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="H2" s="1">
         <v>10</v>
@@ -1232,13 +1392,13 @@
         <v>1</v>
       </c>
       <c r="L2" s="1">
-        <v>0.29999999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="M2" s="1">
         <v>1</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="O2" s="1">
         <v>30</v>
@@ -1249,13 +1409,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="D3" s="1">
         <v>250</v>
@@ -1264,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="H3" s="1">
         <v>8</v>
@@ -1276,19 +1436,19 @@
         <v>8</v>
       </c>
       <c r="J3" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" s="1">
         <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>0.14999999999999999</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="M3" s="1">
         <v>1</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="O3" s="1">
         <v>30</v>
@@ -1299,13 +1459,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1">
         <v>250</v>
@@ -1314,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="H4" s="1">
         <v>10</v>
@@ -1332,13 +1492,13 @@
         <v>1</v>
       </c>
       <c r="L4" s="1">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M4" s="1">
         <v>1</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="O4" s="1">
         <v>30</v>
@@ -1349,13 +1509,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="D5" s="1">
         <v>250</v>
@@ -1364,10 +1524,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="H5" s="1">
         <v>30</v>
@@ -1388,7 +1548,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="O5" s="1">
         <v>30</v>
@@ -1399,13 +1559,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1">
         <v>250</v>
@@ -1414,10 +1574,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="H6" s="1">
         <v>20</v>
@@ -1432,13 +1592,13 @@
         <v>3</v>
       </c>
       <c r="L6" s="1">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="1">
         <v>3</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="O6" s="1">
         <v>30</v>
@@ -1449,13 +1609,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1">
         <v>250</v>
@@ -1464,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="H7" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I7" s="1">
         <v>3</v>
@@ -1488,7 +1648,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="O7" s="1">
         <v>30</v>
@@ -1499,13 +1659,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1">
         <v>250</v>
@@ -1514,10 +1674,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="H8" s="1">
         <v>30</v>
@@ -1538,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="O8" s="1">
         <v>30</v>
@@ -1549,23 +1709,23 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="H9" s="1">
         <v>10</v>
@@ -1586,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="O9" s="1">
         <v>30</v>
@@ -1595,31 +1755,31 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>113</v>
+        <v>31</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="H10" s="1">
         <v>8</v>
@@ -1640,7 +1800,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="O10" s="1">
         <v>30</v>
@@ -1649,29 +1809,29 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>111</v>
+        <v>38</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -1692,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="O11" s="1">
         <v>30</v>
@@ -1701,28 +1861,28 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>109</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="H12" s="1">
         <v>30</v>
@@ -1743,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="O12" s="1">
         <v>30</v>
@@ -1752,28 +1912,28 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="H13" s="1">
         <v>20</v>
@@ -1794,7 +1954,7 @@
         <v>3</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="O13" s="1">
         <v>30</v>
@@ -1803,31 +1963,31 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="H14" s="1">
         <v>3</v>
@@ -1848,7 +2008,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="O14" s="1">
         <v>30</v>
@@ -1857,31 +2017,31 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="H15" s="1">
         <v>30</v>
@@ -1902,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="O15" s="1">
         <v>30</v>
@@ -1911,11 +2071,11 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,360 +15,360 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
+  <si>
+    <t xml:space="preserve">적을 관통하며 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">넓은 범위에 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60011;60012;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일을 발사해 범위 피해를 줍니다,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주변 적을 둔화 시키며 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다수의 적을 공격하고 감전 시킵니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주변 적을 밀치며 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위에 지속적으로 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">높은 공격 속도로 적을 공격합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저를 발사해 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt;범위 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
+  </si>
   <si>
     <t xml:space="preserve">30005</t>
   </si>
   <si>
-    <t xml:space="preserve">31003</t>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
   </si>
   <si>
     <t xml:space="preserve">기관총 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기본 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
+    <t xml:space="preserve">20001</t>
   </si>
   <si>
     <t xml:space="preserve">31004</t>
   </si>
   <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
     <t xml:space="preserve">31006</t>
   </si>
   <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">다수의 적을 공격하고 감전 시킵니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일을 발사해 범위 피해를 줍니다,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">주변 적을 둔화 시키며 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">넓은 범위에 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">적을 관통하며 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저를 발사해 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt;범위 피해를 줍니다.</t>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
   </si>
   <si>
     <t xml:space="preserve">엘리트 미사일 포탑</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
     <t xml:space="preserve">prefab_id</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">attack_area</t>
   </si>
   <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위에 지속적으로 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">높은 공격 속도로 적을 공격합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">주변 적을 밀치며 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60011;60012;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
     <t xml:space="preserve">range_projectile_prefab_id</t>
   </si>
   <si>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
   </si>
 </sst>
 </file>
@@ -510,39 +510,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFAEBFEA"/>
-          <bgColor rgb="FFAEBFEA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF94A5DF"/>
-          <bgColor rgb="FF94A5DF"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color rgb="FF6182D6"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF6182D6"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -636,6 +604,64 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F2"/>
+          <bgColor rgb="FFDCE6F2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF96B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F2"/>
+          <bgColor rgb="FFDCE6F2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF96B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFB8CCE5"/>
           <bgColor rgb="FFB8CCE5"/>
         </patternFill>
@@ -651,25 +677,18 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="8">
-      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="3"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="2"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" size="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="secondColumnStripe" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="2">
+      <tableStyleElement type="headerRow" size="1" dxfId="1"/>
+      <tableStyleElement type="totalRow" size="1"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
-      <tableStyleElement type="wholeTable" size="1" dxfId="5"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="10"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="9"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="8"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" size="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="7"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
+      <tableStyleElement type="wholeTable" size="1" dxfId="2"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="7"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="6"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="5"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="5"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="4"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -967,42 +986,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1">
         <v>250</v>
@@ -1011,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1028,75 +1047,78 @@
   <cols>
     <col min="2" max="2" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.2109375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.35546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>114</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D2" s="1">
         <v>250</v>
@@ -1105,10 +1127,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="H2" s="1">
         <v>5</v>
@@ -1126,7 +1148,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="N2" s="1">
         <v>30</v>
@@ -1137,13 +1159,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1">
         <v>250</v>
@@ -1152,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="H3" s="1">
         <v>5</v>
@@ -1173,7 +1195,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="N3" s="1">
         <v>30</v>
@@ -1184,28 +1206,28 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="D4" s="1">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H4" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I4" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J4" s="1">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
@@ -1214,7 +1236,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="N4" s="1">
         <v>30</v>
@@ -1223,45 +1245,45 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="D5" s="1">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H5" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I5" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J5" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.14999999999999999</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="N5" s="1">
         <v>30</v>
@@ -1270,10 +1292,10 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1294,7 +1316,7 @@
     <col min="6" max="6" width="21.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.2109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="9" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1303,69 +1325,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="Q1" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D2" s="1">
         <v>250</v>
@@ -1374,10 +1396,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="H2" s="1">
         <v>10</v>
@@ -1398,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="O2" s="1">
         <v>30</v>
@@ -1409,13 +1431,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D3" s="1">
         <v>250</v>
@@ -1424,10 +1446,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="H3" s="1">
         <v>8</v>
@@ -1448,7 +1470,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="O3" s="1">
         <v>30</v>
@@ -1459,13 +1481,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1">
         <v>250</v>
@@ -1474,10 +1496,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="H4" s="1">
         <v>10</v>
@@ -1498,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="O4" s="1">
         <v>30</v>
@@ -1509,13 +1531,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D5" s="1">
         <v>250</v>
@@ -1524,10 +1546,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="H5" s="1">
         <v>30</v>
@@ -1548,7 +1570,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="O5" s="1">
         <v>30</v>
@@ -1559,13 +1581,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1">
         <v>250</v>
@@ -1574,10 +1596,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="H6" s="1">
         <v>20</v>
@@ -1598,7 +1620,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="O6" s="1">
         <v>30</v>
@@ -1609,13 +1631,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1">
         <v>250</v>
@@ -1624,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="H7" s="1">
         <v>20</v>
@@ -1648,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="O7" s="1">
         <v>30</v>
@@ -1659,13 +1681,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
         <v>250</v>
@@ -1674,10 +1696,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="H8" s="1">
         <v>30</v>
@@ -1698,7 +1720,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O8" s="1">
         <v>30</v>
@@ -1709,10 +1731,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
@@ -1722,10 +1744,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="H9" s="1">
         <v>10</v>
@@ -1734,19 +1756,19 @@
         <v>10</v>
       </c>
       <c r="J9" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>0.29999999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="M9" s="1">
         <v>1</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="O9" s="1">
         <v>30</v>
@@ -1755,18 +1777,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
@@ -1776,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="H10" s="1">
         <v>8</v>
@@ -1788,19 +1810,19 @@
         <v>8</v>
       </c>
       <c r="J10" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <v>0.14999999999999999</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="M10" s="1">
         <v>1</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="O10" s="1">
         <v>30</v>
@@ -1809,16 +1831,16 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1">
@@ -1828,10 +1850,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -1840,19 +1862,19 @@
         <v>10</v>
       </c>
       <c r="J11" s="1">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="1">
-        <v>1.25</v>
+        <v>0.69999999999999996</v>
       </c>
       <c r="M11" s="1">
         <v>1</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="O11" s="1">
         <v>30</v>
@@ -1861,15 +1883,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
@@ -1879,10 +1901,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="H12" s="1">
         <v>30</v>
@@ -1891,7 +1913,7 @@
         <v>30</v>
       </c>
       <c r="J12" s="1">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
@@ -1903,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="O12" s="1">
         <v>30</v>
@@ -1912,15 +1934,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>104</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
@@ -1930,10 +1952,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="H13" s="1">
         <v>20</v>
@@ -1942,19 +1964,19 @@
         <v>20</v>
       </c>
       <c r="J13" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K13" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L13" s="1">
         <v>1</v>
       </c>
       <c r="M13" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="O13" s="1">
         <v>30</v>
@@ -1963,18 +1985,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>7</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="1" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
@@ -1984,19 +2006,19 @@
         <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="H14" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I14" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J14" s="1">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
@@ -2008,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="O14" s="1">
         <v>30</v>
@@ -2017,18 +2039,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
@@ -2038,10 +2060,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="H15" s="1">
         <v>30</v>
@@ -2050,19 +2072,19 @@
         <v>30</v>
       </c>
       <c r="J15" s="1">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>1</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="M15" s="1">
         <v>1</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O15" s="1">
         <v>30</v>
@@ -2071,7 +2093,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="train_data" sheetId="1" r:id="rId4"/>
@@ -15,348 +15,348 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="118">
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일을 발사해 범위 피해를 줍니다,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주변 적을 둔화 시키며 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다수의 적을 공격하고 감전 시킵니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">높은 공격 속도로 적을 공격합니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주변 적을 밀치며 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위에 지속적으로 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">넓은 범위에 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 줍니다.</t>
+  </si>
   <si>
     <t xml:space="preserve">적을 관통하며 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 줍니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">넓은 범위에 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt; 피해를 줍니다.</t>
+    <t xml:space="preserve">레이저를 발사해 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt;범위 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본 기차</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 화염 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 저격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 미사일 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 레이저 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 폭발 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 전기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 기관총 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 냉기 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엘리트 포격 포탑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
   </si>
   <si>
     <t xml:space="preserve">attack_damage</t>
   </si>
   <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
     <t xml:space="preserve">critical_chance</t>
   </si>
   <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가장 기본이 되는 기차이다.</t>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60011;60012;</t>
   </si>
   <si>
     <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60011;60012;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일을 발사해 범위 피해를 줍니다,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">주변 적을 둔화 시키며 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">다수의 적을 공격하고 감전 시킵니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">주변 적을 밀치며 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위에 지속적으로 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">높은 공격 속도로 적을 공격합니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저를 발사해 &lt;color=#FFDD52&gt;&lt;shake&gt;강력한&lt;/shake&gt;&lt;/color&gt;범위 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기본 기차</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 냉기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 폭발 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 전기 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 포격 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 기관총 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">엘리트 미사일 포탑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
   </si>
   <si>
     <t xml:space="preserve">range_projectile_prefab_id</t>
@@ -510,39 +510,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -677,18 +645,14 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="2">
-      <tableStyleElement type="headerRow" size="1" dxfId="1"/>
-      <tableStyleElement type="totalRow" size="1"/>
-    </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
-      <tableStyleElement type="wholeTable" size="1" dxfId="2"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="7"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="6"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="5"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="3"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="4"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="6">
+      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="3"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="2"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" size="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="1"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -986,42 +950,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="D2" s="1">
         <v>250</v>
@@ -1030,7 +994,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1059,66 +1023,66 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>114</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1">
         <v>250</v>
@@ -1127,10 +1091,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="H2" s="1">
         <v>5</v>
@@ -1148,7 +1112,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="N2" s="1">
         <v>30</v>
@@ -1159,13 +1123,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D3" s="1">
         <v>250</v>
@@ -1174,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="H3" s="1">
         <v>5</v>
@@ -1195,7 +1159,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N3" s="1">
         <v>30</v>
@@ -1206,10 +1170,10 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D4" s="1">
         <v>250</v>
@@ -1221,13 +1185,13 @@
         <v>117</v>
       </c>
       <c r="H4" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I4" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J4" s="1">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="K4" s="1">
         <v>1</v>
@@ -1236,7 +1200,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="N4" s="1">
         <v>30</v>
@@ -1245,18 +1209,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D5" s="1">
         <v>250</v>
@@ -1265,16 +1229,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H5" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I5" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J5" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
@@ -1283,7 +1247,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N5" s="1">
         <v>30</v>
@@ -1292,10 +1256,10 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>4</v>
+        <v>109</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1325,69 +1289,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>115</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1">
         <v>250</v>
@@ -1396,10 +1360,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H2" s="1">
         <v>10</v>
@@ -1420,7 +1384,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="O2" s="1">
         <v>30</v>
@@ -1431,13 +1395,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D3" s="1">
         <v>250</v>
@@ -1446,10 +1410,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H3" s="1">
         <v>8</v>
@@ -1470,7 +1434,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O3" s="1">
         <v>30</v>
@@ -1481,13 +1445,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1">
         <v>250</v>
@@ -1496,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H4" s="1">
         <v>10</v>
@@ -1520,7 +1484,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="O4" s="1">
         <v>30</v>
@@ -1531,13 +1495,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1">
         <v>250</v>
@@ -1546,10 +1510,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H5" s="1">
         <v>30</v>
@@ -1570,7 +1534,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="O5" s="1">
         <v>30</v>
@@ -1581,13 +1545,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1">
         <v>250</v>
@@ -1596,10 +1560,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="H6" s="1">
         <v>20</v>
@@ -1620,7 +1584,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="O6" s="1">
         <v>30</v>
@@ -1631,13 +1595,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="D7" s="1">
         <v>250</v>
@@ -1646,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H7" s="1">
         <v>20</v>
@@ -1670,7 +1634,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O7" s="1">
         <v>30</v>
@@ -1681,13 +1645,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D8" s="1">
         <v>250</v>
@@ -1696,10 +1660,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H8" s="1">
         <v>30</v>
@@ -1720,7 +1684,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O8" s="1">
         <v>30</v>
@@ -1731,10 +1695,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1">
@@ -1744,10 +1708,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H9" s="1">
         <v>10</v>
@@ -1756,19 +1720,19 @@
         <v>10</v>
       </c>
       <c r="J9" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="M9" s="1">
         <v>1</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="O9" s="1">
         <v>30</v>
@@ -1777,18 +1741,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
@@ -1798,10 +1762,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H10" s="1">
         <v>8</v>
@@ -1810,7 +1774,7 @@
         <v>8</v>
       </c>
       <c r="J10" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K10" s="1">
         <v>1</v>
@@ -1822,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O10" s="1">
         <v>30</v>
@@ -1831,7 +1795,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="R10" s="3"/>
     </row>
@@ -1840,7 +1804,7 @@
         <v>68</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1">
@@ -1850,10 +1814,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -1862,19 +1826,19 @@
         <v>10</v>
       </c>
       <c r="J11" s="1">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="1">
-        <v>0.69999999999999996</v>
+        <v>1</v>
       </c>
       <c r="M11" s="1">
         <v>1</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="O11" s="1">
         <v>30</v>
@@ -1883,15 +1847,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
@@ -1901,10 +1865,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H12" s="1">
         <v>30</v>
@@ -1913,7 +1877,7 @@
         <v>30</v>
       </c>
       <c r="J12" s="1">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
@@ -1925,7 +1889,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="O12" s="1">
         <v>30</v>
@@ -1934,15 +1898,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
@@ -1955,7 +1919,7 @@
         <v>116</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="H13" s="1">
         <v>20</v>
@@ -1964,10 +1928,10 @@
         <v>20</v>
       </c>
       <c r="J13" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K13" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L13" s="1">
         <v>1</v>
@@ -1976,7 +1940,7 @@
         <v>8</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="O13" s="1">
         <v>30</v>
@@ -1985,18 +1949,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="1" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
@@ -2006,19 +1970,19 @@
         <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H14" s="1">
         <v>20</v>
       </c>
       <c r="I14" s="1">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J14" s="1">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="K14" s="1">
         <v>1</v>
@@ -2030,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O14" s="1">
         <v>30</v>
@@ -2039,18 +2003,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="1" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
@@ -2060,11 +2024,11 @@
         <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="H15" s="1">
         <v>30</v>
       </c>
@@ -2072,19 +2036,19 @@
         <v>30</v>
       </c>
       <c r="J15" s="1">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>0.80000000000000004</v>
+        <v>1</v>
       </c>
       <c r="M15" s="1">
         <v>1</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O15" s="1">
         <v>30</v>
@@ -2093,7 +2057,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="118">
   <si>
     <t xml:space="preserve">train_name</t>
   </si>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,360 +15,360 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
   <si>
     <t xml:space="preserve">train_name</t>
   </si>
   <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
     <t xml:space="preserve">is_main_train</t>
   </si>
   <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
+  <si>
     <t xml:space="preserve">attack_range</t>
   </si>
   <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
     <t xml:space="preserve">현대무기_대포_288스마</t>
   </si>
   <si>
-    <t xml:space="preserve">60006;60007;</t>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
   </si>
   <si>
     <t xml:space="preserve">60004;60005;</t>
   </si>
   <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">LaserProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">60002;60003;</t>
+    <t xml:space="preserve">60014;60015;</t>
   </si>
   <si>
     <t xml:space="preserve">60011;60012;</t>
   </si>
   <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
     <t xml:space="preserve">attack_area</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
   </si>
   <si>
     <t xml:space="preserve">40002</t>
   </si>
   <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
     <t xml:space="preserve">50001;</t>
   </si>
   <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
   </si>
   <si>
     <t xml:space="preserve">30007</t>
   </si>
   <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
     <t xml:space="preserve">30006</t>
   </si>
   <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
     <t xml:space="preserve">31002</t>
   </si>
   <si>
     <t xml:space="preserve">50006;</t>
   </si>
   <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_42001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_42002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
     <t xml:space="preserve">MainTrain</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">range_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
 </sst>
 </file>
@@ -510,23 +510,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF94A5DF"/>
-          <bgColor rgb="FF94A5DF"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color rgb="FF6182D6"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF6182D6"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -701,22 +685,20 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="6">
-      <tableStyleElement type="headerRow" size="1" dxfId="3"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="2"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="1"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="1"/>
-      <tableStyleElement type="firstRowStripe" size="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="4">
+      <tableStyleElement type="headerRow" size="1" dxfId="2"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="1"/>
+      <tableStyleElement type="firstColumn" size="1"/>
+      <tableStyleElement type="lastColumn" size="1"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
-      <tableStyleElement type="wholeTable" size="1" dxfId="4"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="9"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="8"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="7"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="5"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="6"/>
+      <tableStyleElement type="wholeTable" size="1" dxfId="3"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="8"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="7"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="6"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="4"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="5"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -1014,42 +996,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1075,75 +1057,77 @@
   <cols>
     <col min="2" max="2" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.2109375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.35546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P1" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1152,16 +1136,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H2" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I2" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J2" s="3">
         <v>50</v>
@@ -1173,7 +1157,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="N2" s="3">
         <v>30</v>
@@ -1184,13 +1168,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1199,16 +1183,16 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I3" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3" s="3">
         <v>2</v>
@@ -1220,7 +1204,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="N3" s="3">
         <v>30</v>
@@ -1231,26 +1215,26 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H4" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J4" s="3">
         <v>50</v>
@@ -1262,7 +1246,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="N4" s="3">
         <v>30</v>
@@ -1271,34 +1255,34 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" s="0">
         <v>2</v>
@@ -1310,7 +1294,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="N5" s="3">
         <v>30</v>
@@ -1319,10 +1303,10 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1352,69 +1336,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q1" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1423,10 +1407,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="H2" s="3">
         <v>10</v>
@@ -1447,7 +1431,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="O2" s="3">
         <v>30</v>
@@ -1458,13 +1442,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1473,10 +1457,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="H3" s="3">
         <v>8</v>
@@ -1497,7 +1481,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O3" s="3">
         <v>30</v>
@@ -1508,13 +1492,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1523,10 +1507,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="H4" s="3">
         <v>10</v>
@@ -1547,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="O4" s="3">
         <v>30</v>
@@ -1558,13 +1542,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1573,10 +1557,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3">
         <v>30</v>
@@ -1597,7 +1581,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O5" s="3">
         <v>30</v>
@@ -1608,13 +1592,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1623,10 +1607,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="H6" s="3">
         <v>20</v>
@@ -1647,7 +1631,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="O6" s="3">
         <v>30</v>
@@ -1658,13 +1642,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1673,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="H7" s="3">
         <v>20</v>
@@ -1697,7 +1681,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="O7" s="3">
         <v>30</v>
@@ -1708,13 +1692,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1723,10 +1707,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="H8" s="3">
         <v>30</v>
@@ -1747,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="O8" s="3">
         <v>30</v>
@@ -1758,10 +1742,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="3" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1771,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="H9" s="0">
         <v>10</v>
@@ -1795,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="O9" s="3">
         <v>30</v>
@@ -1804,18 +1788,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1825,10 +1809,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1849,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O10" s="3">
         <v>30</v>
@@ -1858,16 +1842,16 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1877,10 +1861,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="H11" s="0">
         <v>10</v>
@@ -1901,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="O11" s="3">
         <v>30</v>
@@ -1910,15 +1894,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1928,10 +1912,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="H12" s="0">
         <v>30</v>
@@ -1952,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" s="3">
         <v>30</v>
@@ -1961,15 +1945,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1979,10 +1963,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="H13" s="0">
         <v>20</v>
@@ -2003,7 +1987,7 @@
         <v>3</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="O13" s="3">
         <v>30</v>
@@ -2012,18 +1996,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -2033,10 +2017,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="H14" s="0">
         <v>20</v>
@@ -2057,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="O14" s="3">
         <v>30</v>
@@ -2066,18 +2050,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -2087,10 +2071,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="H15" s="0">
         <v>30</v>
@@ -2111,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="O15" s="3">
         <v>30</v>
@@ -2120,7 +2104,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -17,358 +17,358 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
   <si>
+    <t xml:space="preserve">Train_30003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">description</t>
   </si>
   <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">prefab_id</t>
   </si>
   <si>
-    <t xml:space="preserve">train_name</t>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
   </si>
   <si>
     <t xml:space="preserve">is_main_train</t>
   </si>
   <si>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
     <t xml:space="preserve">attack_interval</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
     <t xml:space="preserve">현대무기_대포_288스마</t>
   </si>
   <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
     <t xml:space="preserve">60011;60012;</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_42001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_42002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">range_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
   </si>
 </sst>
 </file>
@@ -510,23 +510,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -685,20 +669,17 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="4">
-      <tableStyleElement type="headerRow" size="1" dxfId="2"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumn" size="1"/>
-      <tableStyleElement type="lastColumn" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="1">
+      <tableStyleElement type="headerRow" size="1"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
-      <tableStyleElement type="wholeTable" size="1" dxfId="3"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="8"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="7"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="6"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="6"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="4"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="5"/>
+      <tableStyleElement type="wholeTable" size="1" dxfId="1"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="6"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="5"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="4"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="3"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -996,42 +977,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1040,7 +1021,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1068,66 +1049,66 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1136,16 +1117,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="H2" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3">
         <v>50</v>
@@ -1157,7 +1138,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="N2" s="3">
         <v>30</v>
@@ -1168,13 +1149,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1183,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="H3" s="3">
         <v>3</v>
@@ -1204,7 +1185,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="N3" s="3">
         <v>30</v>
@@ -1215,10 +1196,10 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="3" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -1228,13 +1209,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="3">
         <v>50</v>
@@ -1246,7 +1227,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="N4" s="3">
         <v>30</v>
@@ -1255,18 +1236,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="3" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -1294,7 +1275,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="N5" s="3">
         <v>30</v>
@@ -1303,10 +1284,10 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1336,69 +1317,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>6</v>
+        <v>98</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1407,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="H2" s="3">
         <v>10</v>
@@ -1431,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="O2" s="3">
         <v>30</v>
@@ -1442,13 +1423,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1457,10 +1438,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="H3" s="3">
         <v>8</v>
@@ -1481,7 +1462,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O3" s="3">
         <v>30</v>
@@ -1492,13 +1473,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1507,10 +1488,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="H4" s="3">
         <v>10</v>
@@ -1531,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="O4" s="3">
         <v>30</v>
@@ -1542,13 +1523,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>110</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1557,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="H5" s="3">
         <v>30</v>
@@ -1581,7 +1562,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="O5" s="3">
         <v>30</v>
@@ -1592,13 +1573,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1607,10 +1588,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="H6" s="3">
         <v>20</v>
@@ -1631,7 +1612,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="O6" s="3">
         <v>30</v>
@@ -1642,13 +1623,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1657,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H7" s="3">
         <v>20</v>
@@ -1681,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="O7" s="3">
         <v>30</v>
@@ -1692,13 +1673,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1707,10 +1688,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H8" s="3">
         <v>30</v>
@@ -1731,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="O8" s="3">
         <v>30</v>
@@ -1742,10 +1723,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="3" t="s">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1755,10 +1736,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="H9" s="0">
         <v>10</v>
@@ -1779,7 +1760,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="O9" s="3">
         <v>30</v>
@@ -1788,18 +1769,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1809,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1833,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O10" s="3">
         <v>30</v>
@@ -1842,16 +1823,16 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1861,10 +1842,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="H11" s="0">
         <v>10</v>
@@ -1885,7 +1866,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="O11" s="3">
         <v>30</v>
@@ -1894,15 +1875,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1912,10 +1893,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="H12" s="0">
         <v>30</v>
@@ -1936,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="O12" s="3">
         <v>30</v>
@@ -1945,15 +1926,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>18</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1963,10 +1944,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="H13" s="0">
         <v>20</v>
@@ -1987,7 +1968,7 @@
         <v>3</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="O13" s="3">
         <v>30</v>
@@ -1996,18 +1977,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -2017,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H14" s="0">
         <v>20</v>
@@ -2041,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="O14" s="3">
         <v>30</v>
@@ -2050,18 +2031,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -2071,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H15" s="0">
         <v>30</v>
@@ -2095,7 +2076,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="O15" s="3">
         <v>30</v>
@@ -2104,7 +2085,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="train_data" sheetId="1" r:id="rId4"/>
@@ -17,355 +17,355 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
   <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">Train_30003_Desc</t>
   </si>
   <si>
+    <t xml:space="preserve">Train_42001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31001_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">SniperProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_42001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31006_Name</t>
+    <t xml:space="preserve">Train_31003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Desc</t>
   </si>
   <si>
     <t xml:space="preserve">Weapon_KMD_10_UI</t>
   </si>
   <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">60008;60009;60010;</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
+    <t xml:space="preserve">Train_30007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
   </si>
   <si>
     <t xml:space="preserve">Train_30001_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_42002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
   </si>
   <si>
     <t xml:space="preserve">31001</t>
   </si>
   <si>
-    <t xml:space="preserve">60013;</t>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
   </si>
   <si>
     <t xml:space="preserve">40001</t>
   </si>
   <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
   </si>
   <si>
     <t xml:space="preserve">30005</t>
   </si>
   <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
+    <t xml:space="preserve">31007</t>
   </si>
   <si>
     <t xml:space="preserve">50006;</t>
   </si>
   <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
   </si>
   <si>
     <t xml:space="preserve">critical_damage</t>
   </si>
   <si>
-    <t xml:space="preserve">critical_chance</t>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
   </si>
   <si>
     <t xml:space="preserve">60006;60007;</t>
   </si>
   <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
     <t xml:space="preserve">is_main_train</t>
   </si>
   <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
   </si>
   <si>
     <t xml:space="preserve">FireTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
+    <t xml:space="preserve">60011;60012;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
   </si>
   <si>
     <t xml:space="preserve">LaserProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60011;60012;</t>
-  </si>
-  <si>
     <t xml:space="preserve">turret_projectile_prefab_id</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">range_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">EliteExplosionRangeTrain</t>
@@ -510,39 +510,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -669,17 +637,13 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="1">
-      <tableStyleElement type="headerRow" size="1"/>
-    </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
-      <tableStyleElement type="wholeTable" size="1" dxfId="1"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="6"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="5"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="4"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="3"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="5">
+      <tableStyleElement type="headerRow" size="1" dxfId="3"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="2"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="1"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -977,42 +941,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1021,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1049,66 +1013,66 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="I1" s="3" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>99</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1117,10 +1081,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="H2" s="3">
         <v>4</v>
@@ -1138,7 +1102,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="N2" s="3">
         <v>30</v>
@@ -1149,13 +1113,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1164,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>112</v>
@@ -1185,7 +1149,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="N3" s="3">
         <v>30</v>
@@ -1196,10 +1160,10 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -1227,7 +1191,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="N4" s="3">
         <v>30</v>
@@ -1236,18 +1200,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -1257,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
@@ -1275,7 +1239,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="N5" s="3">
         <v>30</v>
@@ -1284,10 +1248,10 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1308,6 +1272,7 @@
     <col min="6" max="6" width="21.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.2109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1317,43 +1282,43 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="I1" s="3" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>114</v>
@@ -1362,24 +1327,24 @@
         <v>99</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1388,16 +1353,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="H2" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I2" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J2" s="3">
         <v>10</v>
@@ -1412,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="O2" s="3">
         <v>30</v>
@@ -1423,13 +1388,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1438,16 +1403,16 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="H3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J3" s="3">
         <v>2</v>
@@ -1462,7 +1427,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="O3" s="3">
         <v>30</v>
@@ -1473,13 +1438,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1488,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="H4" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I4" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J4" s="3">
         <v>30</v>
@@ -1512,7 +1477,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="O4" s="3">
         <v>30</v>
@@ -1523,13 +1488,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1538,16 +1503,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="H5" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I5" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J5" s="3">
         <v>50</v>
@@ -1562,7 +1527,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O5" s="3">
         <v>30</v>
@@ -1573,13 +1538,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1588,16 +1553,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="H6" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I6" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J6" s="3">
         <v>10</v>
@@ -1612,7 +1577,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="O6" s="3">
         <v>30</v>
@@ -1623,13 +1588,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1638,13 +1603,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H7" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I7" s="3">
         <v>3</v>
@@ -1662,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="O7" s="3">
         <v>30</v>
@@ -1673,13 +1638,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1688,16 +1653,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="H8" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I8" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J8" s="3">
         <v>50</v>
@@ -1712,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="O8" s="3">
         <v>30</v>
@@ -1723,10 +1688,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1736,10 +1701,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="H9" s="0">
         <v>10</v>
@@ -1760,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="O9" s="3">
         <v>30</v>
@@ -1769,18 +1734,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1790,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1814,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="O10" s="3">
         <v>30</v>
@@ -1823,16 +1788,16 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1842,10 +1807,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="H11" s="0">
         <v>10</v>
@@ -1866,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="O11" s="3">
         <v>30</v>
@@ -1875,15 +1840,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1893,16 +1858,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="H12" s="0">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I12" s="0">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J12" s="0">
         <v>50</v>
@@ -1917,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O12" s="3">
         <v>30</v>
@@ -1926,15 +1891,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1944,16 +1909,16 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="H13" s="0">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I13" s="0">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J13" s="0">
         <v>10</v>
@@ -1968,7 +1933,7 @@
         <v>3</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="O13" s="3">
         <v>30</v>
@@ -1977,18 +1942,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1998,13 +1963,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H14" s="0">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I14" s="0">
         <v>3</v>
@@ -2022,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="O14" s="3">
         <v>30</v>
@@ -2031,18 +1996,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -2052,16 +2017,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="H15" s="0">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I15" s="0">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J15" s="0">
         <v>50</v>
@@ -2076,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="O15" s="3">
         <v>30</v>
@@ -2085,7 +2050,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="118">
   <si>
     <t xml:space="preserve">id</t>
   </si>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,66 +15,132 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
+  <si>
+    <t xml:space="preserve">60011;60012;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
   <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">EliteLaserTurretTrain</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">EliteFireTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">active_skill_data_id</t>
   </si>
   <si>
     <t xml:space="preserve">ElectrickTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
     <t xml:space="preserve">EliteNormalTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">ColdAirRangeTrain</t>
   </si>
   <si>
     <t xml:space="preserve">Weapon_MEL_16_UI</t>
   </si>
   <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42001_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">ColdAirProjectile</t>
   </si>
   <si>
     <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
   </si>
   <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31003_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">60016;60017;60018</t>
   </si>
   <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_42001_Name</t>
+    <t xml:space="preserve">Train_20001_Name</t>
   </si>
   <si>
     <t xml:space="preserve">Train_31004_Name</t>
@@ -89,283 +155,217 @@
     <t xml:space="preserve">MissileProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_31006_Name</t>
-  </si>
-  <si>
     <t xml:space="preserve">Train_31007_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
+    <t xml:space="preserve">Train_30007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
   </si>
   <si>
     <t xml:space="preserve">Train_30005_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Name</t>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
   </si>
   <si>
     <t xml:space="preserve">ElectrickProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_42002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
   </si>
   <si>
     <t xml:space="preserve">Weapon_KMD_12_UI</t>
   </si>
   <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
   </si>
   <si>
     <t xml:space="preserve">Train_20001_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
     <t xml:space="preserve">Train_30001_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
-  </si>
-  <si>
     <t xml:space="preserve">60008;60009;60010;</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_30007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
     <t xml:space="preserve">Train_30001_Desc</t>
   </si>
   <si>
     <t xml:space="preserve">ExplosionProjectile</t>
   </si>
   <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
     <t xml:space="preserve">train_name</t>
   </si>
   <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
     <t xml:space="preserve">attack_area</t>
   </si>
   <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
     <t xml:space="preserve">MainTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60011;60012;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">range_projectile_prefab_id</t>
   </si>
   <si>
     <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
   </si>
   <si>
     <t xml:space="preserve">EliteExplosionRangeTrain</t>
@@ -510,23 +510,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-      </border>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -638,12 +622,11 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="5">
-      <tableStyleElement type="headerRow" size="1" dxfId="3"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="2"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="1"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="4">
+      <tableStyleElement type="headerRow" size="1" dxfId="2"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="1"/>
+      <tableStyleElement type="firstColumn" size="1"/>
+      <tableStyleElement type="lastColumn" size="1"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -941,42 +924,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -985,7 +968,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1013,66 +996,66 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1081,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H2" s="3">
         <v>4</v>
@@ -1102,7 +1085,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="N2" s="3">
         <v>30</v>
@@ -1113,13 +1096,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1128,10 +1111,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="H3" s="3">
         <v>3</v>
@@ -1149,7 +1132,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="N3" s="3">
         <v>30</v>
@@ -1160,10 +1143,10 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="3" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -1191,7 +1174,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="N4" s="3">
         <v>30</v>
@@ -1200,18 +1183,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -1221,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
@@ -1239,7 +1222,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="N5" s="3">
         <v>30</v>
@@ -1248,10 +1231,10 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1282,69 +1265,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>108</v>
+        <v>11</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1353,16 +1336,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="H2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3">
         <v>10</v>
@@ -1377,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="O2" s="3">
         <v>30</v>
@@ -1388,13 +1371,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1403,16 +1386,16 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="H3" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3" s="3">
         <v>2</v>
@@ -1427,7 +1410,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O3" s="3">
         <v>30</v>
@@ -1438,13 +1421,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1453,16 +1436,16 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="H4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4" s="3">
         <v>30</v>
@@ -1477,7 +1460,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="O4" s="3">
         <v>30</v>
@@ -1488,13 +1471,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1503,16 +1486,16 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H5" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I5" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J5" s="3">
         <v>50</v>
@@ -1527,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>113</v>
+        <v>2</v>
       </c>
       <c r="O5" s="3">
         <v>30</v>
@@ -1538,13 +1521,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1553,16 +1536,16 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H6" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" s="3">
         <v>10</v>
@@ -1577,7 +1560,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="O6" s="3">
         <v>30</v>
@@ -1588,13 +1571,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1603,13 +1586,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I7" s="3">
         <v>3</v>
@@ -1627,7 +1610,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="O7" s="3">
         <v>30</v>
@@ -1638,13 +1621,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1653,16 +1636,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="H8" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I8" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" s="3">
         <v>50</v>
@@ -1677,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="O8" s="3">
         <v>30</v>
@@ -1688,10 +1671,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1701,16 +1684,16 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="H9" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I9" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J9" s="0">
         <v>10</v>
@@ -1725,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="O9" s="3">
         <v>30</v>
@@ -1734,18 +1717,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q9" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="R9" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1755,10 +1738,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1779,7 +1762,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O10" s="3">
         <v>30</v>
@@ -1788,16 +1771,16 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1807,16 +1790,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="H11" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I11" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J11" s="0">
         <v>30</v>
@@ -1831,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="O11" s="3">
         <v>30</v>
@@ -1840,15 +1823,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1858,16 +1841,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H12" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I12" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J12" s="0">
         <v>50</v>
@@ -1882,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>113</v>
+        <v>2</v>
       </c>
       <c r="O12" s="3">
         <v>30</v>
@@ -1891,15 +1874,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1909,16 +1892,16 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H13" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J13" s="0">
         <v>10</v>
@@ -1933,7 +1916,7 @@
         <v>3</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="O13" s="3">
         <v>30</v>
@@ -1942,18 +1925,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1963,13 +1946,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H14" s="0">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I14" s="0">
         <v>3</v>
@@ -1987,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="O14" s="3">
         <v>30</v>
@@ -1996,18 +1979,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -2017,16 +2000,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="H15" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I15" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J15" s="0">
         <v>50</v>
@@ -2041,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="O15" s="3">
         <v>30</v>
@@ -2050,7 +2033,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="118">
   <si>
     <t xml:space="preserve">60011;60012;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Train_40002_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_42001_Name</t>
+    <t xml:space="preserve">Train_41001_Name</t>
   </si>
   <si>
     <t xml:space="preserve">ColdAirProjectile</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">LaserTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_42002_Name</t>
+    <t xml:space="preserve">Train_41002_Name</t>
   </si>
   <si>
     <t xml:space="preserve">Train_31002_Name</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">30001</t>
   </si>
   <si>
-    <t xml:space="preserve">42001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42002</t>
+    <t xml:space="preserve">41001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41002</t>
   </si>
   <si>
     <t xml:space="preserve">30006</t>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,360 +15,360 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="118">
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_41002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_41001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">range_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
   <si>
     <t xml:space="preserve">60011;60012;</t>
   </si>
   <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
     <t xml:space="preserve">is_main_train</t>
   </si>
   <si>
-    <t xml:space="preserve">LaserProjectile</t>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
   </si>
   <si>
     <t xml:space="preserve">60004;60005;</t>
   </si>
   <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
     <t xml:space="preserve">현대무기_대포_288스마</t>
   </si>
   <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">passive_skill_data_id</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_41001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_41002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
   </si>
 </sst>
 </file>
@@ -510,41 +510,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDCE6F2"/>
-          <bgColor rgb="FFDCE6F2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF96B3D7"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDCE6F2"/>
-          <bgColor rgb="FFDCE6F2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF96B3D7"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -622,12 +588,7 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="4">
-      <tableStyleElement type="headerRow" size="1" dxfId="2"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumn" size="1"/>
-      <tableStyleElement type="lastColumn" size="1"/>
-    </tableStyle>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0"/>
   </tableStyles>
 </styleSheet>
 </file>
@@ -924,42 +885,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -968,7 +929,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>113</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -989,73 +950,74 @@
     <col min="6" max="6" width="24.2109375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.35546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>6</v>
-      </c>
       <c r="K1" s="3" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1064,10 +1026,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="H2" s="3">
         <v>4</v>
@@ -1085,7 +1047,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="N2" s="3">
         <v>30</v>
@@ -1096,13 +1058,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1111,10 +1073,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="H3" s="3">
         <v>3</v>
@@ -1123,16 +1085,16 @@
         <v>3</v>
       </c>
       <c r="J3" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="3">
         <v>1</v>
       </c>
       <c r="L3" s="3">
-        <v>0.14999999999999999</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N3" s="3">
         <v>30</v>
@@ -1143,10 +1105,10 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="3" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -1156,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="H4" s="3">
         <v>4</v>
@@ -1174,7 +1136,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="N4" s="3">
         <v>30</v>
@@ -1183,18 +1145,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="3" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -1204,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
@@ -1213,16 +1175,16 @@
         <v>3</v>
       </c>
       <c r="J5" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="3">
         <v>1</v>
       </c>
       <c r="L5" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N5" s="3">
         <v>30</v>
@@ -1231,10 +1193,10 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1265,69 +1227,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>6</v>
-      </c>
       <c r="K1" s="3" t="s">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="N1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="R1" s="3" t="s">
-        <v>25</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1336,10 +1298,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H2" s="3">
         <v>8</v>
@@ -1360,7 +1322,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="O2" s="3">
         <v>30</v>
@@ -1371,13 +1333,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1386,31 +1348,31 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="H3" s="3">
         <v>8</v>
       </c>
       <c r="I3" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J3" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3" s="3">
         <v>1</v>
       </c>
       <c r="L3" s="3">
-        <v>0.10000000000000001</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="M3" s="3">
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="O3" s="3">
         <v>30</v>
@@ -1421,13 +1383,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1436,10 +1398,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="H4" s="3">
         <v>8</v>
@@ -1460,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="O4" s="3">
         <v>30</v>
@@ -1471,13 +1433,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1486,10 +1448,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H5" s="3">
         <v>15</v>
@@ -1510,7 +1472,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="O5" s="3">
         <v>30</v>
@@ -1521,13 +1483,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1536,10 +1498,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="H6" s="3">
         <v>11</v>
@@ -1560,7 +1522,7 @@
         <v>3</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="O6" s="3">
         <v>30</v>
@@ -1571,13 +1533,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1586,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="H7" s="3">
         <v>13</v>
@@ -1610,7 +1572,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="O7" s="3">
         <v>30</v>
@@ -1621,13 +1583,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1636,10 +1598,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="H8" s="3">
         <v>12</v>
@@ -1660,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="O8" s="3">
         <v>30</v>
@@ -1671,10 +1633,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1684,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="H9" s="0">
         <v>8</v>
@@ -1708,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="O9" s="3">
         <v>30</v>
@@ -1717,18 +1679,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>108</v>
+        <v>59</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1738,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1750,19 +1712,19 @@
         <v>8</v>
       </c>
       <c r="J10" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K10" s="0">
         <v>1</v>
       </c>
       <c r="L10" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="M10" s="3">
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="O10" s="3">
         <v>30</v>
@@ -1771,16 +1733,16 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>7</v>
+        <v>102</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1790,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="H11" s="0">
         <v>8</v>
@@ -1814,7 +1776,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="O11" s="3">
         <v>30</v>
@@ -1823,15 +1785,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1841,10 +1803,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H12" s="0">
         <v>15</v>
@@ -1865,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="O12" s="3">
         <v>30</v>
@@ -1874,15 +1836,15 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>0</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1892,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="H13" s="0">
         <v>11</v>
@@ -1916,7 +1878,7 @@
         <v>3</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="O13" s="3">
         <v>30</v>
@@ -1925,18 +1887,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1946,10 +1908,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="H14" s="0">
         <v>13</v>
@@ -1970,7 +1932,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="O14" s="3">
         <v>30</v>
@@ -1979,18 +1941,18 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -2000,10 +1962,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="H15" s="0">
         <v>12</v>
@@ -2024,7 +1986,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="O15" s="3">
         <v>30</v>
@@ -2033,7 +1995,7 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="train_data" sheetId="1" r:id="rId4"/>
@@ -15,360 +15,360 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="118">
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
   <si>
     <t xml:space="preserve">60011;60012;</t>
   </si>
   <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
     <t xml:space="preserve">is_main_train</t>
   </si>
   <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
   </si>
   <si>
     <t xml:space="preserve">critical_damage</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">range_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
   </si>
   <si>
     <t xml:space="preserve">passive_skill_data_id</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
     <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_42001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_42002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
   </si>
 </sst>
 </file>
@@ -510,28 +510,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDCE6F2"/>
-          <bgColor rgb="FFDCE6F2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF96B3D7"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -622,11 +601,8 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="4">
-      <tableStyleElement type="headerRow" size="1" dxfId="2"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumn" size="1"/>
-      <tableStyleElement type="lastColumn" size="1"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="1">
+      <tableStyleElement type="headerRow" size="1"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -924,42 +900,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -968,7 +944,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -990,72 +966,73 @@
     <col min="7" max="7" width="36.35546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="M1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1064,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H2" s="3">
         <v>4</v>
@@ -1085,24 +1062,24 @@
         <v>4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="N2" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1111,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="H3" s="3">
         <v>3</v>
@@ -1132,18 +1109,18 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="N3" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O3" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="3" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>31</v>
@@ -1156,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="H4" s="3">
         <v>4</v>
@@ -1174,27 +1151,27 @@
         <v>4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="N4" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="3" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -1204,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
@@ -1222,19 +1199,19 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="N5" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O5" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1258,6 +1235,7 @@
     <col min="9" max="10" width="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17.140625" style="2" bestFit="1" customWidth="1"/>
@@ -1265,69 +1243,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="N1" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="R1" s="3" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1336,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H2" s="3">
         <v>8</v>
@@ -1360,24 +1338,24 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="O2" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P2" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1386,10 +1364,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H3" s="3">
         <v>8</v>
@@ -1410,24 +1388,24 @@
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="O3" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P3" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1436,10 +1414,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H4" s="3">
         <v>8</v>
@@ -1460,24 +1438,24 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="O4" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P4" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1486,10 +1464,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H5" s="3">
         <v>15</v>
@@ -1510,24 +1488,24 @@
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="O5" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P5" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1536,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H6" s="3">
         <v>11</v>
@@ -1560,24 +1538,24 @@
         <v>3</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="O6" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P6" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1586,10 +1564,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="H7" s="3">
         <v>13</v>
@@ -1610,24 +1588,24 @@
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="O7" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P7" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1636,10 +1614,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="H8" s="3">
         <v>12</v>
@@ -1660,21 +1638,21 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="O8" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1684,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H9" s="0">
         <v>8</v>
@@ -1708,27 +1686,27 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="O9" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>94</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1738,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1762,25 +1740,25 @@
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="O10" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1790,10 +1768,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H11" s="0">
         <v>8</v>
@@ -1814,24 +1792,24 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="O11" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P11" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1841,10 +1819,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H12" s="0">
         <v>15</v>
@@ -1865,24 +1843,24 @@
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="O12" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P12" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1892,10 +1870,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H13" s="0">
         <v>11</v>
@@ -1916,27 +1894,27 @@
         <v>3</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="O13" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P13" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1946,10 +1924,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="H14" s="0">
         <v>13</v>
@@ -1970,27 +1948,27 @@
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="O14" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P14" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -2000,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="H15" s="0">
         <v>12</v>
@@ -2024,16 +2002,16 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="O15" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3">
-        <v>0.29999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="train_data" sheetId="1" r:id="rId4"/>
@@ -15,360 +15,360 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60011;60012;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
   <si>
     <t xml:space="preserve">31006</t>
   </si>
   <si>
+    <t xml:space="preserve">50006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
     <t xml:space="preserve">max_hp</t>
   </si>
   <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
     <t xml:space="preserve">30005</t>
   </si>
   <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
     <t xml:space="preserve">31005</t>
   </si>
   <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
     <t xml:space="preserve">50005;</t>
   </si>
   <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_42001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_42002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60011;60012;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
   </si>
   <si>
     <t xml:space="preserve">range_projectile_prefab_id</t>
   </si>
   <si>
     <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
   </si>
 </sst>
 </file>
@@ -510,20 +510,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDCE6F2"/>
-          <bgColor rgb="FFDCE6F2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF96B3D7"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -601,9 +588,7 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1"/>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="1">
-      <tableStyleElement type="headerRow" size="1"/>
-    </tableStyle>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0"/>
   </tableStyles>
 </styleSheet>
 </file>
@@ -900,42 +885,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -944,7 +929,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>85</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -973,66 +958,66 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="M1" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1041,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>28</v>
@@ -1062,7 +1047,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N2" s="3">
         <v>0</v>
@@ -1073,13 +1058,13 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1088,10 +1073,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="H3" s="3">
         <v>3</v>
@@ -1109,7 +1094,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N3" s="3">
         <v>0</v>
@@ -1120,10 +1105,10 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -1133,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="H4" s="3">
         <v>4</v>
@@ -1151,7 +1136,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N4" s="3">
         <v>0</v>
@@ -1160,18 +1145,18 @@
         <v>0.5</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -1181,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
@@ -1199,7 +1184,7 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N5" s="3">
         <v>0</v>
@@ -1208,10 +1193,10 @@
         <v>0.5</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1232,8 +1217,9 @@
     <col min="6" max="6" width="21.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.2109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1243,58 +1229,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>83</v>
+        <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="M1" s="3" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -1302,10 +1288,10 @@
         <v>80</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1314,10 +1300,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H2" s="3">
         <v>8</v>
@@ -1338,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="O2" s="3">
         <v>0</v>
@@ -1349,13 +1335,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1364,10 +1350,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H3" s="3">
         <v>8</v>
@@ -1388,7 +1374,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="O3" s="3">
         <v>0</v>
@@ -1399,13 +1385,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1414,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H4" s="3">
         <v>8</v>
@@ -1438,7 +1424,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="O4" s="3">
         <v>0</v>
@@ -1449,13 +1435,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1464,10 +1450,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H5" s="3">
         <v>15</v>
@@ -1488,7 +1474,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="O5" s="3">
         <v>0</v>
@@ -1499,13 +1485,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1514,10 +1500,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H6" s="3">
         <v>11</v>
@@ -1529,16 +1515,16 @@
         <v>10</v>
       </c>
       <c r="K6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" s="3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="O6" s="3">
         <v>0</v>
@@ -1549,13 +1535,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1564,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H7" s="3">
         <v>13</v>
@@ -1588,7 +1574,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O7" s="3">
         <v>0</v>
@@ -1599,13 +1585,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1614,10 +1600,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H8" s="3">
         <v>12</v>
@@ -1638,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -1652,7 +1638,7 @@
         <v>79</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1662,10 +1648,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H9" s="0">
         <v>8</v>
@@ -1686,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
@@ -1695,18 +1681,18 @@
         <v>0.5</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1716,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1740,7 +1726,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -1749,16 +1735,16 @@
         <v>0.5</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1768,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H11" s="0">
         <v>8</v>
@@ -1792,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="O11" s="3">
         <v>0</v>
@@ -1801,15 +1787,15 @@
         <v>0.5</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1819,10 +1805,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H12" s="0">
         <v>15</v>
@@ -1843,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="O12" s="3">
         <v>0</v>
@@ -1852,15 +1838,15 @@
         <v>0.5</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1870,10 +1856,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H13" s="0">
         <v>11</v>
@@ -1885,16 +1871,16 @@
         <v>10</v>
       </c>
       <c r="K13" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" s="0">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M13" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="O13" s="3">
         <v>0</v>
@@ -1903,18 +1889,18 @@
         <v>0.5</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>11</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1924,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H14" s="0">
         <v>13</v>
@@ -1948,7 +1934,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1957,15 +1943,15 @@
         <v>0.5</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>62</v>
@@ -1978,10 +1964,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H15" s="0">
         <v>12</v>
@@ -2002,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -2011,7 +1997,7 @@
         <v>0.5</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="train_data" sheetId="1" r:id="rId4"/>
@@ -15,357 +15,360 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="119">
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_42002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60011;60012;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
   <si>
     <t xml:space="preserve">train_name</t>
   </si>
   <si>
+    <t xml:space="preserve">slow_rate</t>
+  </si>
+  <si>
     <t xml:space="preserve">MainTrain</t>
   </si>
   <si>
     <t xml:space="preserve">attack_area</t>
   </si>
   <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60011;60012;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_42002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_42001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
     <t xml:space="preserve">31006</t>
   </si>
   <si>
+    <t xml:space="preserve">42001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
     <t xml:space="preserve">50006;</t>
   </si>
   <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
     <t xml:space="preserve">30006</t>
   </si>
   <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42002</t>
+  </si>
+  <si>
     <t xml:space="preserve">30002</t>
   </si>
   <si>
-    <t xml:space="preserve">31001</t>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
   </si>
   <si>
     <t xml:space="preserve">30001</t>
   </si>
   <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
   </si>
   <si>
     <t xml:space="preserve">31003</t>
   </si>
   <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
     <t xml:space="preserve">40002</t>
   </si>
   <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
+    <t xml:space="preserve">range_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
   </si>
   <si>
     <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
   </si>
   <si>
     <t xml:space="preserve">EliteExplosionRangeTrain</t>
@@ -493,7 +496,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -504,6 +507,9 @@
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -885,42 +891,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -929,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +947,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -951,73 +957,76 @@
     <col min="7" max="7" width="36.35546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+        <v>63</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="P1" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q1" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="R1" s="0" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1026,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>28</v>
@@ -1046,25 +1055,30 @@
       <c r="L2" s="3">
         <v>4</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N2" s="3">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3">
+      <c r="M2" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="N2" s="0">
+        <v>0</v>
+      </c>
+      <c r="O2" s="0">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1073,10 +1087,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="H3" s="3">
         <v>3</v>
@@ -1093,22 +1107,27 @@
       <c r="L3" s="3">
         <v>0.14999999999999999</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" s="3">
-        <v>0</v>
-      </c>
-      <c r="O3" s="3">
+      <c r="M3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="0">
+        <v>0</v>
+      </c>
+      <c r="O3" s="0">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
         <v>88</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -1118,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3">
         <v>4</v>
@@ -1135,28 +1154,31 @@
       <c r="L4" s="3">
         <v>4</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N4" s="3">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3">
+      <c r="M4" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="N4" s="0">
+        <v>0</v>
+      </c>
+      <c r="O4" s="0">
         <v>0.5</v>
       </c>
-      <c r="P4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="P4" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q4" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="3" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -1166,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
@@ -1183,20 +1205,23 @@
       <c r="L5" s="0">
         <v>0.14999999999999999</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="3">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3">
+      <c r="M5" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="N5" s="0">
+        <v>0</v>
+      </c>
+      <c r="O5" s="0">
         <v>0.5</v>
       </c>
-      <c r="P5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>89</v>
+      <c r="P5" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q5" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="R5" s="4">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1229,69 +1254,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1300,10 +1325,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="H2" s="3">
         <v>8</v>
@@ -1324,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="O2" s="3">
         <v>0</v>
@@ -1335,13 +1360,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1350,10 +1375,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="H3" s="3">
         <v>8</v>
@@ -1374,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="O3" s="3">
         <v>0</v>
@@ -1385,13 +1410,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1400,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H4" s="3">
         <v>8</v>
@@ -1424,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="O4" s="3">
         <v>0</v>
@@ -1435,13 +1460,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1450,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3">
         <v>15</v>
@@ -1474,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="O5" s="3">
         <v>0</v>
@@ -1485,13 +1510,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1500,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H6" s="3">
         <v>11</v>
@@ -1524,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O6" s="3">
         <v>0</v>
@@ -1535,13 +1560,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1550,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="H7" s="3">
         <v>13</v>
@@ -1574,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O7" s="3">
         <v>0</v>
@@ -1585,13 +1610,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1600,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="H8" s="3">
         <v>12</v>
@@ -1624,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -1635,10 +1660,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="3" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1648,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="H9" s="0">
         <v>8</v>
@@ -1672,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
@@ -1681,18 +1706,18 @@
         <v>0.5</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1702,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1726,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -1735,16 +1760,16 @@
         <v>0.5</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1754,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H11" s="0">
         <v>8</v>
@@ -1778,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="O11" s="3">
         <v>0</v>
@@ -1787,15 +1812,15 @@
         <v>0.5</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1805,10 +1830,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H12" s="0">
         <v>15</v>
@@ -1829,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="O12" s="3">
         <v>0</v>
@@ -1838,15 +1863,15 @@
         <v>0.5</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1856,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H13" s="0">
         <v>11</v>
@@ -1880,7 +1905,7 @@
         <v>2</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O13" s="3">
         <v>0</v>
@@ -1889,18 +1914,18 @@
         <v>0.5</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1910,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="H14" s="0">
         <v>13</v>
@@ -1934,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1943,18 +1968,18 @@
         <v>0.5</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -1964,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="H15" s="0">
         <v>12</v>
@@ -1988,7 +2013,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1997,7 +2022,7 @@
         <v>0.5</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="119">
   <si>
     <t xml:space="preserve">LaserTurretTrain</t>
   </si>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="0">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="O3" s="0">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="O4" s="0">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P4" s="0" t="s">
         <v>56</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="0">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P5" s="0" t="s">
         <v>62</v>
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="P2" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1455,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>96</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>64</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>24</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>54</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>104</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>53</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="P15" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>26</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,11 +15,203 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="119">
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60011;60012;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_41002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_41001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
   <si>
     <t xml:space="preserve">LaserTurretTrain</t>
   </si>
   <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_288_19_UI</t>
   </si>
   <si>
@@ -35,196 +227,118 @@
     <t xml:space="preserve">Train_30001_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_41001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_41002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60011;60012;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slow_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">range_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">EliteSniperTurretTrain</t>
@@ -233,145 +347,31 @@
     <t xml:space="preserve">FireEffectProjectile</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">EliteCannonTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
+    <t xml:space="preserve">passive_skill_data_id</t>
   </si>
   <si>
     <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slow_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
   </si>
 </sst>
 </file>
@@ -891,42 +891,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -935,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -956,77 +956,77 @@
     <col min="6" max="6" width="24.2109375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.35546875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1038,7 +1038,7 @@
         <v>51</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H2" s="3">
         <v>4</v>
@@ -1056,7 +1056,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="N2" s="0">
         <v>0</v>
@@ -1072,13 +1072,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="3" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1087,28 +1087,28 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="H3" s="3">
         <v>3</v>
       </c>
       <c r="I3" s="3">
+        <v>5</v>
+      </c>
+      <c r="J3" s="3">
         <v>3</v>
       </c>
-      <c r="J3" s="3">
-        <v>2</v>
-      </c>
       <c r="K3" s="3">
         <v>1</v>
       </c>
       <c r="L3" s="3">
-        <v>0.14999999999999999</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="N3" s="0">
         <v>0</v>
@@ -1119,15 +1119,15 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="H4" s="3">
         <v>4</v>
@@ -1155,7 +1155,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="N4" s="0">
         <v>0</v>
@@ -1164,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="R4" s="4">
         <v>0</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="3" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -1188,25 +1188,25 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
       </c>
       <c r="I5" s="3">
+        <v>5</v>
+      </c>
+      <c r="J5" s="0">
         <v>3</v>
       </c>
-      <c r="J5" s="0">
-        <v>2</v>
-      </c>
       <c r="K5" s="3">
         <v>1</v>
       </c>
       <c r="L5" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="N5" s="0">
         <v>0</v>
@@ -1215,13 +1215,13 @@
         <v>0</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="R5" s="4">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1254,69 +1254,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1325,10 +1325,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3">
         <v>8</v>
@@ -1349,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="O2" s="3">
         <v>0</v>
@@ -1360,13 +1360,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1375,10 +1375,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H3" s="3">
         <v>8</v>
@@ -1399,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="O3" s="3">
         <v>0</v>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1425,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H4" s="3">
         <v>8</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="O4" s="3">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1475,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3">
         <v>15</v>
@@ -1499,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="O5" s="3">
         <v>0</v>
@@ -1510,13 +1510,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="H6" s="3">
         <v>11</v>
@@ -1549,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="O6" s="3">
         <v>0</v>
@@ -1560,13 +1560,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1575,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H7" s="3">
         <v>13</v>
@@ -1599,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="O7" s="3">
         <v>0</v>
@@ -1610,13 +1610,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1625,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H8" s="3">
         <v>12</v>
@@ -1649,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="3" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1673,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H9" s="0">
         <v>8</v>
@@ -1697,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
@@ -1706,18 +1706,18 @@
         <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1727,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1751,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -1760,16 +1760,16 @@
         <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1779,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="H11" s="0">
         <v>8</v>
@@ -1803,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="O11" s="3">
         <v>0</v>
@@ -1812,12 +1812,12 @@
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>50</v>
@@ -1830,10 +1830,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H12" s="0">
         <v>15</v>
@@ -1854,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="O12" s="3">
         <v>0</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1881,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="H13" s="0">
         <v>11</v>
@@ -1905,7 +1905,7 @@
         <v>2</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="O13" s="3">
         <v>0</v>
@@ -1914,18 +1914,18 @@
         <v>0</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H14" s="0">
         <v>13</v>
@@ -1959,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1968,18 +1968,18 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -1989,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="H15" s="0">
         <v>12</v>
@@ -2013,7 +2013,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="train_data" sheetId="1" r:id="rId4"/>
@@ -17,316 +17,352 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="119">
   <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slow_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_41002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_41001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
     <t xml:space="preserve">critical_chance</t>
   </si>
   <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">target_count</t>
   </si>
   <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60011;60012;</t>
+  </si>
+  <si>
     <t xml:space="preserve">60006;60007;</t>
   </si>
   <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
     <t xml:space="preserve">attack_count</t>
   </si>
   <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60011;60012;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_41002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_41001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slow_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
   </si>
   <si>
     <t xml:space="preserve">range_projectile_prefab_id</t>
@@ -335,43 +371,7 @@
     <t xml:space="preserve">turret_projectile_prefab_id</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
   </si>
 </sst>
 </file>
@@ -891,42 +891,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -935,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>100</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -964,69 +964,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="L1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="O1" s="0" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="P1" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q1" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="R1" s="0" t="s">
         <v>5</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="O1" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q1" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="R1" s="0" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="H2" s="3">
         <v>4</v>
@@ -1056,7 +1056,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="N2" s="0">
         <v>0</v>
@@ -1072,13 +1072,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="3" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1087,10 +1087,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="H3" s="3">
         <v>3</v>
@@ -1108,7 +1108,7 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="N3" s="0">
         <v>0</v>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H4" s="3">
         <v>4</v>
@@ -1155,7 +1155,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="N4" s="0">
         <v>0</v>
@@ -1164,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="R4" s="4">
         <v>0</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="3" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
@@ -1206,7 +1206,7 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="N5" s="0">
         <v>0</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="R5" s="4">
         <v>25</v>
@@ -1254,69 +1254,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="L1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="Q1" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1325,10 +1325,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H2" s="3">
         <v>8</v>
@@ -1349,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O2" s="3">
         <v>0</v>
@@ -1360,13 +1360,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1375,10 +1375,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="H3" s="3">
         <v>8</v>
@@ -1399,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="O3" s="3">
         <v>0</v>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1425,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H4" s="3">
         <v>8</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="O4" s="3">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1475,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H5" s="3">
         <v>15</v>
@@ -1499,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="O5" s="3">
         <v>0</v>
@@ -1510,13 +1510,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="H6" s="3">
         <v>11</v>
@@ -1549,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="O6" s="3">
         <v>0</v>
@@ -1560,13 +1560,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1575,31 +1575,31 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="3">
+        <v>85</v>
+      </c>
+      <c r="H7" s="0">
         <v>13</v>
       </c>
-      <c r="I7" s="3">
-        <v>3</v>
-      </c>
-      <c r="J7" s="3">
+      <c r="I7" s="0">
+        <v>2</v>
+      </c>
+      <c r="J7" s="0">
         <v>50</v>
       </c>
-      <c r="K7" s="3">
-        <v>1</v>
-      </c>
-      <c r="L7" s="3">
-        <v>3</v>
+      <c r="K7" s="0">
+        <v>1</v>
+      </c>
+      <c r="L7" s="0">
+        <v>2</v>
       </c>
       <c r="M7" s="3">
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="O7" s="3">
         <v>0</v>
@@ -1610,13 +1610,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1625,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H8" s="3">
         <v>12</v>
@@ -1649,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="3" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1673,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="H9" s="0">
         <v>8</v>
@@ -1697,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
@@ -1706,18 +1706,18 @@
         <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1727,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1751,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -1760,16 +1760,16 @@
         <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1779,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H11" s="0">
         <v>8</v>
@@ -1803,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="O11" s="3">
         <v>0</v>
@@ -1812,15 +1812,15 @@
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1830,10 +1830,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H12" s="0">
         <v>15</v>
@@ -1854,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="O12" s="3">
         <v>0</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1881,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="H13" s="0">
         <v>11</v>
@@ -1905,7 +1905,7 @@
         <v>2</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="O13" s="3">
         <v>0</v>
@@ -1914,18 +1914,18 @@
         <v>0</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1935,16 +1935,16 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="H14" s="0">
         <v>13</v>
       </c>
       <c r="I14" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" s="0">
         <v>50</v>
@@ -1953,13 +1953,13 @@
         <v>1</v>
       </c>
       <c r="L14" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M14" s="3">
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1968,18 +1968,18 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -1989,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H15" s="0">
         <v>12</v>
@@ -2013,7 +2013,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -17,361 +17,361 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="119">
   <si>
+    <t xml:space="preserve">50004;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slow_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slow_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60011;60012;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
   </si>
   <si>
     <t xml:space="preserve">MissileTurretTrain</t>
   </si>
   <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_41002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_MEL_16_UI</t>
   </si>
   <si>
+    <t xml:space="preserve">Train_30001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_41001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_KMD_12_UI</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_30003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Name</t>
   </si>
   <si>
     <t xml:space="preserve">60008;60009;60010;</t>
   </si>
   <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
+    <t xml:space="preserve">Train_40001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31001_Name</t>
   </si>
   <si>
     <t xml:space="preserve">Train_30007_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_31007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_41002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
+    <t xml:space="preserve">Train_31004_Name</t>
   </si>
   <si>
     <t xml:space="preserve">Train_31003_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_41001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60011;60012;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">range_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">EliteSniperTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">passive_skill_data_id</t>
   </si>
   <si>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">EliteLaserTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
 </sst>
 </file>
@@ -891,42 +891,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -935,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -964,69 +964,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="P1" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q1" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="N1" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="O1" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="P1" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q1" s="0" t="s">
-        <v>112</v>
-      </c>
       <c r="R1" s="0" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H2" s="3">
         <v>4</v>
@@ -1056,7 +1056,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="N2" s="0">
         <v>0</v>
@@ -1072,13 +1072,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1087,10 +1087,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="H3" s="3">
         <v>3</v>
@@ -1108,7 +1108,7 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="N3" s="0">
         <v>0</v>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H4" s="3">
         <v>4</v>
@@ -1155,7 +1155,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="N4" s="0">
         <v>0</v>
@@ -1164,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R4" s="4">
         <v>0</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
@@ -1206,7 +1206,7 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="N5" s="0">
         <v>0</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R5" s="4">
         <v>25</v>
@@ -1254,69 +1254,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1325,10 +1325,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H2" s="3">
         <v>8</v>
@@ -1349,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="O2" s="3">
         <v>0</v>
@@ -1360,13 +1360,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1375,10 +1375,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H3" s="3">
         <v>8</v>
@@ -1399,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="O3" s="3">
         <v>0</v>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1425,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H4" s="3">
         <v>8</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="O4" s="3">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>80</v>
@@ -1484,7 +1484,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J5" s="3">
         <v>50</v>
@@ -1499,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="O5" s="3">
         <v>0</v>
@@ -1510,13 +1510,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="H6" s="3">
         <v>11</v>
@@ -1549,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="O6" s="3">
         <v>0</v>
@@ -1560,13 +1560,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1575,16 +1575,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H7" s="0">
         <v>13</v>
       </c>
       <c r="I7" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" s="0">
         <v>50</v>
@@ -1599,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="O7" s="3">
         <v>0</v>
@@ -1610,13 +1610,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1625,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="H8" s="3">
         <v>12</v>
@@ -1649,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1673,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H9" s="0">
         <v>8</v>
@@ -1697,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
@@ -1706,18 +1706,18 @@
         <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1727,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1751,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -1760,16 +1760,16 @@
         <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1779,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H11" s="0">
         <v>8</v>
@@ -1803,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="O11" s="3">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1820,7 +1820,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>80</v>
@@ -1839,7 +1839,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="0">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J12" s="0">
         <v>50</v>
@@ -1854,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="O12" s="3">
         <v>0</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1881,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="H13" s="0">
         <v>11</v>
@@ -1905,7 +1905,7 @@
         <v>2</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="O13" s="3">
         <v>0</v>
@@ -1914,18 +1914,18 @@
         <v>0</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1938,13 +1938,13 @@
         <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H14" s="0">
         <v>13</v>
       </c>
       <c r="I14" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="0">
         <v>50</v>
@@ -1959,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1968,18 +1968,18 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -1989,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="H15" s="0">
         <v>12</v>
@@ -2013,7 +2013,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,318 +15,321 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="119">
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60016;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60011;60012;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60013;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
   <si>
     <t xml:space="preserve">50004;</t>
   </si>
   <si>
-    <t xml:space="preserve">20001</t>
+    <t xml:space="preserve">31004</t>
   </si>
   <si>
     <t xml:space="preserve">30004</t>
   </si>
   <si>
-    <t xml:space="preserve">40002</t>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50001;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
   </si>
   <si>
     <t xml:space="preserve">30002</t>
   </si>
   <si>
-    <t xml:space="preserve">60013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50001;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31003</t>
-  </si>
-  <si>
     <t xml:space="preserve">31005</t>
   </si>
   <si>
+    <t xml:space="preserve">30001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
     <t xml:space="preserve">60001</t>
   </si>
   <si>
-    <t xml:space="preserve">41001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31002</t>
+    <t xml:space="preserve">30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31001</t>
   </si>
   <si>
     <t xml:space="preserve">31006</t>
   </si>
   <si>
-    <t xml:space="preserve">30006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
   </si>
   <si>
     <t xml:space="preserve">41002</t>
   </si>
   <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31001</t>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_41001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_41002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
   </si>
   <si>
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">train_name</t>
   </si>
   <si>
+    <t xml:space="preserve">slow_rate</t>
+  </si>
+  <si>
     <t xml:space="preserve">prefab_id</t>
   </si>
   <si>
-    <t xml:space="preserve">slow_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60011;60012;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_41002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31003_Name</t>
   </si>
   <si>
     <t xml:space="preserve">ColdAirRangeTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_41001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60016;60017;60018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31003_Name</t>
+    <t xml:space="preserve">EliteElectrickTurretTrain</t>
   </si>
   <si>
     <t xml:space="preserve">EliteExplosionRangeTrain</t>
@@ -335,43 +338,40 @@
     <t xml:space="preserve">turret_projectile_prefab_id</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
     <t xml:space="preserve">range_projectile_prefab_id</t>
   </si>
   <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
     <t xml:space="preserve">EliteFireTurretTrain</t>
   </si>
   <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
   </si>
   <si>
     <t xml:space="preserve">EliteCannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
   </si>
 </sst>
 </file>
@@ -891,42 +891,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -935,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -964,69 +964,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="L1" s="3" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>107</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="H2" s="3">
         <v>4</v>
@@ -1053,10 +1053,10 @@
         <v>1</v>
       </c>
       <c r="L2" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="N2" s="0">
         <v>0</v>
@@ -1072,13 +1072,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1087,10 +1087,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H3" s="3">
         <v>3</v>
@@ -1108,7 +1108,7 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N3" s="0">
         <v>0</v>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H4" s="3">
         <v>4</v>
@@ -1152,10 +1152,10 @@
         <v>1</v>
       </c>
       <c r="L4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="N4" s="0">
         <v>0</v>
@@ -1164,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="R4" s="4">
         <v>0</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
@@ -1206,7 +1206,7 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N5" s="0">
         <v>0</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="R5" s="4">
         <v>25</v>
@@ -1254,69 +1254,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="L1" s="3" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1325,10 +1325,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H2" s="3">
         <v>8</v>
@@ -1349,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="O2" s="3">
         <v>0</v>
@@ -1360,13 +1360,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1375,10 +1375,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="H3" s="3">
         <v>8</v>
@@ -1399,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O3" s="3">
         <v>0</v>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1425,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="H4" s="3">
         <v>8</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O4" s="3">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1475,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3">
         <v>15</v>
@@ -1493,13 +1493,13 @@
         <v>1</v>
       </c>
       <c r="L5" s="3">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M5" s="3">
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="O5" s="3">
         <v>0</v>
@@ -1510,13 +1510,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H6" s="3">
         <v>11</v>
@@ -1549,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="O6" s="3">
         <v>0</v>
@@ -1560,13 +1560,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1575,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="H7" s="0">
         <v>13</v>
@@ -1599,7 +1599,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="O7" s="3">
         <v>0</v>
@@ -1610,13 +1610,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1625,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="H8" s="3">
         <v>12</v>
@@ -1649,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1673,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="H9" s="0">
         <v>8</v>
@@ -1697,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
@@ -1706,18 +1706,18 @@
         <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1727,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1751,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -1760,16 +1760,16 @@
         <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1779,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="H11" s="0">
         <v>8</v>
@@ -1803,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O11" s="3">
         <v>0</v>
@@ -1812,15 +1812,15 @@
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1830,10 +1830,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H12" s="0">
         <v>15</v>
@@ -1848,13 +1848,13 @@
         <v>1</v>
       </c>
       <c r="L12" s="0">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M12" s="3">
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="O12" s="3">
         <v>0</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1881,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H13" s="0">
         <v>11</v>
@@ -1905,7 +1905,7 @@
         <v>2</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="O13" s="3">
         <v>0</v>
@@ -1914,18 +1914,18 @@
         <v>0</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>95</v>
+        <v>4</v>
       </c>
       <c r="H14" s="0">
         <v>13</v>
@@ -1959,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1968,18 +1968,18 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -1989,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="H15" s="0">
         <v>12</v>
@@ -2013,7 +2013,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>90</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,7 +15,91 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="119">
+  <si>
+    <t xml:space="preserve">EliteMissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteLaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteFireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteNormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteSniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteCannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_288스마</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60006;60007;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60011;60012;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004;60005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60014;60015;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60002;60003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
   <si>
     <t xml:space="preserve">Weapon_288_19_UI</t>
   </si>
@@ -23,114 +107,222 @@
     <t xml:space="preserve">Train_40001_Desc</t>
   </si>
   <si>
+    <t xml:space="preserve">Train_30004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60008;60009;60010;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31004_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">60016;60017;60018</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_20001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31006_Name</t>
-  </si>
-  <si>
     <t xml:space="preserve">Train_30006_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">ExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31001_Name</t>
-  </si>
-  <si>
     <t xml:space="preserve">Weapon_KMD_12_UI</t>
   </si>
   <si>
-    <t xml:space="preserve">Train_31004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_헤리콥터리코를_어쎄신</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60008;60009;60010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30007_Desc</t>
+    <t xml:space="preserve">Train_30002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_20001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31002_Name</t>
   </si>
   <si>
     <t xml:space="preserve">Train_31007_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60014;60015;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60006;60007;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">현대무기_대포_288스마</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004;60005;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60011;60012;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60002;60003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_41001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_41002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_40002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_30001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_31003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slow_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50003;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50004;</t>
   </si>
   <si>
     <t xml:space="preserve">30007</t>
   </si>
   <si>
+    <t xml:space="preserve">50005;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50006;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31005</t>
+  </si>
+  <si>
     <t xml:space="preserve">60013;</t>
   </si>
   <si>
@@ -140,58 +332,28 @@
     <t xml:space="preserve">31002</t>
   </si>
   <si>
-    <t xml:space="preserve">30003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50004;</t>
-  </si>
-  <si>
     <t xml:space="preserve">31004</t>
   </si>
   <si>
-    <t xml:space="preserve">30004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50005;</t>
-  </si>
-  <si>
     <t xml:space="preserve">31003</t>
   </si>
   <si>
-    <t xml:space="preserve">50003;</t>
+    <t xml:space="preserve">30001</t>
   </si>
   <si>
     <t xml:space="preserve">50001;</t>
   </si>
   <si>
-    <t xml:space="preserve">50006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60001</t>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31006</t>
   </si>
   <si>
     <t xml:space="preserve">30006</t>
@@ -200,178 +362,16 @@
     <t xml:space="preserve">31001</t>
   </si>
   <si>
-    <t xml:space="preserve">31006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_40002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_41001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_20001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_30001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_41002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slow_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Train_31003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirRangeTrain</t>
+    <t xml:space="preserve">turret_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">range_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EliteExplosionRangeTrain</t>
   </si>
   <si>
     <t xml:space="preserve">EliteElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteExplosionRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteMissileTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteLaserTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteColdAirRangeTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteFireTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteNormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteSniperTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EliteCannonTurretTrain</t>
   </si>
 </sst>
 </file>
@@ -891,42 +891,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>114</v>
+        <v>10</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -935,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -964,69 +964,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="O1" s="0" t="s">
-        <v>27</v>
-      </c>
       <c r="P1" s="0" t="s">
-        <v>114</v>
+        <v>10</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="H2" s="3">
         <v>4</v>
@@ -1056,7 +1056,7 @@
         <v>3</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="N2" s="0">
         <v>0</v>
@@ -1072,13 +1072,13 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1087,10 +1087,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H3" s="3">
         <v>3</v>
@@ -1108,7 +1108,7 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="N3" s="0">
         <v>0</v>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H4" s="3">
         <v>4</v>
@@ -1155,7 +1155,7 @@
         <v>3</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="N4" s="0">
         <v>0</v>
@@ -1164,10 +1164,10 @@
         <v>0</v>
       </c>
       <c r="P4" s="0" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="R4" s="4">
         <v>0</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="3" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3">
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="H5" s="3">
         <v>3</v>
@@ -1206,7 +1206,7 @@
         <v>0.20000000000000001</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="N5" s="0">
         <v>0</v>
@@ -1215,10 +1215,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="R5" s="4">
         <v>25</v>
@@ -1254,69 +1254,69 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="Q1" s="3" t="s">
-        <v>114</v>
+        <v>10</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>112</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D2" s="3">
         <v>250</v>
@@ -1325,10 +1325,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H2" s="3">
         <v>8</v>
@@ -1349,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O2" s="3">
         <v>0</v>
@@ -1360,13 +1360,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="D3" s="3">
         <v>250</v>
@@ -1375,10 +1375,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="H3" s="3">
         <v>8</v>
@@ -1399,7 +1399,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="O3" s="3">
         <v>0</v>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="D4" s="3">
         <v>250</v>
@@ -1425,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="H4" s="3">
         <v>8</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="O4" s="3">
         <v>0</v>
@@ -1460,13 +1460,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3">
         <v>250</v>
@@ -1475,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H5" s="3">
         <v>15</v>
@@ -1499,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O5" s="3">
         <v>0</v>
@@ -1510,13 +1510,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D6" s="3">
         <v>250</v>
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>115</v>
+        <v>8</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H6" s="3">
         <v>11</v>
@@ -1549,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="O6" s="3">
         <v>0</v>
@@ -1560,13 +1560,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="D7" s="3">
         <v>250</v>
@@ -1575,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="H7" s="0">
         <v>13</v>
@@ -1593,13 +1593,13 @@
         <v>1</v>
       </c>
       <c r="L7" s="0">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M7" s="3">
         <v>1</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="O7" s="3">
         <v>0</v>
@@ -1610,13 +1610,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D8" s="3">
         <v>250</v>
@@ -1625,10 +1625,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H8" s="3">
         <v>12</v>
@@ -1649,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="3" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -1673,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="H9" s="0">
         <v>8</v>
@@ -1697,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
@@ -1706,18 +1706,18 @@
         <v>0</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
@@ -1727,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="H10" s="0">
         <v>8</v>
@@ -1751,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
@@ -1760,16 +1760,16 @@
         <v>0</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="3" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -1779,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="H11" s="0">
         <v>8</v>
@@ -1803,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="O11" s="3">
         <v>0</v>
@@ -1812,15 +1812,15 @@
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="3" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
@@ -1830,10 +1830,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H12" s="0">
         <v>15</v>
@@ -1854,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O12" s="3">
         <v>0</v>
@@ -1863,15 +1863,15 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="3" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -1881,10 +1881,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H13" s="0">
         <v>11</v>
@@ -1905,7 +1905,7 @@
         <v>2</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="O13" s="3">
         <v>0</v>
@@ -1914,18 +1914,18 @@
         <v>0</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>118</v>
+        <v>6</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="H14" s="0">
         <v>13</v>
@@ -1953,13 +1953,13 @@
         <v>1</v>
       </c>
       <c r="L14" s="0">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M14" s="3">
         <v>1</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1971,15 +1971,15 @@
         <v>21</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="3" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
@@ -1989,10 +1989,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H15" s="0">
         <v>12</v>
@@ -2013,7 +2013,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="124">
   <si>
     <t xml:space="preserve">EliteMissileTurretTrain</t>
   </si>
@@ -372,6 +372,21 @@
   </si>
   <si>
     <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_39999_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Train_39999_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60001;60002;60003;60008;60009;60010;60011;60012;60013;60014;60015;60017;60018</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">60001;60002;60003;60008;60009;60010;60011;60012;60013;60014;60015;60017;60018;60099</t>
   </si>
 </sst>
 </file>
@@ -1233,7 +1248,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -2025,6 +2040,62 @@
         <v>44</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>39999</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="0">
+        <v>9999</v>
+      </c>
+      <c r="E16" s="0">
+        <v>0</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="0">
+        <v>30</v>
+      </c>
+      <c r="I16" s="0">
+        <v>12</v>
+      </c>
+      <c r="J16" s="0">
+        <v>9999</v>
+      </c>
+      <c r="K16" s="0">
+        <v>5</v>
+      </c>
+      <c r="L16" s="0">
+        <v>0.1</v>
+      </c>
+      <c r="M16" s="0">
+        <v>10</v>
+      </c>
+      <c r="N16" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="O16" s="0">
+        <v>1</v>
+      </c>
+      <c r="P16" s="0">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="R16" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1319,7 +1319,7 @@
         <v>78</v>
       </c>
       <c r="D2" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E2" s="3">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         <v>47</v>
       </c>
       <c r="D3" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E3" s="3">
         <v>0</v>
@@ -1419,7 +1419,7 @@
         <v>66</v>
       </c>
       <c r="D4" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
@@ -1469,7 +1469,7 @@
         <v>30</v>
       </c>
       <c r="D5" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
@@ -1519,7 +1519,7 @@
         <v>61</v>
       </c>
       <c r="D6" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -1569,7 +1569,7 @@
         <v>59</v>
       </c>
       <c r="D7" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
@@ -1619,7 +1619,7 @@
         <v>42</v>
       </c>
       <c r="D8" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E13" s="3">
         <v>0</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1337,7 +1337,7 @@
         <v>8</v>
       </c>
       <c r="J2" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1543,7 +1543,7 @@
         <v>2</v>
       </c>
       <c r="L6" s="3">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M6" s="3">
         <v>2</v>
@@ -1899,7 +1899,7 @@
         <v>2</v>
       </c>
       <c r="L13" s="0">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M13" s="3">
         <v>2</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1047,7 +1047,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>
@@ -1099,13 +1099,13 @@
         <v>5</v>
       </c>
       <c r="J3" s="3">
+        <v>2</v>
+      </c>
+      <c r="K3" s="3">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3">
         <v>3</v>
-      </c>
-      <c r="K3" s="3">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0.20000000000000001</v>
       </c>
       <c r="M3" s="0" t="s">
         <v>55</v>
@@ -1119,7 +1119,7 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1334,16 +1334,16 @@
         <v>8</v>
       </c>
       <c r="I2" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>
       </c>
       <c r="L2" s="3">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="M2" s="3">
         <v>1</v>
@@ -1384,7 +1384,7 @@
         <v>8</v>
       </c>
       <c r="I3" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J3" s="3">
         <v>4</v>
@@ -1393,7 +1393,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="3">
-        <v>0.20000000000000001</v>
+        <v>3</v>
       </c>
       <c r="M3" s="3">
         <v>1</v>
@@ -1434,10 +1434,10 @@
         <v>8</v>
       </c>
       <c r="I4" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J4" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K4" s="3">
         <v>1</v>
@@ -1484,7 +1484,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="3">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J5" s="3">
         <v>50</v>
@@ -1534,16 +1534,16 @@
         <v>11</v>
       </c>
       <c r="I6" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K6" s="3">
         <v>2</v>
       </c>
       <c r="L6" s="3">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="M6" s="3">
         <v>2</v>
@@ -1587,7 +1587,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="0">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K7" s="0">
         <v>1</v>
@@ -1634,16 +1634,16 @@
         <v>12</v>
       </c>
       <c r="I8" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K8" s="3">
         <v>1</v>
       </c>
       <c r="L8" s="3">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M8" s="3">
         <v>1</v>
@@ -1682,7 +1682,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="0">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="J9" s="0">
         <v>10</v>
@@ -1788,7 +1788,7 @@
         <v>8</v>
       </c>
       <c r="I11" s="0">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="J11" s="0">
         <v>30</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1166,9 +1166,6 @@
       <c r="P4" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="Q4" s="0" t="s">
-        <v>94</v>
-      </c>
       <c r="R4" s="4">
         <v>0</v>
       </c>
@@ -1216,9 +1213,6 @@
       </c>
       <c r="P5" s="0" t="s">
         <v>19</v>
-      </c>
-      <c r="Q5" s="0" t="s">
-        <v>87</v>
       </c>
       <c r="R5" s="4">
         <v>25</v>
@@ -1708,9 +1702,6 @@
       <c r="Q9" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>108</v>
-      </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="3" t="s">
@@ -1916,9 +1907,6 @@
       <c r="Q13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="R13" s="3" t="s">
-        <v>96</v>
-      </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="3" t="s">
@@ -1969,9 +1957,6 @@
       </c>
       <c r="Q14" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:17">

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="122">
   <si>
     <t xml:space="preserve">EliteMissileTurretTrain</t>
   </si>
@@ -372,6 +372,15 @@
   </si>
   <si>
     <t xml:space="preserve">EliteElectrickTurretTrain</t>
+  </si>
+  <si>
+    <t>60009;60010;</t>
+  </si>
+  <si>
+    <t>60015;</t>
+  </si>
+  <si>
+    <t>60017;</t>
   </si>
 </sst>
 </file>
@@ -1803,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1956,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -2007,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1543,7 +1543,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3">
         <v>1.4</v>
@@ -1896,7 +1896,7 @@
         <v>10</v>
       </c>
       <c r="K13" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" s="0">
         <v>1.3</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1484,7 +1484,7 @@
         <v>28</v>
       </c>
       <c r="H5" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I5" s="3">
         <v>1.5</v>
@@ -1836,7 +1836,7 @@
         <v>28</v>
       </c>
       <c r="H12" s="0">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I12" s="0">
         <v>3</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="3">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M3" s="0" t="s">
         <v>55</v>
@@ -1396,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3" s="3">
         <v>1</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1209,7 +1209,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="0">
-        <v>0.20000000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="M5" s="0" t="s">
         <v>55</v>
@@ -1745,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="0">
-        <v>0.20000000000000001</v>
+        <v>2</v>
       </c>
       <c r="M10" s="3">
         <v>1</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>1</v>
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>1</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col width="16.42578125" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
@@ -741,6 +741,11 @@
           <t>slow_rate</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>burst_duration</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -803,6 +808,9 @@
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -869,6 +877,9 @@
       <c r="R3" s="4" t="n">
         <v>30</v>
       </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -927,6 +938,9 @@
       <c r="R4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -984,6 +998,9 @@
       </c>
       <c r="R5" s="4" t="n">
         <v>30</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -998,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col width="17.42578125" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
@@ -1108,6 +1125,11 @@
           <t>active_skill_data_id</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>burst_duration</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -1170,6 +1192,9 @@
       <c r="P2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1216,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="4" t="n">
         <v>1</v>
@@ -1231,6 +1256,9 @@
       </c>
       <c r="P3" s="4" t="n">
         <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1294,6 +1322,9 @@
       <c r="P4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1356,6 +1387,9 @@
       <c r="P5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1418,6 +1452,9 @@
       <c r="P6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1480,6 +1517,9 @@
       <c r="P7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1540,6 +1580,9 @@
         <v>0</v>
       </c>
       <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1605,6 +1648,9 @@
           <t>60001</t>
         </is>
       </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1647,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>1</v>
@@ -1669,6 +1715,9 @@
         </is>
       </c>
       <c r="R10" s="4" t="n"/>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1732,6 +1781,9 @@
           <t>60009;60010;</t>
         </is>
       </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1795,6 +1847,9 @@
           <t>60011;60012;</t>
         </is>
       </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1858,6 +1913,9 @@
           <t>60013;</t>
         </is>
       </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1921,6 +1979,9 @@
           <t>60015;</t>
         </is>
       </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1983,6 +2044,9 @@
         <is>
           <t>60017;</t>
         </is>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -741,7 +741,7 @@
           <t>slow_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>burst_duration</t>
         </is>
@@ -810,7 +810,7 @@
       <c r="R2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -853,7 +853,7 @@
         <v>5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>1</v>
@@ -877,7 +877,7 @@
       <c r="R3" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -938,7 +938,7 @@
       <c r="R4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -972,7 +972,7 @@
         <v>5</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>1</v>
@@ -999,7 +999,7 @@
       <c r="R5" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
           <t>active_skill_data_id</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>burst_duration</t>
         </is>
@@ -1192,7 +1192,7 @@
       <c r="P2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M3" s="4" t="n">
         <v>1</v>
@@ -1257,7 +1257,7 @@
       <c r="P3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       <c r="P4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       <c r="P5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       <c r="P6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       <c r="P7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       <c r="P8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
           <t>60001</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="S9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M10" s="4" t="n">
         <v>1</v>
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="R10" s="4" t="n"/>
-      <c r="S10" t="n">
+      <c r="S10" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
           <t>60009;60010;</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="S11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
           <t>60011;60012;</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="S12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
           <t>60013;</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="S13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
           <t>60015;</t>
         </is>
       </c>
-      <c r="S14" t="n">
+      <c r="S14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
           <t>60017;</t>
         </is>
       </c>
-      <c r="S15" t="n">
+      <c r="S15" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1232,7 +1232,7 @@
         <v>6</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>6</v>
@@ -1684,7 +1684,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>6</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1362,7 +1362,7 @@
         <v>20</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>50</v>
@@ -1817,7 +1817,7 @@
         <v>20</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>50</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -764,7 +764,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
@@ -955,7 +955,7 @@
       </c>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>0</v>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>1</v>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>0</v>
@@ -1430,13 +1430,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="M6" s="4" t="n">
         <v>2</v>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>0</v>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>0</v>
@@ -1621,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>1</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="M13" s="4" t="n">
         <v>2</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0</v>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -783,7 +783,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>30</v>
@@ -908,7 +908,7 @@
         <v>4</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>30</v>
@@ -1170,13 +1170,13 @@
         <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>1</v>
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>1</v>
@@ -1560,13 +1560,13 @@
         <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>1</v>
@@ -1621,13 +1621,13 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="M9" s="4" t="n">
         <v>1</v>
@@ -1886,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>1</v>
@@ -2018,13 +2018,13 @@
         <v>0</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="M15" s="4" t="n">
         <v>1</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>1</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>3</v>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>1</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>3</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>0</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1508,7 +1508,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>CannonProjectile</t>
+          <t>CannonShellProjectile</t>
         </is>
       </c>
       <c r="O7" s="4" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>CannonProjectile</t>
+          <t>CannonShellProjectile</t>
         </is>
       </c>
       <c r="O14" s="4" t="n">

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Weapon_MEL_14_UI</t>
+          <t>CannonMortarTop</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1942,7 +1942,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Weapon_MEL_14_UI</t>
+          <t>CannonMortarTop</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1164,13 +1164,13 @@
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>1</v>
@@ -1232,7 +1232,7 @@
         <v>6</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>6</v>
@@ -1300,7 +1300,7 @@
         <v>2</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>1</v>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>1</v>
@@ -1371,7 +1371,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>1</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>3</v>
@@ -1554,13 +1554,13 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>1</v>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>1</v>
@@ -1684,7 +1684,7 @@
         <v>6</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>6</v>
@@ -1754,7 +1754,7 @@
         <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>1</v>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>1</v>
@@ -1826,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="M12" s="4" t="n">
         <v>1</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>3</v>
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>1</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1362,7 +1362,7 @@
         <v>28</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>50</v>
@@ -1430,16 +1430,16 @@
         <v>0</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>26</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>40</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>30</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -966,19 +966,19 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>30</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="R10" s="4" t="n"/>
       <c r="S10" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>1.2</v>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>40</v>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>1</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>3</v>
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>0</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -993,7 +993,7 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>60004;60005;</t>
+          <t>60004;60020;</t>
         </is>
       </c>
       <c r="R5" s="4" t="n">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>60015;</t>
+          <t>60018;60019;</t>
         </is>
       </c>
       <c r="S14" s="4" t="n">

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>30</v>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>7</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>30</v>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>7</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -875,7 +875,7 @@
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="S3" s="4" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Train_41001_Name</t>
+          <t>Train_40001_Name</t>
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -950,7 +950,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Train_41002_Name</t>
+          <t>Train_40002_Name</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="R5" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="S5" s="4" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Train_31001_Name</t>
+          <t>Train_30001_Name</t>
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Train_31002_Name</t>
+          <t>Train_30002_Name</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Train_31003_Name</t>
+          <t>Train_30003_Name</t>
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Train_31004_Name</t>
+          <t>Train_30004_Name</t>
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Train_31005_Name</t>
+          <t>Train_30005_Name</t>
         </is>
       </c>
       <c r="C13" s="4" t="n"/>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Train_31006_Name</t>
+          <t>Train_30006_Name</t>
         </is>
       </c>
       <c r="C14" s="4" t="n"/>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Train_31007_Name</t>
+          <t>Train_30007_Name</t>
         </is>
       </c>
       <c r="C15" s="4" t="n"/>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1645,7 +1645,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>60001</t>
+          <t>60001;60021;</t>
         </is>
       </c>
       <c r="S9" s="4" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>60002;60003;</t>
+          <t>60002;60003;60022;</t>
         </is>
       </c>
       <c r="R10" s="4" t="n"/>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>60011;60012;</t>
+          <t>60011;60012;60023;</t>
         </is>
       </c>
       <c r="S12" s="4" t="n">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>60013;</t>
+          <t>60013;60024;60025;</t>
         </is>
       </c>
       <c r="S13" s="4" t="n">

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1235,7 +1235,7 @@
         <v>3.8</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>1</v>
@@ -1300,7 +1300,7 @@
         <v>2</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>1</v>
@@ -1687,7 +1687,7 @@
         <v>3.8</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>1</v>
@@ -1754,7 +1754,7 @@
         <v>2</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>1</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1817,7 +1817,7 @@
         <v>22</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>50</v>
@@ -1886,16 +1886,16 @@
         <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>0</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>1</v>
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>1</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I2" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>1</v>
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>1</v>
@@ -1365,7 +1365,7 @@
         <v>1.2</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>1</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>1</v>
@@ -1820,7 +1820,7 @@
         <v>1.2</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>1</v>
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>1</v>

--- a/Assets/02_Resources/Data/TrainData.xlsx
+++ b/Assets/02_Resources/Data/TrainData.xlsx
@@ -1976,7 +1976,7 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>60018;60019;</t>
+          <t>60018;60019;60015;</t>
         </is>
       </c>
       <c r="S14" s="4" t="n">
